--- a/data/source/2026-09-28/BSR_ES_Mite-Vacuum_Top50_2026-09-28.xlsx
+++ b/data/source/2026-09-28/BSR_ES_Mite-Vacuum_Top50_2026-09-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="527">
   <si>
     <t>#</t>
   </si>
@@ -232,361 +232,1454 @@
     <t>B0FPQMRBYZ</t>
   </si>
   <si>
-    <t>https://www.amazon.esundefined</t>
-  </si>
-  <si>
-    <t>KÄRCHER Limpiador de colchones VCH 4 UVClean, 500 W, Peso: 2,1 kgsLimpieza profunda e higiénica con luz UV-C, rodillo percu</t>
+    <t>Marca: KÄRCHER | Función especial: Tecnología UV-C-Light y limpieza de colchones | Tipo de filtro: Espuma | Recomendación de superficie: Tapicería | Fuente de alimentación: Eléctrico con cable | Voltaje: 240 Voltios | Componentes incluidos: VCH 4 UVClean, rodillo de golpe, 2 filtros de espuma y 3 filtros de protección del motor | ¿Es inalámbrico?: No | Peso del producto: 2,5 Kilogramos | Capacidad: 400 ml</t>
+  </si>
+  <si>
+    <t>KÄRCHER</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/stores/K%C3%A4rcherEspa%C3%B1a/page/B353BDC4-AECC-4400-8FE8-010A626D7853?lp_asin=B0FPQMRBYZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>KÄRCHER Limpiador de colchones VCH 4 UVClean, 500 W, Peso: 2,1 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limpieza profunda e higiénica: El VCH 4 UVClean limpia colchones, tapizados, cojines y otras superficies textiles, eliminando suciedad visible e invisible
+Tecnología triple: El rodillo vibratorio con golpes elimina la suciedad profunda y los ácaros, que luego se aspiran a fondo; La luz UV-C neutraliza hasta el 99,9 % de las bacterias y ácaros
+Sistema de contenedores de 2 cámaras: La tecnología ciclónica asegura que la suciedad gruesa se recoja en una cámara y el polvo fino en la otra; esto garantiza una potencia de succión constante y elevada
+Diseño compacto: El dispositivo con mango ergonómico pesa 2,1 kg y permite trabajar durante largos períodos sin fatiga; después de la limpieza, se puede guardar ocupando poco espacio
+Contenido del paquete: Limpiador de colchones Kärcher VCH 4 UVClean, rodillo percutor, 2 filtros de espuma, 3 filtros de protección del motor</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0FPQMRBYZ?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/81RtcozDdwL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/81RtcozDdwL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras:Aspiradoras de futones</t>
+  </si>
+  <si>
+    <t>Hogar y cocina</t>
+  </si>
+  <si>
+    <t>Aspiradoras de futones</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>2025-10-02</t>
+  </si>
+  <si>
+    <t>AMZ</t>
+  </si>
+  <si>
+    <t>17天</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Opción Amazon</t>
+  </si>
+  <si>
+    <t>2,5 Kilogramos</t>
+  </si>
+  <si>
+    <t>2.50 kg</t>
+  </si>
+  <si>
+    <t>39,3l. x 29,3an. x 19,2al. centímetros</t>
+  </si>
+  <si>
+    <t>3.2 kg</t>
+  </si>
+  <si>
+    <t>3.20 kg</t>
+  </si>
+  <si>
+    <t>39.1 x 29.4 x 19.3 cm</t>
+  </si>
+  <si>
+    <t>39.10 x 29.40 x 19.30 cm</t>
+  </si>
+  <si>
+    <t>标准包裹</t>
   </si>
   <si>
     <t>B0GXVR9CY9</t>
   </si>
   <si>
-    <t>Jimmy BX8 Aspirador de Mano para Colchones, 600W 15kPa Succion Aspiradora Antiacaros con Ultravioleta UV-C, Secado Termico 65</t>
+    <t>Color: Violeta</t>
+  </si>
+  <si>
+    <t>Marca: Jimmy | Función especial: Aire caliente a 65℃, Eliminación ultrasónica de ácaros, Filtración dual ciclónica, Pantalla LED, Modo de golpeteo fuerte y suave, Succión potente de 15 kPa, Luz UV-C, Sensor de polvo | Tipo de filtro: Filtro MIF de grado HEPA | Recomendación de superficie: Colchones, camas, sofás, alfombras, tapicería | Fuente de alimentación: Eléctrico con cable | Voltaje: 230 Voltios | Componentes incluidos: Aspiradora de colchón, Cepillo de limpieza, Filtro, Manual de usuario | ¿Es inalámbrico?: No | Peso del producto: 2,1 Kilogramos | Capacidad: 500 ml</t>
+  </si>
+  <si>
+    <t>Jimmy</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/Jimmy/b/ref=bl_dp_s_web_17484947031?ie=UTF8&amp;node=17484947031&amp;field-lbr_brands_browse-bin=Jimmy</t>
+  </si>
+  <si>
+    <t>Jimmy BX8 Aspirador de Mano para Colchones, 600W 15kPa Succion Aspiradora Antiacaros con Ultravioleta UV-C, Secado Termico 65℃, Deteccion Inteligente Sensor, Función de Iones Negativos (Violeta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aspiradora de gran potencia: este dispositivo de limpieza está equipado con una potencia de 600 vatios y puede proporcionar una succión de 15 kpa, con la boquilla de 240 mm de ancho, lo ayuda enormemente a limpiar la cama en solo unos minutos
+Aspiradora con luz UV-C: Ayuda a eliminar el 99% de ácaros y alérgenos de camas, colchones, sábanas o sofás. La luz se apaga automáticamente al levantar el aparato, lo que hace que su uso sea fácil y seguro
+Equipado con sensor inteligente: sensor de polvo inteligente incorporado, puede ayudarlo a juzgar el grado de limpieza a través del índice y los cambios de color en la pantalla LED, lo que le permite ahorrar tiempo
+Limpieza más eficaz: el cepillo giratorio se ha mejorado con una tira de goma y un cepillo giratorio de metal, que no se enreda con el pelo y es más fácil de acariciar y enrollar, lo que hace que la limpieza de tapicerías sea más eficaz. Ideal para familias con mascotas
+Función de viento caliente: con una tecnología única de calentamiento por aire caliente, el BX8 puede alcanzar temperaturas de hasta 65 °C, no solo ayuda a eliminar los ácaros del polvo y la humedad, sino que también hace que las camas sean suaves y lujosas
+Limpieza profunda: Equipado con un emisor de iones negativos integrado, puede liberar iones negativos de forma continua durante el uso, lo que garantiza un aire más limpio</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0GXVR9CY9?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71um1FaVwRL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41bn7Lrs3VL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0GY2TN25G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Fenglian home</t>
+  </si>
+  <si>
+    <t>CN(HK)</t>
+  </si>
+  <si>
+    <t>KWUN TONG HONG KONG 999077 HK</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AUUOYWQE00J1M</t>
+  </si>
+  <si>
+    <t>2,1 Kilogramos</t>
+  </si>
+  <si>
+    <t>2.10 kg</t>
+  </si>
+  <si>
+    <t>28l. x 20an. x 34al. centímetros</t>
+  </si>
+  <si>
+    <t>3.17 kg</t>
+  </si>
+  <si>
+    <t>39 x 33 x 20.2 cm</t>
+  </si>
+  <si>
+    <t>39.00 x 33.00 x 20.20 cm</t>
+  </si>
+  <si>
+    <t>B0CHMPZVZT</t>
+  </si>
+  <si>
+    <t>Marca: JIGOO | Función especial: Sensor de ácaros, luz UV, cepillo metálico innovador | Tipo de filtro: Cartucho | Recomendación de superficie: Tapicería | Fuente de alimentación: Eléctrico con cable | Voltaje: 220 Voltios | Componentes incluidos: [Componentes básicos] | ¿Es inalámbrico?: No | Peso del producto: 1,8 Kilogramos | Capacidad: 479 g</t>
+  </si>
+  <si>
+    <t>JIGOO</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/stores/JIGOO-ES/page/23E9C8F3-B11D-41BE-B25B-391D7999E178?lp_asin=B0CHMPZVZT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>JIGOO J300 - Aspirador antiácaros con Sensor de ácaros y luz UV, 500 W, con indicador LED Inteligente, para alérgicos, Elimina el 99,9% de alérgenos, para colchones, Camas y sofás</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【Sensor inteligente de ácaros】: el aspirador JIGOO J300 está equipado con un sensor inteligente que puede detectar los ácaros en el entorno de alta precisión. Una pantalla LED inteligente muestra el índice de ácaros y el estado de limpieza en tiempo real para ayudarlo a limpiar de forma inteligente.
+Aspirador antiácaros eficaz: la aspiradora JIGOO J300 para colchones cuenta con una potencia de 500 W y una potencia de succión de 13 kpa, así como un innovador rodillo de metal que golpea continuamente y con fuerza a 12.000 revoluciones por minuto sobre colchones y tejidos para eliminar eficazmente los ácaros en el interior del colchón, eliminando eficazmente los ácaros en el interior del colchón. está protegido. Te ofrece una limpieza profunda y eficaz.
+【99,9% eficaz eliminación de ácaros】: el aspirador JIGOO J300 está equipado con una lámpara UV de 254 nm y tecnología ultrasónica que puede matar eficazmente los ácaros y las bacterias en un 99,99 % de profundidad. La tecnología ultrasónica evita la proliferación de ácaros y garantiza la eliminación completa de ácaros, polvo, caspa y otros alérgenos ocultos en la profundidad del colchón.
+【Sistema de filtrado eficaces】: el aspirador antiácaros JIGOO J300 está equipado con dos recipientes, uno para el filtro y otro para el almacenamiento de polvo. Este diseño evita obstrucciones en el filtro y prolonga el tiempo de limpieza. Además, separa eficazmente los ácaros del polvo y otros alérgenos del aire, los mantiene frescos y crea un ambiente saludable.
+【Esterilización y deshumidificación a alta temperatura】: el aspirador JIGOO J300 con luz UV se puede calentar rápidamente a 55 grados Celsius para penetrar profundamente en el colchón, matar ácaros y deshumidificar el colchón. Además, el ganador de la prueba de ácaros JIGOO J300 para colchones ha pasado estrictas pruebas de calidad y ha recibido todas las certificaciones relevantes para aspiradoras de mano, lo que muestra su notable rendimiento entre productos similares.</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/dp/B0CHMPZVZT?psc=1</t>
+  </si>
+  <si>
+    <t>https://images-na.ssl-images-amazon.com/images/I/71FO+Ga+gLL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2023-10-18</t>
+  </si>
+  <si>
+    <t>Bell-shop</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3HDNBYVK69SMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales reciclados (Global Recycled Standard)
+Químicos más seguros (Global Recycled Standard)
+Bienestar laboral (Global Recycled Standard)</t>
+  </si>
+  <si>
+    <t>1,8 kg</t>
+  </si>
+  <si>
+    <t>1.80 kg</t>
+  </si>
+  <si>
+    <t>28 x 24 x 20 cm</t>
+  </si>
+  <si>
+    <t>28.00 x 24.00 x 20.00 cm</t>
+  </si>
+  <si>
+    <t>2.41 kg</t>
+  </si>
+  <si>
+    <t>34.3 x 28.1 x 27.9 cm</t>
+  </si>
+  <si>
+    <t>34.30 x 28.10 x 27.90 cm</t>
+  </si>
+  <si>
+    <t>轻型标准大件</t>
+  </si>
+  <si>
+    <t>B0HBMBNXJ1</t>
+  </si>
+  <si>
+    <t>Marca: RANJIMA | Función especial: Luz UV | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Tapicería | Fuente de alimentación: Batería | Componentes incluidos: 1 cable de carga, 1 limpiador al vacío, 1 × Manual de instrucciones | ¿Es inalámbrico?: Sí | Capacidad: 200 ml | Usos recomendados para el producto: Cama, Pelo de mascota | Factor de forma: De mano</t>
+  </si>
+  <si>
+    <t>RANJIMA</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=RANJIMA</t>
+  </si>
+  <si>
+    <t>Aspirador de ácaros para colchón, recargable, con luz UV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【Combinación triple contra alérgenos】Con solo pulsar un botón, activa simultáneamente tres funciones de limpieza: golpeo intenso, succión fuerte y luz germicida UV-C. Nuestro limpiador de colchones elimina eficazmente hasta el 99,9 % de los ácaros del polvo y las bacterias, así como los desencadenantes de alergias visibles e invisibles como el pelo de las mascotas y el polvo doméstico. Simplemente enciéndalo, pase por la superficie y disfrute de una tapicería higiénica y limpia, la solución ideal para colchones, sofás y otros tejidos que necesitan una limpieza rápida y profunda.
+Potente sistema de succión de 10 kPa: gracias a una potencia de succión de 10 kPa, el aspirador de colchón elimina de forma fiable el polvo, las micropartículas y los residuos de superficies delicadas como camas, colchones, tapicería y alfombras. Así se garantiza una limpieza profunda en cada uso. Por favor, utilice el dispositivo limpiador de ácaros exclusivamente en superficies textiles suaves y no en suelos duros o mesas.
+【Inalámbrico y portátil gracias a la batería】La batería recargable permite hasta una hora de tiempo de funcionamiento después de una carga completa. Sin cables molestos, el aspirador antiácaros ofrece la máxima flexibilidad de forma inalámbrica, ya sea en casa, en viajes o en el camping. La práctica carga USB-C lo convierte en el compañero perfecto para viajar y permite una limpieza espontánea de cualquier superficie de tapicería.
+Práctico recipiente de recogida lavable: el depósito de polvo de gran volumen con sistema de filtro multietapa evita obstrucciones y asegura una potencia de succión constante. Tanto el filtro HEPA extraíble como el recipiente se pueden limpiar fácilmente con agua corriente. De este modo, el rendimiento sigue siendo alto y una limpieza regular es posible sin esfuerzo. Importante: siempre deje que el filtro se seque completamente antes de su próximo uso.
+【Silencioso en el uso】La aspiradora antiácaros funciona muy silenciosamente, por lo que se puede utilizar incluso en tiempos de descanso o por la noche sin molestar a los demás. Ideal para hogares en los que se valora un ambiente tranquilo, ya sea mientras duermes, estudias o te relajas.
+Versátil para superficies textiles: ya sea colchones, sofás, alfombras, almohadas, cunas o esterillas deportivas, la aspiradora para colchón es adecuada para todas las superficies de tela del hogar. El manejo inalámbrico te permite llegar a lugares de difícil acceso sin esfuerzo. Cree un entorno de vida limpio y sin alérgenos con este ayudante confiable.</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/dp/B0HBMBNXJ1?psc=1</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/31DuAHlA2DL._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>25l. x 20an. x 11al. centímetros</t>
+  </si>
+  <si>
+    <t>B0HFRH1NNC</t>
+  </si>
+  <si>
+    <t>Color: Blanco + Oro Champán</t>
+  </si>
+  <si>
+    <t>Marca: Lubluelu | Función especial: Luz UV | Recomendación de superficie: Tapicería | ¿Es inalámbrico?: Sí | Peso del producto: 1000 Gramos | Capacidad: 650 ml | Usos recomendados para el producto: colchones, sofás, alfombras, ropa de cama y otros textiles | Factor de forma: De mano | Color: Blanco + Oro Champán | Dimensiones del producto: 30l. x 25an. x 18al. centímetros</t>
+  </si>
+  <si>
+    <t>Lubluelu</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/stores/Lubluelu/page/6949B717-1950-436B-B468-8BFB57AEF209?lp_asin=B0HFRH1NNC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>Lubluelu Aspirador antiácaros 20 kPa para colchones con luz UV-C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Potente succión de 20 kPa y resistente cepillo de rodillo metálico: el potente motor recoge de forma fiable el polvo, la suciedad, los ácaros del polvo, las escamas de piel y el pelo de mascotas. El resistente cepillo de rodillo metálico realiza intensos movimientos de golpeteo para ayudar a limpiar en profundidad colchones, sofás, alfombras, ropa de cama y peluches.
+Limpieza profunda con luz UV-C, vibración ultrasónica y calor: la luz UV-C, la vibración mecánica de golpeteo y el calor trabajan conjuntamente para limpiar a fondo las superficies textiles. Las partículas desprendidas, el polvo y los alérgenos se aspiran posteriormente gracias a la potente succión de 20 kPa. Ideal para colchones, camas, sofás y otros textiles.
+Hasta un 99,99 % menos de alérgenos y limpieza suave: la limpieza se realiza sin aditivos químicos y combina tecnología UV-C, vibración y calor. Ayuda a reducir los alérgenos, los ácaros del polvo y las partículas finas, por lo que es especialmente adecuado para hogares con niños, mascotas y personas alérgicas.
+Para colchones, sofás, alfombras y otros textiles: el aspirador antiácaros está especialmente diseñado para limpiar directamente grandes superficies textiles. Elimina el polvo, las escamas de piel y el pelo de mascotas de colchones, sofás, alfombras, ropa de cama y tapicerías, y ayuda a mantener una higiene adecuada en toda la casa.
+Uso cómodo con cable de 4 m y depósito de polvo fácil de limpiar: el cable de 4 metros ofrece un amplio radio de movimiento y permite una limpieza flexible sin necesidad de cambiar de toma con frecuencia. El diseño compacto facilita el manejo sobre colchones y muebles tapizados. El depósito de polvo es fácil de vaciar y permite limpiar el filtro cómodamente.
+Los ácaros del polvo no son visibles a simple vista y suelen encontrarse en los textiles, donde, entre otras cosas, se alimentan de escamas de piel. El aspirador antiácaros Lubluelu combina luz UV-C, calor y vibración para desprender y aspirar posteriormente partículas, polvo y alérgenos de forma fiable. La limpieza profunda ayuda a eliminar hasta el 99,99 % de los alérgenos y contribuye a crear un entorno de vida más limpio.</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/dp/B0HFRH1NNC?psc=1</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/41WpJwb0PhL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0G654P9MD</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>12天</t>
+  </si>
+  <si>
+    <t>1 kg</t>
+  </si>
+  <si>
+    <t>1,000.00 g</t>
+  </si>
+  <si>
+    <t>42 x 31 x 18 cm</t>
+  </si>
+  <si>
+    <t>42.00 x 31.00 x 18.00 cm</t>
   </si>
   <si>
     <t>B0GMPVWCZM</t>
   </si>
   <si>
-    <t>Elecbee Aspirador de ácaros inalámbrico para colchón, Aspirador de ácaros con luz UV, Pantalla LED, aspiradora de colchón ult</t>
+    <t>Color: Morado</t>
+  </si>
+  <si>
+    <t>Marca: Elecbee | Función especial: Luz UV | Fuente de alimentación: Batería | ¿Es inalámbrico?: Sí | Usos recomendados para el producto: colchones, sofás, moquetas | Factor de forma: De mano | Color: Morado | Dimensiones del producto: 20l. x 30an. x 20al. centímetros | Fabricante: Elecbee | Número de productos: 1</t>
+  </si>
+  <si>
+    <t>Elecbee</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/Elecbee/b/ref=bl_dp_s_web_51202246031?ie=UTF8&amp;node=51202246031&amp;field-lbr_brands_browse-bin=Elecbee</t>
+  </si>
+  <si>
+    <t>Elecbee Aspirador de ácaros inalámbrico para colchón, Aspirador de ácaros con luz UV, Pantalla LED, aspiradora de colchón ultrasónica, aspiradora de Mano para colchón, sofá, moqueta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【18.000 golpes de alta frecuencia por minuto】El diseño de sacudida similar al de una mano extrae profundamente los cadáveres de ácaros y las escamas de la piel.
+【13000Pa de succión】Una fuerte succión lleva la suciedad a la superficie y la elimina inmediatamente. Te ofrece una limpieza profunda y eficaz.
+【Esterilización doble UV+ultrasonido】 La tecnología de esterilización UV limpia a fondo, UV inactiva los ácaros, el ultrasonido inhibe la reproducción, la capacidad de succión y limpieza es superior al 99 %.
+【Limpieza inteligente de cuatro modos】 Demite/ultrasonido/cepillo de rodillo/esterilización UV cuatro modos se cambian con un botón y la pantalla LED se muestra claramente.
+【Diseño inalámbrico】 El aspirador de ácaros tiene un diseño inalámbrico, carga rápida tipo C, deshazte de enchufes y cables, disponible en sofás/colchones en cualquier lugar.</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0GMPVWCZM?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/81J2yw2XZnL._AC_UL300_SR300,200_.jpg</t>
-  </si>
-  <si>
-    <t>B0HFRH1NNC</t>
-  </si>
-  <si>
-    <t>Lubluelu Aspirador antiácaros 20 kPa para colchones con luz UV-CsLimpiador de colchones de limpieza profunda, elimina hasta</t>
-  </si>
-  <si>
-    <t>https://www.amazon.es/dp/B0HFRH1NNC?psc=1</t>
-  </si>
-  <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41tqM0+3BpL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0H45T73K1</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>WUHAN RENHOTEC TECHNOLOGY LTD</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>武汉市 洪山区 湖北省 430070 CN</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WTTH4P2M430O</t>
+  </si>
+  <si>
+    <t>2 kg</t>
+  </si>
+  <si>
+    <t>2.00 kg</t>
+  </si>
+  <si>
+    <t>20l. x 30an. x 20al. centímetros</t>
   </si>
   <si>
     <t>B0D3QGFGR8</t>
   </si>
   <si>
-    <t>JIGOO Aspiradora de Ácaros con Sensor de Ácaros y Pantalla LED Inteligente, Aspiradora Antiácaros para Colchones con luz UV,</t>
+    <t>Marca: JIGOO | Función especial: Inalámbrico, con_cable | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Colchón y revestimiento | Fuente de alimentación: Batería | Componentes incluidos: Filtro HEPA, lámpara UV, cable de alimentación de 5 metros | ¿Es inalámbrico?: Sí | Vataje: 500 vatios | Succión máxima: 13 Centímetros | Usos recomendados para el producto: Para colchones y sofás</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/stores/JIGOO-ES/page/23E9C8F3-B11D-41BE-B25B-391D7999E178?lp_asin=B0D3QGFGR8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>JIGOO Aspiradora de Ácaros con Sensor de Ácaros y Pantalla LED Inteligente, Aspiradora Antiácaros para Colchones con luz UV, Combate Las chinches, Elimina el 99,9% de los alérgenos, Especial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JIGOO Aspirador de ácaros con indicador LED
+Wattage: 500.0 watts</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0D3QGFGR8?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/716CxESQq9L._AC_UL300_SR300,200_.jpg</t>
-  </si>
-  <si>
-    <t>B0CHMPZVZT</t>
-  </si>
-  <si>
-    <t>JIGOO J300 - Aspirador antiácaros con Sensor de ácaros y luz UV, 500 W, con indicador LED Inteligente, para alérgicos, Elimin</t>
-  </si>
-  <si>
-    <t>https://www.amazon.es/dp/B0CHMPZVZT?psc=1</t>
-  </si>
-  <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71FO+Ga+gLL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/716CxESQq9L._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>ZILLOW TECH</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>ESPLUGUES DE LLOBREGAT BARCELONA 08950 ES</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3DJH46Q40BXN4</t>
+  </si>
+  <si>
+    <t>1,99 kg</t>
+  </si>
+  <si>
+    <t>1.99 kg</t>
+  </si>
+  <si>
+    <t>30l. x 24an. x 21al. centímetros</t>
+  </si>
+  <si>
+    <t>34.8 x 28.5 x 19.5 cm</t>
+  </si>
+  <si>
+    <t>34.80 x 28.50 x 19.50 cm</t>
+  </si>
+  <si>
+    <t>B0HG11J16S</t>
+  </si>
+  <si>
+    <t>Marca: Beghdhu | Capacidad: 200 ml | Factor de forma: De mano | Color: Blanco</t>
+  </si>
+  <si>
+    <t>Beghdhu</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Beghdhu</t>
+  </si>
+  <si>
+    <t>Aspiradora Antiacaros para Colchones sin Cable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【Aspiradora de colchón con fuerte succión】Nuestra aspiradora de cama tiene una fuerte succión y una alta frecuencia de más de 6.000 revoluciones por minuto con doble cabezal de vibración, lo que elimina fácilmente el polvo superficial y oculto y le ahorra tiempo
+【Sistema de filtración HEPA de 3 niveles】El depósito de polvo de gran capacidad y sistema de filtración multietapa evita obstrucciones. El filtro extraíble y el depósito de polvo son fáciles de limpiar. Por favor, seca el filtro después del lavado antes de volver a colocarlo en la aspiradora
+Fuerte penetración】253,7 nm de luz violeta y almohadilla de pulsación doble oscilante. La vibración de alta frecuencia de la almohadilla de pulsaciones disuelve el polvo y la suciedad y lleva el polvo a la superficie de la tela. La aspiradora de colchón absorbe el polvo de manera eficiente, y la luz violeta puede limpiar profundamente la tela nuevamente de manera efectiva
+【Depósito de polvo lavable y visible】El depósito de polvo acoplable del limpiador de colchones es fácil de limpiar y se puede limpiar directamente con agua corriente. Limpieza regular sin problemas de succión o polvo obstruido. Nota: el filtro debe secarse antes de reutilizarlo
+【Ámbito de aplicación】La aspiradora para colchón aspira fácilmente el pelo de animales y la caspa, etc. Adecuado para superficies de tela como colchones, sábanas, almohadas, alfombras, sofás de tela, etc. El diseño silencioso no molesta a los bebés o mascotas que duermen</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/dp/B0HG11J16S?psc=1</t>
+  </si>
+  <si>
+    <t>https://images-na.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>2026-08-29</t>
+  </si>
+  <si>
+    <t>BeiBoGuanShi</t>
+  </si>
+  <si>
+    <t>武汉市 湖北 430080 CN</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2DJZ6ZEQ14JUA</t>
+  </si>
+  <si>
+    <t>200 g</t>
+  </si>
+  <si>
+    <t>200.00 g</t>
+  </si>
+  <si>
+    <t>6 x 4 x 8 cm</t>
+  </si>
+  <si>
+    <t>6.00 x 4.00 x 8.00 cm</t>
+  </si>
+  <si>
+    <t>8 x 8 x 4 cm</t>
+  </si>
+  <si>
+    <t>8.00 x 8.00 x 4.00 cm</t>
+  </si>
+  <si>
+    <t>大号信封</t>
+  </si>
+  <si>
+    <t>B0GHQLQBYD</t>
+  </si>
+  <si>
+    <t>Marca: ALLILUYAA | Función especial: Luz UV, Filtro Antialérgenos, Portátil, Compacto | Recomendación de superficie: Tapicería | Fuente de alimentación: Transformador de carga | Componentes incluidos: batiente, luz UV-C, filtro | ¿Es inalámbrico?: No | Succión máxima: 20000 Milímetros | Usos recomendados para el producto: alfombras, sofás de tela, eliminación de pelo de animales | Factor de forma: De mano | Color: 1</t>
+  </si>
+  <si>
+    <t>ALLILUYAA</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/stores/ALILILUYAA/page/6F2D9C3F-3247-41D0-93BE-BD3270082609?lp_asin=B0GHQLQBYD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
+    <t>Aspiradora Antiacaros, Aspirador Acaros Sofa y Colchon con Una Gran Potencia de Aspiración, Aspirador Antiacaros para Colchones y Sofás Ropa de Cama y Sofás de Tela (Blanco)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASPIRADOR PARA COLCHONES LIGERO Y COMPACTO: Este aspirador de ácaros para colchones está equipado con una función 3 en 1 que combina golpeadores de alta frecuencia, una potente aspiración y una luz UV-C. Cuenta con una doble placa batidora de pulsación, una luz UV-C de 253,7 nm, que ofrece un área de limpieza más amplia y una mayor eficiencia de limpieza.
+SISTEMA DE FILTRACIÓN DE ALTO RENDIMIENTO: Este aspirador de ácaros filtra el 99,97% de las partículas finas de hasta 0,3 micras. El sistema de filtración completamente sellado separa eficazmente el aire limpio sin fugas. El filtro extraíble debe limpiarse regularmente para evitar pérdidas de succión y obstrucciones, manteniendo así un buen rendimiento de aspiración.
+ALTA POTENCIA DE ASPIRACIÓN: El aspirador para sofás y colchones funciona en modo batidor con 8000 vibraciones por minuto, lo que elimina eficazmente la suciedad incrustada en el interior del colchón. El potente modo de aspiración de 10 kPa puede aspirar sin esfuerzo el polvo y la suciedad, garantizando así un hogar limpio y confortable.
+DEPÓSITO DE POLVO TRANSPARENTE Y LAVABLE: El depósito de polvo del aspirador de ácaros está diseñado como un modelo de inserción, es fácil de limpiar y se puede enjuagar directamente bajo el grifo. Una limpieza regular previene molestas pérdidas de succión u obstrucciones. Nota: El filtro debe secarse después de la limpieza antes de volver a utilizarlo.
+ÁMBITOS DE APLICACIÓN: El aspirador de ácaros para colchones aspira sin esfuerzo pelo de animales y células muertas de la piel, etc. Es adecuado para superficies de tela como colchones, sábanas, almohadas, alfombras, sofás de tela, etc. Su diseño de bajo ruido no molesta a los bebés ni a las mascotas que duermen.</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/dp/B0GHQLQBYD?psc=1</t>
+  </si>
+  <si>
+    <t>https://images-na.ssl-images-amazon.com/images/I/610gU-iwIJL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>2026-03-28</t>
+  </si>
+  <si>
+    <t>HONGTELL</t>
+  </si>
+  <si>
+    <t>bayuquan Liao Ning 115007 CN</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ASTEKNQOF9QUQ</t>
+  </si>
+  <si>
+    <t>620 g</t>
+  </si>
+  <si>
+    <t>620.00 g</t>
+  </si>
+  <si>
+    <t>10l. x 10an. x 10al. milímetros</t>
+  </si>
+  <si>
+    <t>25.3 x 20.8 x 11.1 cm</t>
+  </si>
+  <si>
+    <t>25.30 x 20.80 x 11.10 cm</t>
+  </si>
+  <si>
+    <t>小包裹</t>
   </si>
   <si>
     <t>B0GFCJ4JWY</t>
   </si>
   <si>
-    <t>PEXCHO Aspirador de ácaros PM600 con luz UV, 500 W, para alérgicos, Elimina el 99,9% de los ácaros del Polvo, alérgenos, Pelo</t>
+    <t>Color: Gris Plateado Violeta</t>
+  </si>
+  <si>
+    <t>Marca: PEXCHO | Función especial: HEPA,U-V Luz,Filtro lavable,Sensores de alta precisión,Limpieza sin manchas,Ruedas | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Colchones, sofás, alfombras, almohadas, sábanas, juguetes de peluche | Fuente de alimentación: Eléctrico con cable | Voltaje: 230 Voltios | Componentes incluidos: Filtro HEPA | ¿Es inalámbrico?: No | Vataje: 500 vatios | Usos recomendados para el producto: Colchones, sofás, alfombras, almohadas, sábanas, juguetes de peluche</t>
+  </si>
+  <si>
+    <t>PEXCHO</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=PEXCHO</t>
+  </si>
+  <si>
+    <t>PEXCHO Aspirador de ácaros PM600 con luz UV, 500 W, para alérgicos, Elimina el 99,9% de los ácaros del Polvo, alérgenos, Pelo de Animales de colchones, alfombras y sofás</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Succión superfuerte: la aspiradora PEXCHO está equipada con motor de 500 W. Probado en laboratorio con una fuerza de succión de 15 kPa penetra las fibras del colchón de 20 cm de profundidad. Elimina el 99,9% de ácaros, polvo y escamas de la piel de camas, sofás y alfombras. Depósito de polvo doble mejorado + sistema de filtro HEPA separa eficazmente incluso los alérgenos persistentes. Disfrute de las vías respiratorias liberadas y un sueño reparador para toda la familia!
+Comentarios en tiempo real sobre los niveles de ácaros: indicador LED para mostrar la carga de partículas, equipado con un aspirador de ácaros con luz ultravioleta y ultrasonido, que inhibe eficazmente la proliferación de nuevos ácaros del polvo. Las personas alérgicas ya no sufren de irritantes ocultos por la noche, tienen que despedirse de la picazón/estornudos inexplicables. (El sensor de gravedad asegura que la luz ultravioleta se apague automáticamente al levantar el dispositivo)
+Secado suave: el aspirador antiácaros para colchones afloja los ácaros rebeldes con una frecuencia de impacto de 60.000/min y los aspira inmediatamente. Aire caliente constante a 65 °C (≈ 3 horas de luz solar directa). Seca los colchones de manera eficiente, destruye los ácaros en la fuente, por lo que las cunas y los peluches vuelven a ser suaves como las nubes. Crea un ambiente de ensueño y libre de alérgenos para que tu hijo crezca.
+Ideal para dueños de mascotas: el cepillo de rodillo de aleación de aluminio hace que el pelo de las mascotas de pelo largo se enrede. El depósito de polvo de 0,18 litros puede contener la cantidad de pelo que tres gatos de pelo largo pierden al cambiar el pelaje una vez. Con el cable de 4 m, la potente aspiradora también puede eliminar el pelo que dejan los gatos mientras juegan en las esquinas de los sofás y alfombras. Disfruta sin preocupaciones del tiempo íntimo de jugar.
+Seguro y fácil de mantener: la aspiradora de mano se apaga automáticamente en caso de sobrecalentamiento o sobrecorriente para evitar daños. Incluye un filtro de repuesto y el depósito de polvo es lavable, no necesita bolsas de polvo. Las ruedas de suelo flexibles dejan el aspirador sin peso sobre colchones y sofás. ¡Incluso las personas mayores pueden usarlo sin esfuerzo! Calidad de precisión, duradera y con soporte sin preocupaciones.</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0GFCJ4JWY?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71AmFHqQF6L._AC_UL300_SR300,200_.jpg</t>
-  </si>
-  <si>
-    <t>B0HG11J16S</t>
-  </si>
-  <si>
-    <t>Beghdhu Aspiradora Antiacaros para Colchones sin Cable</t>
-  </si>
-  <si>
-    <t>https://www.amazon.es/dp/B0HG11J16S?psc=1</t>
-  </si>
-  <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/51KOcYPAxDL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0FHF6RYSW</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>2026-02-27</t>
+  </si>
+  <si>
+    <t>THOMASCLAKR STORE</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>BELFAST NORTHERN IRELAND BT5 5AD GB</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1FS4IJJC47VBD</t>
+  </si>
+  <si>
+    <t>2,32 kg</t>
+  </si>
+  <si>
+    <t>2.32 kg</t>
+  </si>
+  <si>
+    <t>30 x 24,7 x 18 cm</t>
+  </si>
+  <si>
+    <t>30.00 x 24.70 x 18.00 cm</t>
+  </si>
+  <si>
+    <t>32.7 x 29.6 x 20.6 cm</t>
+  </si>
+  <si>
+    <t>32.70 x 29.60 x 20.60 cm</t>
+  </si>
+  <si>
+    <t>B0CJFR8YZ1</t>
+  </si>
+  <si>
+    <t>Marca: JIGOO | Función especial: Sensor de ácaros con pantalla LED inteligente, luz UV para matar bacterias y ácaros | Tipo de filtro: Espuma o tela | Recomendación de superficie: Colchones Sofás | Fuente de alimentación: Adaptador de CA | Voltaje: 220 Voltios (CA) | Componentes incluidos: Aspiradora, Cepillos, Manual de usuario | ¿Es inalámbrico?: No | Peso del producto: 2,3 Kilogramos | Capacidad: 340 g</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/stores/JIGOO-ES/page/23E9C8F3-B11D-41BE-B25B-391D7999E178?lp_asin=B0CJFR8YZ1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>JIGOO S300 Pro Aspirador de Ácaros con Sensor de Ácaros y Pantalla Digital, 500W Aspiradora antiácaros con Luz UV, 13KPa de succión, para Alergias, Elimina alérgenos en colchones, Camas y sofás</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【Potente potencia de succión】: JIGOO S300 Pro aspirador antiácaros, potencia de 500 W y succión de 13 kPa, está especialmente diseñado para eliminar los ácaros, ofreciendo cuatro modos de funcionamiento diferentes para una limpieza efectiva y completa.
+【Tasa de eliminación de ácaros del 99,9% 】: Equipado con lámpara UV y ultrasónica, esta aspiradora de colchón libera una longitud de onda de 253,7 nanómetros en rayos ultravioleta, combinando esterilización a alta temperatura y una función de golpeo de cepillo para eliminar en profundidad el 99,99% de ácaros y bacterias, al tiempo que inhibe la multiplicación de forma duradera de ácaros y bacterias en el colchón, asegurando un ambiente de sueño higiénico, especialmente adecuado para personas alérgicas.
+【Sensor inteligente de ácaros】: La aspiradora de colchón JIGOO S300 Pro puede detectar con precisión los ácaros circundantes, mostrando el índice de ácaros y el estado de limpieza para una limpieza inteligente.
+【Pantalla LED inteligente】: esta aspiradora de cama está equipada con una pantalla LED clara para monitorear en tiempo real la actividad de los ácaros y el estado de limpieza del colchón, ofreciendo cuatro modos de funcionamiento diferentes para que puedas seguir fácilmente el progreso de la limpieza.
+【Rodillo de cepillo de metal innovador】: El rodillo de metal de esta aspiradora antiácaros es capaz de batir rápida y vigorosamente el colchón, eliminando fácilmente los ácaros mientras protege eficazmente la superficie del colchón.
+【Diseño original de doble corte】: este aspirador de colchón antiácaros separa eficazmente los ácaros y los alérgenos del aire para una filtración de aire más eficiente, evitando así el bloqueo del filtro.
+【Calefacción multidirección】: esta aspiradora antiácaros se puede calentar a 55 grados Celsius en 5 segundos para eliminar los ácaros y la humedad, desinfectando así el colchón para una limpieza eficaz y completa.</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/dp/B0CJFR8YZ1?psc=1</t>
+  </si>
+  <si>
+    <t>https://images-na.ssl-images-amazon.com/images/I/71wwrAJ4EpL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>2023-09-22</t>
+  </si>
+  <si>
+    <t>GOOD PRICE ONLY</t>
+  </si>
+  <si>
+    <t>RO</t>
+  </si>
+  <si>
+    <t>Jud. Neamt 617218 RO</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SBFZKR4LHBTM</t>
+  </si>
+  <si>
+    <t>2,3 Kilogramos</t>
+  </si>
+  <si>
+    <t>2.30 kg</t>
+  </si>
+  <si>
+    <t>32,5l. x 27,3an. x 19al. centímetros</t>
+  </si>
+  <si>
+    <t>2.76 kg</t>
+  </si>
+  <si>
+    <t>36.2 x 31.3 x 24.7 cm</t>
+  </si>
+  <si>
+    <t>36.20 x 31.30 x 24.70 cm</t>
   </si>
   <si>
     <t>B0GF7CNTYL</t>
   </si>
   <si>
-    <t>Aspirador de colchón UV-C y ultrasónico doble vaso para cama y sofásAspirador de ácaros inalámbrico para colchones, sofás d</t>
+    <t>Marca: Liwankaqi | Función especial: Luz UV | Recomendación de superficie: Tapicería | Fuente de alimentación: Batería | ¿Es inalámbrico?: Sí | Peso del producto: 1300 Gramos | Capacidad: 200 ml | Usos recomendados para el producto: Colchones, almohadas, sofás de tela, alfombras | Factor de forma: De mano | Color: Como En La Imagen</t>
+  </si>
+  <si>
+    <t>Liwankaqi</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
+  </si>
+  <si>
+    <t>Aspirador de colchón UV-C y ultrasónico doble vaso para cama y sofá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuerte succión gracias a la vibración y la tecnología de succión: nuestro aspirador antiácaros para colchones utiliza vibración y una fuerte succión. Este dispositivo limpiador de colchones con doble cojín plegable limpia a fondo, un verdadero ganador de la prueba.
+Funcionamiento inalámbrico con batería integrada: este limpiador de ácaros inalámbrico con batería ofrece una larga duración. El dispositivo limpiador de colchones permite el movimiento libre sin cables.
+Ultrasónico y luz UV para una limpieza profunda higiénica: el aspirador antiácaros inhibe los ácaros con ultrasonidos. Este aspirador de colchón con luz UV limpia más profundamente que un colchón limpiador a vapor.
+Sistema de filtrado eficiente contra el recirculación de polvo: el aspirador antiácaros tiene un sistema de filtro sellado. Este limpiador de vacío de cama evita la recirculación del polvo y la contaminación secundaria.
+Componentes extraíbles y lavables para la limpieza: la aspiradora ergonómica para ácaros tiene partes extraíbles. Este limpiador de vacío Mattress es fácil de limpiar para un rendimiento duradero.</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0GF7CNTYL?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_UL300_SR300,200_.jpg</t>
-  </si>
-  <si>
-    <t>B0GHQLQBYD</t>
-  </si>
-  <si>
-    <t>Aspiradora Antiacaros, Aspirador Acaros Sofa y Colchon con Una Gran Potencia de Aspiración, Aspirador Antiacaros para Colchon</t>
-  </si>
-  <si>
-    <t>https://www.amazon.es/dp/B0GHQLQBYD?psc=1</t>
-  </si>
-  <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/610gU-iwIJL._AC_UL300_SR300,200_.jpg</t>
-  </si>
-  <si>
-    <t>B0CJFR8YZ1</t>
-  </si>
-  <si>
-    <t>JIGOO S300 Pro Aspirador de Ácaros con Sensor de Ácaros y Pantalla Digital, 500W Aspiradora antiácaros con Luz UV, 13KPa de s</t>
-  </si>
-  <si>
-    <t>https://www.amazon.es/dp/B0CJFR8YZ1?psc=1</t>
-  </si>
-  <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71wwrAJ4EpL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41CQc-U9WtL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>liwantech</t>
+  </si>
+  <si>
+    <t>深圳市 南山区 广东 518000 CN</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y</t>
+  </si>
+  <si>
+    <t>1300 Gramos</t>
+  </si>
+  <si>
+    <t>1.30 kg</t>
+  </si>
+  <si>
+    <t>28l. x 27an. x 11al. centímetros</t>
+  </si>
+  <si>
+    <t>1.3 kg</t>
+  </si>
+  <si>
+    <t>28 x 27 x 17 cm</t>
+  </si>
+  <si>
+    <t>28.00 x 27.00 x 17.00 cm</t>
   </si>
   <si>
     <t>B0H8Z6R4ZK</t>
   </si>
   <si>
-    <t>Aspirador de colchón recargable inalámbrico portátil para camas sofássAspirador de mano silencioso, limpiador profundo inte</t>
+    <t>Marca: Bcuuozeeing | Función especial: Ahorro de energía, Compacto, Filtro lavable, Regulación de potencia de succión sin niveles, Sin bolsa | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Ropa de cama, sofá, manta, suelo duro, alfombra | Fuente de alimentación: Funciona con red | Componentes incluidos: Aspiradora | ¿Es inalámbrico?: Sí | Vataje: 60 vatios | Tiempo de carga: 1,5 Horas | Longitud de la manguera: 1 Metros</t>
+  </si>
+  <si>
+    <t>Bcuuozeeing</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Bcuuozeeing</t>
+  </si>
+  <si>
+    <t>Aspirador de colchón recargable inalámbrico portátil para camas sofás</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aspirador de ácaros de mano silencioso con control inteligente de funciones: portátil para todo el hogar. La aspiradora inalámbrica recargable es perfecta para colchones, ropa de cama y sofás de tela.
+Equipado con un rodillo de golpeo y una fuerte succión para una limpieza profunda e higiénica. Elimina eficazmente la suciedad profunda de los tejidos y la aspira inmediatamente.
+Eliminación fiable de ácaros, bacterias y polvo doméstico: ideal para personas alérgicas para crear un ambiente saludable y sin polvo.
+Diseño de carga inalámbrica sin molestos cables de alimentación, tamaño compacto y portátil para un fácil manejo. El funcionamiento silencioso no le molesta ni durante la limpieza ni en el hogar.
+Limpiador de colchones versátil para todas las superficies textiles: colchones, camas, cojines, sofás y cortinas. Un dispositivo práctico para la limpieza diaria del hogar.</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0H8Z6R4ZK?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61HKr6BnAHL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41ei98pWxqL._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>18l. x 10an. x 23al. centímetros</t>
   </si>
   <si>
     <t>B0D9BQHSWQ</t>
   </si>
   <si>
-    <t>Jimmy BX6 Lite Aspirador Antiácaros para Colchones, con Potencia de Succión de 600 W, 15 kpa, Aspiradora con Sensor de Polvo,</t>
+    <t>Marca: Jimmy | Función especial: Cepillo giratorio metálico con tira de goma, Ciclón doble, Luz UV-C, Pantalla LED, Sensor de polvo | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Tapicería | Fuente de alimentación: Eléctrico con cable | Voltaje: 230 Voltios | Componentes incluidos: Aspiradora, Cepillo de limpieza, Filtro, Filtros, Manual de usuario | ¿Es inalámbrico?: No | Peso del producto: 1,9 Kilogramos | Capacidad: 400 ml</t>
+  </si>
+  <si>
+    <t>Jimmy BX6 Lite Aspirador Antiácaros para Colchones, con Potencia de Succión de 600 W, 15 kpa, Aspiradora con Sensor de Polvo, Aire Caliente, Luz UV-C, Tecnología Ultrasónica, para Colchón Cama Sofá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15KPA Succión: alta velocidad de succión interna rotación de limpieza profunda, con tira de goma rodillo de cepillo de metal 15kpa, cepillo de alta frecuencia fuerte golpe, chocado del colchón, cojín del sofá y otros ácaros profundos, polvo, etc., el efecto de limpieza es más completo
+Detección inteligente LED de ácaros del polvo, evita la eliminación de ácaros ciegos: el sensor de ácaros del polvo con sensor de polvo puede calcular la cantidad de polvo/ácaros en el entorno con alta precisión, te ayuda a juzgar el grado de limpieza por el valor de los cambios
+Irradiación de aire caliente a gran escala: el calentador de la placa inferior viene con 55 ℃ imitar directamente el ambiente de sol, destruyendo el ambiente de crecimiento de ácaros, hacer que la ropa de cama esponjosa y caliente, días lluviosos también puede ser secado de la ropa de cama
+Función de Lámpara UV-C: la lámpara UV-C ayuda a eliminar bacterias y ácaros, 99% de eficiencia, muy útil para personas alérgicas con mascotas, y también se puede utilizar en la familia
+Cepillo de rodillo de metal de tira de goma: cuerpo de metal con 600 W de potencia y cepillo de rodillo de tira de goma de metal, golpear profundamente, golpear fuera del colchón los ácaros del polvo no se pueden ver</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0D9BQHSWQ?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/619CHOWba4L._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/619CHOWba4L._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>NEXO HOME</t>
+  </si>
+  <si>
+    <t>Barcelona Barcelona 08013 ES</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UUYGTGLOQBB0</t>
+  </si>
+  <si>
+    <t>1,9 Kilogramos</t>
+  </si>
+  <si>
+    <t>1.90 kg</t>
+  </si>
+  <si>
+    <t>30,5l. x 20an. x 38,5al. centímetros</t>
+  </si>
+  <si>
+    <t>2.89 kg</t>
+  </si>
+  <si>
+    <t>38.7 x 31.5 x 20.2 cm</t>
+  </si>
+  <si>
+    <t>38.70 x 31.50 x 20.20 cm</t>
   </si>
   <si>
     <t>B0F6XNKG8M</t>
   </si>
   <si>
-    <t>Aspiradora Antiacaros, Luz UV-C y 400WsElimina el 99,9%| Aire Caliente a 60 Grados Centígrados, Alergenos y Pelos de Mascota</t>
+    <t>Marca: Tiazhan | Función especial: Alta potencia, Alto rendimiento, Eliminación de ácaros, HEPA, Ligero, Luz ultravioleta | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Alfombra, Tapicería | Fuente de alimentación: Eléctrico con cable | Componentes incluidos: Filtro HEPA, 2 depósitos de polvo de 500 ml | ¿Es inalámbrico?: No | Capacidad: 500 ml | Usos recomendados para el producto: Pisos con alfombra, tapicería, colchones y ambientes con ácaros | Factor de forma: De mano</t>
+  </si>
+  <si>
+    <t>Tiazhan</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/stores/Tiazhan/page/B4946EA8-16BD-438A-89E6-C36320E22788?lp_asin=B0F6XNKG8M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
+    <t>Aspiradora Antiacaros, Luz UV-C y 400W| Elimina el 99,9%| Aire Caliente a 60 Grados Centígrados, Alergenos y Pelos de Mascotas, Filtro HEPA y Cajas de Polvo Dobles 0.5L para Camas, para Camas y Sofás</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【Limpieza Profunda 】Esta aspiradora antiacaros ofrece un rendimiento excepcional con su motor de 400 W y potencia de succión. El cepillo giratorio de 40,000 rpm desprende eficazmente ácaros, pelo de mascotas, caspa y alérgenos profundamente incrustados. diseñada para limpiar thoroughly colchones, sofás, almohadas, alfombras y tapicerías, esta aspirador antiacaros garantiza un ambiente saludable en toda la casa.
+【Tecnología de Esterilización UV-C】Esta aspiradora antiacaros equipada con lámpara UV-C de 253.7 nm, este aspirador antiacaros elimina el 99.9% de bacterias, virus y microorganismos. La luz ultravioleta penetra en las fibras textiles realizando una desinfección profunda, complementando perfectamente la acción de succión para una protección anti acaros completa y eficaz.
+【Sistema de Filtración Avanzado】Este aspirador de mano incorpora un sistema de filtrado multietapa con filtro HEPA que retiene el 99.97% de partículas hasta 0.3 micras. Gracias a su diseño extraíble con un solo clic, el mantenimiento de esta aspirador antiacaros es remarkably sencillo, asegurando un rendimiento óptimo en cada uso.
+【Doble Depósito de Gran Capacidad】Con dos depósitos independientes de 500 ml, esta aspiradora antiacaros separa eficientemente diferentes tipos de residuos.Nuestro aspirador antiacaros ell innovador sistema de separación evita la contaminación cruzada y facilita el vaciado, haciendo el proceso de limpieza más higiénico y eficiente.
+【Seguridad y Operación Intuitiva】Diseñado con botón de seguridad (presionar 2 segundos) y dos modos de limpieza, este aspiradora antiacaros previene accidentes y se adapta a diferentes superficies. Nuestro aspirador antiacaros los materiales de primera calidad garantizan durabilidad y estabilidad, siendo ideal para hogares con niños, mascotas o personas alérgicas.
+【Función Integral de Aire Caliente】Generando aire caliente a 60°C, esta aspiradora antiacaros elimina los ácaros por deshidratación térmica mientras seca la humedad ambiental. La combinación de calor, succión potente y luz UV-C crea un sistema triple de limpieza especialmente efectivo en climas húmedos o para personas con problemas respiratorios.</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0F6XNKG8M?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41BYSfgxHfL._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>28l. x 15an. x 68al. centímetros</t>
   </si>
   <si>
     <t>B0FVS559GZ</t>
   </si>
   <si>
-    <t>Yaasier Aspirador de ácaros con luz UV, Mini aspiradora con Filtro HEPA, Aspirador antiacaros con depósito de Polvo Permanent</t>
+    <t>Marca: Yaasier | Función especial: Portátil | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Colchones, ropa de cama, almohada, alfombras, sofás de tela | Fuente de alimentación: Batería | Componentes incluidos: Aspirador de Ácaros | ¿Es inalámbrico?: Sí | Peso del producto: 250 Gramos | Usos recomendados para el producto: Colchones, sábanas, almohadas, alfombras, sofás de tela, pelo de mascotas | Factor de forma: De mano</t>
+  </si>
+  <si>
+    <t>Yaasier</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
+  </si>
+  <si>
+    <t>Yaasier Aspirador de ácaros con luz UV, Mini aspiradora con Filtro HEPA, Aspirador antiacaros con depósito de Polvo Permanente para colchones, sofás, Almohadas, alfombras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Tecnología avanzada tres en uno] Equipado con una almohadilla de pulso de doble ritmo y una luz UV de 253,7 nm, esta aspiradora ofrece una gran área de limpieza y una mayor eficiencia, ideal para eliminar los ácaros del polvo y otros alérgenos de sus colchones y textiles.
+[Diseño inalámbrico ligero] Maximice su comodidad con esta aspiradora inalámbrica ligera que tiene una batería recargable que ofrece hasta 30 minutos de tiempo de funcionamiento. Su diseño moderno y elegante se adapta perfectamente a cualquier decoración de interiores y hace que la limpieza sea fácil.
+[Sistema de filtración de alta eficiencia] Limpiador de colchones con un filtro HEPA lavable y un filtro de algodón en la salida, esta aspiradora atrapa el 99,97 % de las partículas de polvo fino, proporciona un aire más saludable y reduce la contaminación secundaria, ideal para personas sensibles y familias con niños.
+[Fácil de limpiar y lavable] Aspirador de ácaros con el depósito de polvo lavable con agua corriente hace que su aspiradora sea más fácil de limpiar. Seque el filtro antes de reutilizarlo para garantizar una succión óptima y un rendimiento de limpieza constante
+[Versatilidad y comodidad de uso] Aspirador de ácaros con luz UV Ideal para aspirar el pelo de animales y la caspa en diferentes superficies de tela como colchones, cojines, sofás y alfombras. Disfruta de una limpieza silenciosa que no molesta a bebés o mascotas dormidos</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0FVS559GZ?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/31eLjeocEiL._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>B0GHDFVK7R</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>250 Gramos</t>
+  </si>
+  <si>
+    <t>250.00 g</t>
+  </si>
+  <si>
+    <t>6l. x 4an. x 8al. centímetros</t>
   </si>
   <si>
     <t>B0DT1D15C6</t>
   </si>
   <si>
-    <t>CREATULIZE Robot X1, Aspirador de Acaros, Navegación Inteligente, Limpieza Automática de Cama, Manos Libres, Detección de Bor</t>
+    <t>Marca: CREATULIZE | Nombre del modelo: X1 | Recomendación de superficie: Alfombra, Tapicería | Función especial: Anticaídas | Color: Plateado | Dimensiones del producto: 25,8l. x 28,5an. x 15,8al. centímetros | Tipo de controlador: Control de botones | Componentes incluidos: Estación de acoplamiento, Posiblemente cepillo | Tipo de filtro: Tela | Peso del producto: 2,1 Kilogramos</t>
+  </si>
+  <si>
+    <t>CREATULIZE</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=CREATULIZE</t>
+  </si>
+  <si>
+    <t>CREATULIZE Robot X1, Aspirador de Acaros, Navegación Inteligente, Limpieza Automática de Cama, Manos Libres, Detección de Bordes, Cuatro Modos de Limpieza, 55dB Silencioso, Succión de 14AW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limpieza profunda inteligente totalmente automática: Equipado con tecnología de planificación de ruta curva y 9 sensores de alta precisión, identifica con precisión el borde de la cama/sofá y gira inteligentemente para evitar caídas. Puede disfrutar de una experiencia de limpieza profunda desatendida cuando encienda la máquina, liberando completamente sus manos
+14AW succión de huracán y operación ultra silenciosa: 14AW potente succión elimina fácilmente el polvo profundo/alérgenos mientras mantiene 55 dB operación bajo ruido, limpias, eficientes y sin molestias, adecuado para familias madres, bebés/mascotas
+Una máquina para múltiples propósitos, cubriendo todas las escenas: está especialmente optimizada para tres escenas principales de colchones, sofás y alfombras de pelo corto. Está equipada con un modo manual conmutable para limpiar fácilmente almohadas, cojines y otros artículos pequeños para satisfacer las necesidades de limpieza fina de toda la casa
+Diseño portátil para llevarlo a todas partes: el cuerpo ligero se puede plegar y almacenar, y se puede colocar directamente en la maleta cuando viaje de negocios. Puede mantener la higiene de la cama y el sofá del hotel en cualquier momento y en cualquier lugar. Es una opción segura para los viajeros de negocios
+Sistema antibloqueo innovador, limpio sin callejones muertos: el algoritmo de navegación inteligente cubre completamente el camino del arco, rechaza la repetición/omisión, limpia profundamente los rincones complejos y diga adiós a los problemas de desalineación y enredo de las máquinas tradicionales</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0DT1D15C6?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/81vdWh-NSLL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/51ZP52evVDL._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>25,8l. x 28,5an. x 15,8al. centímetros</t>
   </si>
   <si>
     <t>B0FKRC3KQY</t>
   </si>
   <si>
-    <t>Yaasier Aspirador de Ácaros, Mini Aspirador Antiácaros para Colchones con Luz UV, Aspiradora de Mano con Filtro HEPA para Col</t>
+    <t>Marca: Yaasier | Función especial: Portátil | Tipo de filtro: Filtro HEPA | Recomendación de superficie: nan | Fuente de alimentación: Batería | ¿Es inalámbrico?: Sí | Usos recomendados para el producto: Superficies de tela, eliminación de pelo de animales, entornos silenciosos | Factor de forma: De mano | Color: Blanco | Dimensiones del producto: 40l. x 40an. x 80al. milímetros</t>
+  </si>
+  <si>
+    <t>Yaasier Aspirador de Ácaros, Mini Aspirador Antiácaros para Colchones con Luz UV, Aspiradora de Mano con Filtro HEPA para Colchones, Camas, Sofás de Tela, Almohadas, Alfombras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ligero y compacto: el aspirador de cama toma tres en una sola función de flotación de alta frecuencia, fuerte succión y luz violeta penetrante. Almohadilla de pulsación doble Beat, luz púrpura de 253,7 nm, área de limpieza más grande, mayor eficiencia de limpieza.
+Diseño ligero e inalámbrico: disfruta de la libertad de limpieza inalámbrica. La batería recargable ofrece una larga duración de 30 minutos. Nuestra aspiradora es una de las más ligeras del mercado, lo que hace que sea más fácil de usar y menos exigido sus músculos y articulaciones. Nuestro diseño elegante y moderno se adapta a tu estética y a tu hogar.
+Sistema de filtración muy eficiente: la aspiradora de colchón utiliza un filtro HEPA reutilizable y lavable en profundidad en combinación con un tejido filtrante de acero inoxidable que podría recoger aproximadamente el 99,97% de partículas tan pequeñas como 0,3 micras, y aislar las partículas grandes de los residuos, bloqueando firmemente el polvo y la suciedad, y no goteará.
+【Caja de polvo lavable】 Máquina de limpieza de colchones Snap-on, fácil de limpiar, se puede limpiar directamente debajo del grifo, limpieza regular sin la molestia de succión debilitada o polvo obstruido. Nota: el filtro debe usarse después del secado.
+【Ámbito de aplicación】El aspirador de cama puede aspirar fácilmente el pelo de animales y la caspa, etc. Adecuado para superficies de tela: colchones, sábanas, almohadas, alfombras, sofás de tela, etc. El diseño de cancelación de ruido no molestará a los bebés o mascotas dormidos.</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0FKRC3KQY?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/31SPlR-BXSL._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>40l. x 40an. x 80al. milímetros</t>
   </si>
   <si>
     <t>B0FDWVV95V</t>
   </si>
   <si>
+    <t>Marca: JIGOO | Función especial: Hipoalergénica | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Tapicería, Alfombra | Fuente de alimentación: Batería | Componentes incluidos: Cepillo para limpiar el polvo, Herramienta para hendiduras | ¿Es inalámbrico?: Sí | Usos recomendados para el producto: colchones y tapicería | Factor de forma: De mano | Color: Verde</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/stores/JIGOO-ES/page/23E9C8F3-B11D-41BE-B25B-391D7999E178?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
     <t>JIGOO T600 T600 - Tetina antiácaros/Floral Delight (aceite esencial de plantas)</t>
   </si>
   <si>
+    <t>JIGOO T600 - Aspirador antiácaros para colchones: Floral Delight (aceite esencial de plantas)</t>
+  </si>
+  <si>
     <t>https://www.amazon.es/dp/B0FDWVV95V?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/31va0mFb48L._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>6l. x 1,3an. x 8al. centímetros</t>
   </si>
   <si>
     <t>B0GYS43G8G</t>
   </si>
   <si>
-    <t>Aspiradora De Acaros, Aspiradora Antiacaros con Triple Filtración Y Filtro Lavable, Vibración De Alta Frecuencia, Maquina Ant</t>
+    <t>Marca: ALLILUYAA | Función especial: Triple filtración | Recomendación de superficie: Colchón | Componentes incluidos: Filtro lavable | ¿Es inalámbrico?: Sí | Succión máxima: 10000 Milímetros | Usos recomendados para el producto: colchones, sofás, mantas, ropa, peluches y camas para mascotas | Factor de forma: De mano | Color: Blanco | Dimensiones del producto: 10l. x 10an. x 10al. milímetros</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/stores/ALILILUYAA/page/6F2D9C3F-3247-41D0-93BE-BD3270082609?lp_asin=B0GYS43G8G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
+    <t>Aspiradora De Acaros, Aspiradora Antiacaros con Triple Filtración Y Filtro Lavable, Vibración De Alta Frecuencia, Maquina Antiacaros para Artículos Textiles como Sofás, Colchones Y Peluches</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0GYS43G8G?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/31Nn49TeoxL._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
   <si>
     <t>B0D83SRY9V</t>
   </si>
   <si>
-    <t>Aspiradora Antiacaros, 16Kpa Aspiradora Antiácaros con Luz UV, Elimina el 99,9% de los Alérgenos, para Colchones, Camas, Sofá</t>
+    <t>Marca: Redcoutt | Función especial: Luz UV | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Tapicería | Fuente de alimentación: Eléctrico con cable | Componentes incluidos: Filtro HEPA | ¿Es inalámbrico?: No | Vataje: 500 vatios | Succión máxima: 15 Kilómetros | Usos recomendados para el producto: colchones, sofás</t>
+  </si>
+  <si>
+    <t>Redcoutt</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Redcoutt</t>
+  </si>
+  <si>
+    <t>Aspiradora Antiacaros, 16Kpa Aspiradora Antiácaros con Luz UV, Elimina el 99,9% de los Alérgenos, para Colchones, Camas, Sofás y Muebles Tapizados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【Succión potente de 16Kpa】Nuestro colchón aspirador ofrece una potente succión de 16Kpa, asegurando una limpieza profunda de la cama y eliminando eficazmente el polvo, la suciedad y los pelos molestos de animales. Di adiós a un entorno de sueño más limpio y saludable
+Innovadora tecnología UV y ultrasónica: equipada con tecnología UV y ultrasónica avanzada, esta aspiradora para colchones va más allá de la limpieza de la superficie. Penetra profundamente en el colchón, eliminando hasta el 99,9% de los alérgenos, favoreciendo un mejor sueño y un bienestar general.
+Diseño de doble contenedor: una cámara de filtración y otra para la recogida de polvo. Este innovador diseño de doble corte elimina eficazmente los ácaros del polvo y los alérgenos del aire, asegurando una filtración superior, evitando la obstrucción del filtro y manteniendo una potencia de succión fuerte y duradera.
+【Función de calentamiento elevado】 Nuestra aspiradora para colchones tiene una alta función de calentamiento, alcanzando una temperatura de 140 ℉ (60 ℃), eliminando aún más los alérgenos del colchón. Garantiza un entorno de sueño higiénico para ti y tu familia.
+Amplio rango de trabajo: el cable de 3 metros de largo es suficiente para limpiar toda la superficie de un sofá o colchón king size.
+Versátil y fácil de usar: ya sea para limpiar el colchón, el sofá o la tapicería, nuestra aspiradora es la solución ideal. Su diseño ligero y ergonómico hace que sea fácil de manejar, mientras que el recipiente antipolvo extraíble garantiza un vaciado sin esfuerzo.</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0D83SRY9V?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/51LjSaAmb9L._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/51LjSaAmb9L._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>23l. x 28an. x 35al. centímetros</t>
   </si>
   <si>
     <t>B0FN3GPQZM</t>
   </si>
   <si>
+    <t>Marca: Teant | Voltaje: 230 Voltios | Componentes incluidos: Cepillo giratorio con parada automática, Cepillo antienredos | ¿Es inalámbrico?: No | Peso del producto: 1,9 Kilogramos | Factor de forma: De mano | Color: Blanco | Nombre del modelo: MV-GREY</t>
+  </si>
+  <si>
+    <t>Teant</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Teant</t>
+  </si>
+  <si>
     <t>Mayking Teant Aspiradora para Colchones 2 Velocidades (14 kPa/18 kPa)</t>
   </si>
   <si>
+    <t xml:space="preserve">[Limpieza profunda y potente con 2 Velocidades] El Aspiradora para Colchones antiacaros Teant ofrece 2 niveles de succión ajustables hasta 18 kPa, mientras que el motor Hyper Helix proporciona 33 000 rpm de potentes golpes para penetrar en colchones, sofás y tejidos, levantando el polvo, la caspa y los alérgenos. Los contenedores dobles para el polvo y el filtro HEPA capturan el 99,97 % de las micropartículas (de hasta 0,3 µm) y separan los pelos para evitar obstrucciones, manteniendo una potente succión para una limpieza más profunda y uniforme y un espacio de descanso más fresco
+[Detección con luz verde, no se Esconde el Polvo] El aspirador portátil inteligente para colchones utiliza luz verde de 555 nm y tecnología de lente para detectar el polvo oculto, los pelos de animales y las micropartículas en colchones oscuros, sofás y hendiduras profundas de los tejidos, sin dejar ningún punto sin limpiar. El cable extralargo de 5 metros llega a todos los rincones de una cama king size sin tener que desconectarlo, para una limpieza más fácil, inteligente y profunda
+[Pantalla LED Multifunción para una Limpieza Visible] Los LED inteligentes con indicadores dinámicos rojos y azules muestran el progreso de la limpieza en tiempo real. La amplia y clara pantalla LED del aspirador Antiacaro de cama permite supervisar al instante las funciones: Golpes, Calor, UV-C, Ultrasonidos y Aniones. (Consejo: un color rojo prolongado puede indicar que el sensor de polvo está cubierto; límpielo con un paño limpio y húmedo)
+[Apunta a las Micropartículas Ocultas, protege a tu Familia] La luz UV-C de 253,7 nm, combinada con tecnología ultrasónica de 40 000 Hz, permite que el Aspirador de Mano Teant penetre profundamente en las fibras del colchón para detectar y eliminar el 99,9 % de las partículas invisibles. Los rodillos dobles con sensor de gravedad activan los rayos UV solo después de que ambas ruedas hayan estado en contacto con la superficie durante 2 segundos y se apagan si se levantan, lo que evita pérdidas de luz y mantiene a tu familia segura
+[Aire Caliente, Aroma y Iones negativos para un hogar Fresco] Despídase de las camas húmedas y los malos olores. El aspirador para colchones Teant proporciona un flujo de aire calentado a 65 °C para secar eficazmente los tejidos: disfrute de un colchón limpio y seco. La tecnología de iones negativos ayuda a neutralizar las partículas en suspensión en el aire y a refrescarlo, mientras que la pastilla aromática elimina los olores y añade una delicada fragancia natural, perfecta para una noche de sueño limpia y acogedora
+[Doble Protección: Cepillo Antienredos y Protección Contra Sobrecalentamiento] El aspirador de colchones Teant cuenta con un cepillo giratorio con parada automática que se detiene al instante en caso de enredos, protegiendo el motor y prolongando su vida útil. La protección contra sobrecalentamiento incorporada interrumpe automáticamente el funcionamiento tras un uso prolongado. Basta con apagarlo, dejarlo enfriar durante 2 horas y luego reanudar la limpieza con seguridad</t>
+  </si>
+  <si>
     <t>https://www.amazon.es/dp/B0FN3GPQZM?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41B+I610d+L._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>22</t>
   </si>
   <si>
     <t>B0F8HD3649</t>
   </si>
   <si>
+    <t>Marca: Mayking | Función especial: HEPA, Luz UV | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Colchones, camas, sofá, alfombras | Fuente de alimentación: Eléctrico con cable | Voltaje: 230 Voltios | ¿Es inalámbrico?: No | Peso del producto: 1,9 Kilogramos | Succión máxima: 16 Kilómetros | Usos recomendados para el producto: Cama, Muebles tapizados, Pelo de animal, Pelo de mascota, cama</t>
+  </si>
+  <si>
+    <t>Mayking</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Mayking</t>
+  </si>
+  <si>
     <t>Aspiradora Antiacaros con Luz UV, 16 Kpa</t>
   </si>
   <si>
+    <t xml:space="preserve">Limpieza profunda y potente rendimiento de limpieza: el motor Hyper-Helix ofrece 16 kPa de presión de aspiración de vacío en espiral y 33.000 rpm de fuerte golpe para eliminar el polvo en profundidad. El fuerte rendimiento de limpieza del aspirador de ácaros hace que los alérgenos y el pelo de las mascotas en la profundidad de colchones y sofás ya no sean un problema. La pantalla LED le permite reconocer fácilmente el rendimiento de limpieza en tiempo real, garantiza una limpieza profunda y profunda y protege la seguridad de su familia. ¡Este es un gran regalo para familias con mascotas!
+【Tecnología dual: aniones y luz UV-C】Los aniones se unen a las moléculas de olor y las micropartículas en el aire y purifican eficazmente el aire para evitar olores en la salida. La luz ultravioleta UV-C esteriliza y elimina eficazmente los ácaros y limpia colchones, sofás, alfombras y otros textiles en su hogar. La tecnología dual proporciona una limpieza profunda y evita la contaminación secundaria. Para mayor seguridad, el aspirador de colchón está equipado con un bloqueo de luz UV-C: solo cuando ambos sensores de gravedad están completamente presionados en el suelo, la luz UV-C funciona.
+Aire caliente de 149 ℉: la aspiradora antiácaros para colchones dispone de aire caliente de 149 ℉ (65 °C). El aire caliente afloja el polvo, y la combinación de aire caliente, la función de golpeo y la succión elimina eficazmente el polvo y los alérgenos en las profundidades del colchón mientras mantiene la tela seca. Además, la piedra de aromaterapia integrada proporciona una experiencia sensorial fresca y agradable para un ambiente saludable y cómodo.
+Sistema de filtración de polvo HEPA doble: el aspirador antiácaros filtra el 99,97 % de las partículas (0,3 micrones) con el sistema de doble vaso HEPA. El sistema separa eficientemente el pelo y el polvo, evita atascos y fugas de polvo y garantiza una succión estable. Además, la limpieza del recipiente es particularmente fácil.
+Fácil de usar y duradera: la aspiradora antiácaros para colchones tiene un cable de 5 metros y es ligera, por lo que las camas, sofás y alfombras se pueden limpiar sin esfuerzo. La carcasa está hecha de material ABS respetuoso con el medio ambiente, y los componentes interiores de alta calidad proporcionan hasta 10 años de protección de la salud del hogar. Ofrecemos un servicio al cliente integral – contáctenos si tiene alguna pregunta!
+Nota: el cepillo de rodillos tiene una protección de bloqueo del rotor. En caso de enredos de textiles o cabello, el rotor se detiene automáticamente. El funcionamiento continuo puede desencadenar la protección contra sobrecalentamiento. En ambos casos, apague el dispositivo, deje que se enfríe y luego continúe utilizando.</t>
+  </si>
+  <si>
     <t>https://www.amazon.es/dp/B0F8HD3649?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71CtAiuTm1L._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41548PPAf0L._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>36l. x 29an. x 25,4al. centímetros</t>
   </si>
   <si>
     <t>B0DNZ5LDQX</t>
   </si>
   <si>
-    <t>Liwankaqi Aspirador de ácaros 14 kPa, velocidad de esterilización con lámparas UV LED, aspirador de colchón con detergente y</t>
+    <t>Marca: Liwankaqi | Función especial: Sin tallo | Tipo de filtro: Cartucho | Recomendación de superficie: Tapicería, colchones, telas, alfombras | Fuente de alimentación: Batería | Voltaje: 762 Voltios | Componentes incluidos: Mite Remover | ¿Es inalámbrico?: Sí | Peso del producto: 955 Gramos | Usos recomendados para el producto: Limpieza de muebles tapizados, ropa de cama, colchones, textiles y alfombras</t>
+  </si>
+  <si>
+    <t>Aspirador de ácaros 14 kPa, velocidad de esterilización con lámparas UV LED, aspirador de colchón con detergente y vibración de alta frecuencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limpieza profunda: gracias a la vibración de alta frecuencia de al menos 8000 veces por minuto, esta aspiradora Hoover absorbe eficazmente el polvo y la suciedad de las superficies de la tela.
+Niveles de succión ajustables: este aspirador antiácaros para colchones ofrece dos niveles de succión ajustables y una fuerte potencia de succión de 14 kpa para eliminar eficazmente los ácaros del polvo.
+Advanced Purple Light: con luz ultravioleta LED, este limpiador de colchones alcanza una alta tasa de desinfección de hasta el 99,99%.
+Portátil y fácil de usar: nuestro dispositivo de limpieza de sofá inalámbrico y ligero es fácil de usar y perfecto para limpiar cada rincón de tu casa para combatir eficazmente los ácaros del polvo.
+Amplia aplicación: desde sofás y almohadas hasta sábanas, colchones, telas y alfombras, esta aspiradora con batería es adecuada para limpiar una variedad de superficies de tela y es ideal como dispositivo de limpieza de alfombras.</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0DNZ5LDQX?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61YjHSHoT6L._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41VwiuPGuQL._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>955 Gramos</t>
+  </si>
+  <si>
+    <t>955.00 g</t>
+  </si>
+  <si>
+    <t>26l. x 25an. x 20al. centímetros</t>
   </si>
   <si>
     <t>B0FBGQY9YP</t>
   </si>
   <si>
-    <t>Fey Aspirador antiácaros para colchones de 16 KPA, potente limpiador de colchones con luz UV-C, sensor de ácaros del polvo, f</t>
+    <t>Marca: Fey | Función especial: Aspirador de ácaros para colchones, cepillo de doble rodillo con fuerte fuerza de impacto, doble absorción, elimina los ácaros a fondo, Diseño de taza doble integrada grande de 450 ml, contenedor de polvo y vaso doble de filtro que funcionan por separado, no se acumulan ni se obstruyen fácilmente, funcionan de manera eficiente, El aspirador de ácaros con luz UV puede eliminar el 99,9% de los ácaros y bacterias ocultos en el colchón, también tiene luz ultravioleta UV, elimina los ácaros a fondo, Potente succión para una limpieza profunda: la aspiradora antiácaros tiene un motor de 500 W y ofrece una impresionante potencia de succión de 16 KPA para una excelente limpieza profunda. | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Alfombra, tapicería, piso duro | Fuente de alimentación: Eléctrico con cable | Componentes incluidos: Diseño de doble taza | ¿Es inalámbrico?: No | Usos recomendados para el producto: Tapicería, alfombras, superficies blandas | Factor de forma: De mano | Color: Gris</t>
+  </si>
+  <si>
+    <t>Fey</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/stores/Fey/page/43F7FFA5-3E54-4A0B-BF57-3795C4422856?lp_asin=B0FBGQY9YP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
+    <t>Fey Aspirador antiácaros para colchones de 16 KPA, potente limpiador de colchones con luz UV-C, sensor de ácaros del polvo, función ultrasónica para alérgicos, elimina el 99,9% de alérgenos de camas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【Función 5 en 1】 Aspirador de ácaros con fuerte potencia de succión de 16 kpa, 500 W de alto rendimiento, calefacción de aire caliente a 60 °C, interferencia ultrasónica y rodillo doble mejorado con 60.000 rpm. Esta succión de ácaros con luz UV elimina eficazmente hasta un 99,9% de partículas invisibles y garantiza una limpieza profunda gracias a la tecnología de cinco veces.
+【Ventaja única de la protección UV】 Nuestro aspirador antiácaros para colchones está diseñado para la seguridad y garantiza la seguridad al evitar fugas UV-C. Cuenta con tecnología UV-C de 273 nm que utiliza interruptores de gravedad en las dos ruedas de la parte inferior: la luz UV-C se activa cuando se presionan las ruedas del dispositivo y la luz UV-C se apaga cuando las ruedas del dispositivo se levantan o no están en una posición plana.
+【Depósito de polvo doble y cepillo de doble rodillo】 Este aspirador de ácaros cuenta con un diseño único con doble depósito de polvo y cepillo de doble rodillo y ofrece el doble de potencia de limpieza para una limpieza efectiva de la suciedad de diferentes superficies. El diseño de doble depósito de polvo separa el polvo y el pelo para evitar la obstrucción del filtro y mantener una fuerte succión.
+Sistema de filtrado múltiple: la aspiradora antiácaros se combina con HEPA de alta calidad para limpiar a fondo el aire y liberar aire fresco, capturando partículas de hasta 0,3 micras. El filtrado múltiple permite separar eficazmente el polvo y las partículas del aire, lo que garantiza una alta potencia de succión constante.
+【Escenarios de aplicación】 Nuestro aspirador antiácaros para colchones es ligero y viene con un cable de alimentación de 5 m para una limpieza cómoda. La aspiradora de cama puede aspirar fácilmente el polvo, la caspa de la piel y el pelo de mascotas, etc. Adecuado para superficies de tela: ropa de cama, alfombras, sofás, juguetes, ropa y otros tejidos, para proporcionarle un limpio y</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0FBGQY9YP?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71OWNtREIXL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/71OWNtREIXL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0FCCCLS1X</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>2026-02-12</t>
+  </si>
+  <si>
+    <t>Jierun-EU</t>
+  </si>
+  <si>
+    <t>扬州市 江苏 225002 CN</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3MSJ66TMU8M67</t>
+  </si>
+  <si>
+    <t>29l. x 24an. x 23,5al. centímetros</t>
   </si>
   <si>
     <t>B0G4RSJQVT</t>
   </si>
   <si>
-    <t>Lubluelu Aspirador de ácaros 3 en 1 para colchones, 18 KPa fuerte potencia de succión, limpiador de colchones contra ácaros,</t>
+    <t>Color: Gris Oscuro | Tamaño: 500W</t>
+  </si>
+  <si>
+    <t>Marca: Lubluelu | Función especial: Luz UV | Tipo de filtro: Cartucho | Recomendación de superficie: Alfombra | Fuente de alimentación: Eléctrico con cable | Componentes incluidos: Rodillo de cepillo | ¿Es inalámbrico?: No | Succión máxima: 18000 Milímetros | Usos recomendados para el producto: Colchones, sofás, alfombras, ropa de cama, juguetes de peluche, pelo de mascota | Factor de forma: De mano</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/stores/Lubluelu/page/6949B717-1950-436B-B468-8BFB57AEF209?lp_asin=B0G4RSJQVT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>Lubluelu Aspirador de ácaros 3 en 1 para colchones, 18 KPa fuerte potencia de succión, limpiador de colchones contra ácaros, polvo y alérgenos, aspiradora de mano para cama, sofá, tapicería y textiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuerte succión de 18 KPa para una limpieza profunda: potente aspiradora elimina instantáneamente el polvo, la suciedad y los ácaros del polvo de los colchones, sofás, alfombras, ropa de cama y peluches. Proporciona una limpieza profunda en cada esquina.
+Limpieza profunda multietapa de ácaros y alérgenos: combinación de rodillo de cepillo, vibración ultrasónica y calentamiento a alta temperatura, elimina eficazmente los ácaros y alérgenos profundamente en los tejidos, dejando un hogar fresco e higiénico.
+Limpieza hipoalergénica y suave: diseñada para hogares sensibles, la limpieza profunda se basa en tecnología mecánica de golpes y calor en lugar de aditivos químicos. Ideal para personas alérgicas, habitaciones infantiles y familias con mascotas, mientras que los textiles y las superficies se cuidan de manera cuidadosa con el material.
+Versátil para diferentes superficies y usos: adecuado para colchones, sofás, alfombras, ropa de cama y juguetes de peluche. Disuelve el polvo y las partículas de tejidos profundos y ayuda a mantener las zonas de vida muy utilizadas. Ideal para dormitorios, salas de estar y hogares con mascotas, para un hogar higiénico.
+Práctico y fácil de usar en el día a día: cable extralargo de 4 m para un mayor alcance, diseño compacto y ligero para un manejo flexible para la limpieza de colchones y muebles tapizados, así como un mantenimiento sencillo. El depósito de polvo se puede vaciar rápidamente y dejar que el filtro se seque al aire después de la limpieza.</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0G4RSJQVT?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41T59G+lWKL._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>B0HJRMXSZC</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>26,5l. x 25,5an. x 33,5al. centímetros</t>
   </si>
   <si>
     <t>B0F9NJM4V9</t>
   </si>
   <si>
-    <t>Liwankaqi Aspiradora antiácaros UV-C y ultrasonidos, 8 KPa, antialérgenos para cama, sofás, alfombras</t>
+    <t>Marca: Liwankaqi | Función especial: Sin tallo | Tipo de filtro: Tela | Recomendación de superficie: Todos los suelos | Fuente de alimentación: Batería | Voltaje: 523 Voltios | Componentes incluidos: Mite Remover | ¿Es inalámbrico?: Sí | Peso del producto: 2235 Gramos | Capacidad: 520 ml</t>
+  </si>
+  <si>
+    <t>Aspiradora antiácaros UV-C y ultrasonidos, 8 KPa, antialérgenos para cama, sofás, alfombras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Dos potentes modos de succión para una higiene perfecta]: nuestro aspirador antiácaros para colchones ofrece dos niveles de potencia, ¡ideal para alérgicos! La fuerte succión elimina los ácaros, el polvo y la caspa de forma fiable. Perfecto como limpiador de colchones para un ambiente de sueño higiénico y limpio
+Tecnología UV y de alta frecuencia contra ácaros: el aspirador de ácaros con UV combina 4 principios de acción: desinfección UV-C, ultrasonido, rotación del cepillo y 8000Pa fuerza de succión. Así se elimina el 99, 9% de los ácaros y bacterias. Científicamente probado
+[Innovador sistema de 2 cámaras con capacidad de 520 ml]: la aspiradora antiácaros para colchones separa eficazmente los alérgenos y el polvo a través del filtro HEPA y el recipiente transparente. Gran volumen para menos vaciado - conveniente para las familias
+[Ligero e intuitivo de usar]: fácil de usar gracias al diseño ergonómico de la aspiradora de mano. Los componentes se pueden desmontar y limpiar rápidamente. Especialmente adecuado para personas mayores y hogares alérgicos
+[Uso universal en todo el hogar]: ¡no solo para colchones! Ideal para sofás, alfombras, asientos de coche y cestas de mascotas. El potente todoterreno sustituye a los costosos equipos especiales, tu práctico compañero de higiene para cualquier habitación</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0F9NJM4V9?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41skTyVFYpL._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>2235 Gramos</t>
+  </si>
+  <si>
+    <t>2.24 kg</t>
+  </si>
+  <si>
+    <t>29,5l. x 2,7an. x 18,5al. centímetros</t>
   </si>
   <si>
     <t>B0FYM1D13D</t>
   </si>
   <si>
-    <t>Aspirador de ácaros con luz UV, Mini aspiradora con Filtro HEPA, Aspirador antiacaros con depósito de Polvo Permanente para c</t>
+    <t>Marca: Yaasier | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Alfombra, Relleno | Fuente de alimentación: Batería | ¿Es inalámbrico?: Sí | Usos recomendados para el producto: colchones, sofás, textiles, eliminar el pelo de animales, reducción de alérgenos | Factor de forma: De mano | Color: Blanco | Nombre del modelo: 1X1BSCMY | Dimensiones del producto: 6l. x 4an. x 8al. centímetros</t>
+  </si>
+  <si>
+    <t>Aspirador de ácaros con luz UV, Mini aspiradora con Filtro HEPA, Aspirador antiacaros con depósito de Polvo Permanente para colchones, sofás, Almohadas, alfombras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Tecnología avanzada tres en uno] Aspiradora antiácaros equipada [Tecnología avanzada tres en uno] Equipado con una almohadilla de pulso de doble ritmo y luz UV de 253,7 nm, esta aspiradora ofrece un amplio rango de limpieza y una mayor eficiencia, ideal para eliminar los ácaros del polvo y otros alérgenos de sus colchones y textiles. Con una almohadilla de pulso de doble ritmo y 253,7 nm. Esta aspiradora ofrece luz ultravioleta. una amplia zona de limpieza y una mayor eficiencia, ideal para eliminar los ácaros del polvo y otros alérgenos de tus colchones y textiles.
+[Diseño inalámbrico ligero] Maximice su comodidad con esta aspiradora inalámbrica ligera que tiene una batería recargable que ofrece hasta 30 minutos de tiempo de funcionamiento. Su diseño moderno y elegante se adapta perfectamente a cualquier decoración de interiores y hace que la limpieza sea fácil.
+[Sistema de filtración de alta eficiencia] Limpiador de colchones con un filtro HEPA lavable y un filtro de algodón en la salida, esta aspiradora atrapa el 99,97 % de las partículas de polvo fino, proporciona un aire más saludable y reduce la contaminación secundaria, ideal para personas sensibles y familias con niños.
+[Fácil de limpiar y lavable] Aspirador de ácaros con el depósito de polvo lavable con agua corriente hace que su aspiradora sea más fácil de limpiar. Seque el filtro antes de reutilizarlo para garantizar una succión óptima y un rendimiento de limpieza constante.
+[Versatilidad y comodidad de uso] Aspirador de ácaros con luz UV Ideal para aspirar el pelo de animales y la caspa en diferentes superficies de tela como colchones, cojines, sofás y alfombras. Disfruta de una limpieza silenciosa que no molesta a bebés o mascotas dormidos.</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0FYM1D13D?psc=1</t>
   </si>
   <si>
+    <t>28</t>
+  </si>
+  <si>
     <t>B0DWK8LJF9</t>
   </si>
   <si>
-    <t>aichilra Aspirador de ácaros para colchones, 100 W, portátil, inalámbrico, con doble aspiradora y UV-C y ultrasonido para la</t>
+    <t>Marca: aichilra | Función especial: Limpieza impecable, Luz UV, Recargable | Tipo de filtro: Cartucho | Recomendación de superficie: colchón, almohada, sofá, alfombra | Componentes incluidos: Limpiador al vacío | ¿Es inalámbrico?: Sí | Usos recomendados para el producto: Cama, Pelo de animal, Pelo de mascota, cama, Ácaro | Factor de forma: De mano | Color: Ver Imagen | Dimensiones del producto: 28l. x 27an. x 17al. centímetros</t>
+  </si>
+  <si>
+    <t>aichilra</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=aichilra</t>
+  </si>
+  <si>
+    <t>Aspirador de ácaros para colchones, 100 W, portátil, inalámbrico, con doble aspiradora y UV-C y ultrasonido para la limpieza de ropa de cama y sofá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【Ultrasónico UV】la aspiradora para colchón utiliza tecnología ultrasónica para inhibir la nutrición y la reproducción de ácaros del polvo. Los rayos UV incorporados penetran en el tejido y proporcionan una limpieza profunda del colchón, almohada, sofá de tela o alfombra
+【Sistema de filtrado eficiente】el sistema de filtración sellado con dos ventosas atrapa el polvo y la suciedad y evita que el polvo inhalado penetre hacia el exterior, por lo que no vuelve al medio ambiente y causa contaminación secundaria allí
+【Funcionamiento inalámbrico】esta aspiradora de colchón con batería incorporada proporciona un largo tiempo de funcionamiento una vez que está completamente cargada. El diseño inalámbrico le permite limpiar colchones y sofás de tela en toda su casa sin la restricción de cables
+【Fuerte succión】nuestra aspiradora de cama utiliza vibraciones de alta frecuencia para traer suciedad oculta a la superficie, combinándola con una fuerte succión para una limpieza profunda. Diseño de doble almohadilla plegable que mejora la eficiencia de limpieza
+【Extraíble para la limpieza】el mango ergonómico proporciona un agarre cómodo. El filtro y el depósito de polvo son extraíbles, lavables y reutilizables para garantizar un rendimiento duradero y confiable</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0DWK8LJF9?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61TZ0rMGBrL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41ZFdwgCWGL._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>28l. x 27an. x 17al. centímetros</t>
   </si>
   <si>
     <t>B0DNYVJ4PL</t>
   </si>
   <si>
-    <t>FEPPO Aspirador de ácaros para colchones, 16 kpa con luz UV-C de 253,7 nm, calor 140 °F, filtro HEPA y ultrasonidos, aspirado</t>
+    <t>Marca: FEPPO | Función especial: HEPA, Luz UV | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Colchón | Fuente de alimentación: Eléctrico con cable | Voltaje: 220 Voltios | Componentes incluidos: 1 aspiradora de cama, 1 filtro HEPA doble para el polvo, Manual de usuario | ¿Es inalámbrico?: No | Peso del producto: 2,22 Kilogramos | Vataje: 500 vatios</t>
+  </si>
+  <si>
+    <t>FEPPO</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=FEPPO</t>
+  </si>
+  <si>
+    <t>FEPPO Aspirador de ácaros para colchones, 16 kpa con luz UV-C de 253,7 nm, calor 140 °F, filtro HEPA y ultrasonidos, aspiradora versátil para cama, sofá, cuna (cableado, 500 W)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limpieza profunda de alta eficiencia: nuestra aspiradora de colchón UV dispone de un potente motor de 500 W, que ofrece una fuerte potencia de succión de 16 kPa y 30.000 rpm de alta frecuencia. Penetra profundamente en colchones y capas de tela, eliminando eficazmente el polvo fino, partículas, escamas de la piel y otras sustancias invisibles. Mantenga su colchón y sofá frescos y limpios en todo momento, cree un ambiente más saludable para dormir y disfrute de un hogar más saludable.
+Tecnología UV-C avanzada: equipada con luz UV-C de 253,7 nm y ondas ultrasónicas de 40.000 Hz, nuestra aspiradora de cama elimina el 99,9% de las sustancias invisibles profundamente de las capas del colchón. Las ruedas sensibles a la gravedad aseguran que la luz UV-C solo se active cuando esté en contacto con la superficie y se apague automáticamente al levantar o inclinar, para un uso seguro.
+Filtración multicapa: el aspirador de ácaros dispone de un sistema de filtración multietapa y una estructura de depósito de polvo doble para una filtración óptima. El filtro HEPA avanzado captura el 99,97% de las partículas de hasta 0,3 micras de tamaño, separa eficazmente las impurezas, la caspa de la piel y el polvo, evitando la obstrucción del filtro. Esto prolonga la vida útil del filtro y proporciona una fuerte succión permanente.
+Protección de seguridad: este cepillo de rodillo está equipado con una protección de bloqueo del rotor. Si se enreda en la tela, el rotor detiene automáticamente la operación. El dispositivo está protegido contra sobretensión, sobrecorriente, sobrecalentamiento y cortocircuito. El funcionamiento continuo prolongado puede desencadenar la protección contra sobrecalentamiento del motor, lo que conduce a un apagado temporal. En este caso, apague el dispositivo y deje que se enfríe antes de volver a ponerlo en funcionamiento.
+Secado a alta temperatura: la aspiradora de mano ácaros genera aire seco a alta temperatura de 140 °F que penetra profundamente en tejidos como colchones y sofás y elimina eficazmente sustancias nocivas, reduce la humedad y los olores. La imitación de la luz solar altera el hábitat de los alérgenos, el área limpia permanece seca y fresca, lo que ayuda a crear un ambiente saludable y cómodo para dormir.
+【Diseño inteligente fácil de usar】La aspiradora de cama con cable tiene un conector de succión de 18 cm (7 pulgadas) de ancho que cubre una mayor superficie de limpieza y recoge más polvo en una sola pasada. Con su cuerpo ligero de 1,72 kg, mango ergonómico y cable de alimentación de 5 metros, es fácil de maniobrar y reduce la frecuencia de conexión y desconexión para una experiencia de limpieza fácil y conveniente.</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0DNYVJ4PL?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71X5KPbPpoL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41IqIqkjgVL._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>B0DZTSQFKR</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>2,22 Kilogramos</t>
+  </si>
+  <si>
+    <t>2.22 kg</t>
+  </si>
+  <si>
+    <t>30,2l. x 25an. x 19,5al. centímetros</t>
   </si>
   <si>
     <t>B0FBX24WH6</t>
   </si>
   <si>
-    <t>syayw Limpiador Varuum – 68 W Fuerte Cama vacío para Limpieza ProfundasEliminador de para Mascotas vacío para Cojines de so</t>
+    <t>Marca: syayw | Función especial: Inalámbrico | ¿Es inalámbrico?: Sí | Capacidad: 185 ml | Usos recomendados para el producto: Limpieza profunda de cojines, sofás, hojas, tela, ropa de cama y superficies; eliminación de pelo de mascotas | Factor de forma: De mano | Color: Morado | Nombre del modelo: syayw-SQ9687FVEBHB003E | Dimensiones del producto: 26,9l. x 25,2an. x 14,3al. centímetros | Fabricante: syayw</t>
+  </si>
+  <si>
+    <t>syayw</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=syayw</t>
+  </si>
+  <si>
+    <t>Limpiador Varuum – 68 W Fuerte Cama vacío para Limpieza Profunda | Eliminador de para Mascotas vacío para Cojines de sofá Hojas Tela Ropa de Cama Superficies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prevención avanzada del polvo: el uso de acumulación y propagación de polvo de tecnología avanzada, el vacío BED sin cama garantiza que su hogar esté seguro cada vez que lo use
+Filtración avanzada: con un sistema de filtración avanzado, nuestro vacío puede aislar eficazmente los desechos grandes y capturar incluso las partículas más pequeñas para una limpieza profunda para garantizar el máximo saneamiento
+Funcionalidad eficiente: aprovechando la potencia de 10 kPa y la tecnología eficiente, este vacío puede proporcionar un rendimiento confiable y duradero para la limpieza profunda y durabilidad de su
+Portátil de usar: diseño compacto y ligero, inalámbrico, lo hace flexible y fácil de usar para garantizar la limpieza sin esfuerzo de colchones y otras superficies
+Fácil limpieza: con nuestro vacío podrás disfrutar fácilmente con un filtro de alta eficiencia que se puede enjuagar fácilmente con agua. Mantiene su dispositivo a menudo eficaz e higiénico, a menudo</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0FBX24WH6?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61LvanTuKlL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/61LvanTuKlL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0FQ4FRYT7</t>
+  </si>
+  <si>
+    <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras:Aspiradoras de mano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aspiradoras de futones
+Aspiradoras de mano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31
+1852</t>
+  </si>
+  <si>
+    <t>2025-12-03</t>
+  </si>
+  <si>
+    <t>nousaeg</t>
+  </si>
+  <si>
+    <t>蚌埠市 蚌山区 安徽 233000 CN</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3T9BSXCSWI46M</t>
+  </si>
+  <si>
+    <t>1,02 kg</t>
+  </si>
+  <si>
+    <t>1.02 kg</t>
+  </si>
+  <si>
+    <t>26,9l. x 25,2an. x 14,3al. centímetros</t>
+  </si>
+  <si>
+    <t>26.9 x 25.2 x 14.3 cm</t>
+  </si>
+  <si>
+    <t>26.90 x 25.20 x 14.30 cm</t>
   </si>
   <si>
     <t>导出时自动对相同ASIN去重。可能导致导出的产品总数与页面显示数量不一致</t>
@@ -602,9 +1695,6 @@
   </si>
   <si>
     <t>市场份额</t>
-  </si>
-  <si>
-    <t>未知品牌</t>
   </si>
   <si>
     <t>卖家</t>
@@ -776,11 +1866,11 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -846,13 +1936,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -890,13 +1980,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -978,13 +2068,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1022,13 +2112,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1066,13 +2156,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1110,13 +2200,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1154,13 +2244,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1198,13 +2288,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1242,13 +2332,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1286,13 +2376,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1330,13 +2420,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1374,14 +2464,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1418,13 +2508,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1462,13 +2552,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1506,13 +2596,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1550,13 +2640,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1638,14 +2728,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1682,13 +2772,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1726,13 +2816,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1770,13 +2860,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1814,13 +2904,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1858,13 +2948,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1902,13 +2992,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1990,13 +3080,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2102,6 +3192,94 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="undefined">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>192000</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>44999</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>428799</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>269999</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="Picture 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="undefined">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>192000</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>44999</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>428799</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>269999</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="Picture 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2487,7 +3665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR32"/>
+  <dimension ref="A1:BR33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -2755,7 +3933,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="2" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" s="13">
         <v>1</v>
       </c>
@@ -2769,87 +3947,121 @@
         <v>70</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>73</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L2" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="M2" s="1"/>
+      <c r="M2" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N2" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q2" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O2" s="15">
+        <v>18513</v>
+      </c>
+      <c r="P2" s="15">
+        <v>737</v>
+      </c>
+      <c r="Q2" s="16">
+        <v>0.03</v>
       </c>
       <c r="R2" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S2" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U2" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V2" s="15" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="T2" s="15">
+        <v>105</v>
+      </c>
+      <c r="U2" s="16">
+        <v>1.17</v>
+      </c>
+      <c r="V2" s="15">
+        <v>10879</v>
       </c>
       <c r="W2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="X2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z2" s="19">
+        <v>83</v>
+      </c>
+      <c r="X2" s="15">
+        <v>5168</v>
+      </c>
+      <c r="Y2" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="20">
         <v>85.63</v>
       </c>
-      <c r="AD2" s="20">
-        <v>196</v>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="19">
+        <v>197</v>
+      </c>
+      <c r="AE2" s="15">
+        <v>16</v>
       </c>
       <c r="AF2" s="21">
         <v>4.6</v>
       </c>
       <c r="AG2" s="22">
-        <v>0</v>
+        <v>0.1524</v>
+      </c>
+      <c r="AH2" s="20">
+        <v>5.8</v>
       </c>
       <c r="AI2" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="1"/>
-      <c r="AL2" s="20" t="s">
-        <v>70</v>
+        <v>0.79</v>
+      </c>
+      <c r="AK2" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL2" s="19">
+        <v>360</v>
+      </c>
+      <c r="AM2" s="13" t="s">
+        <v>85</v>
       </c>
       <c r="AN2" s="13" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="AO2" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ2" s="20" t="s">
-        <v>70</v>
+      <c r="AP2" s="20">
+        <v>44.94</v>
+      </c>
+      <c r="AQ2" s="19">
+        <v>8</v>
+      </c>
+      <c r="AR2" s="19">
+        <v>2</v>
+      </c>
+      <c r="AS2" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT2" s="13" t="s">
+        <v>85</v>
       </c>
       <c r="AU2" s="13" t="s">
         <v>70</v>
@@ -2864,7 +4076,7 @@
         <v>70</v>
       </c>
       <c r="AY2" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="AZ2" s="13" t="s">
         <v>70</v>
@@ -2876,7 +4088,7 @@
         <v>70</v>
       </c>
       <c r="BC2" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD2" s="13" t="s">
         <v>70</v>
@@ -2885,7 +4097,7 @@
         <v>70</v>
       </c>
       <c r="BF2" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BG2" s="13" t="s">
         <v>70</v>
@@ -2893,20 +4105,38 @@
       <c r="BH2" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BI2" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ2" s="23" t="s">
+        <v>90</v>
+      </c>
       <c r="BK2" s="23" t="s">
-        <v>70</v>
+        <v>91</v>
+      </c>
+      <c r="BL2" s="23" t="s">
+        <v>92</v>
       </c>
       <c r="BM2" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN2" s="23" t="s">
+        <v>93</v>
+      </c>
       <c r="BO2" s="23" t="s">
-        <v>70</v>
+        <v>94</v>
+      </c>
+      <c r="BP2" s="23" t="s">
+        <v>95</v>
       </c>
       <c r="BQ2" s="23" t="s">
-        <v>70</v>
+        <v>96</v>
+      </c>
+      <c r="BR2" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="3" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" s="13">
         <v>2</v>
       </c>
@@ -2914,59 +4144,64 @@
         <v>70</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>70</v>
+        <v>100</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>101</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="K3" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="M3" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="L3" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="M3" s="1"/>
       <c r="N3" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q3" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O3" s="15">
+        <v>29067</v>
+      </c>
+      <c r="P3" s="15">
+        <v>102736</v>
+      </c>
+      <c r="Q3" s="16">
+        <v>0.78</v>
       </c>
       <c r="R3" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S3" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U3" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V3" s="15" t="s">
-        <v>70</v>
+        <v>108</v>
+      </c>
+      <c r="T3" s="15">
+        <v>41</v>
+      </c>
+      <c r="U3" s="16">
+        <v>4.13</v>
+      </c>
+      <c r="V3" s="15">
+        <v>6970</v>
       </c>
       <c r="W3" s="15" t="s">
         <v>70</v>
@@ -2974,22 +4209,41 @@
       <c r="X3" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z3" s="4"/>
-      <c r="AD3" s="20">
-        <v>184</v>
+      <c r="Y3" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="20">
+        <v>169.99</v>
+      </c>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="19">
+        <v>183</v>
+      </c>
+      <c r="AE3" s="15">
+        <v>9</v>
       </c>
       <c r="AF3" s="21">
         <v>4.5</v>
       </c>
       <c r="AG3" s="22">
-        <v>0</v>
+        <v>0.2195</v>
+      </c>
+      <c r="AH3" s="20">
+        <v>5.8</v>
       </c>
       <c r="AI3" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="1"/>
-      <c r="AL3" s="20" t="s">
-        <v>70</v>
+        <v>0.82</v>
+      </c>
+      <c r="AK3" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="AL3" s="19">
+        <v>150</v>
+      </c>
+      <c r="AM3" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN3" s="13" t="s">
         <v>70</v>
@@ -2997,23 +4251,33 @@
       <c r="AO3" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ3" s="20" t="s">
-        <v>70</v>
+      <c r="AP3" s="4"/>
+      <c r="AQ3" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR3" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS3" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="AT3" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU3" s="13" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="AV3" s="14" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="AW3" s="13" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="AX3" s="13" t="s">
         <v>70</v>
       </c>
       <c r="AY3" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="AZ3" s="13" t="s">
         <v>70</v>
@@ -3025,7 +4289,7 @@
         <v>70</v>
       </c>
       <c r="BC3" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD3" s="13" t="s">
         <v>70</v>
@@ -3034,7 +4298,7 @@
         <v>70</v>
       </c>
       <c r="BF3" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BG3" s="13" t="s">
         <v>70</v>
@@ -3042,20 +4306,38 @@
       <c r="BH3" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BI3" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ3" s="23" t="s">
+        <v>115</v>
+      </c>
       <c r="BK3" s="23" t="s">
-        <v>70</v>
+        <v>116</v>
+      </c>
+      <c r="BL3" s="23" t="s">
+        <v>117</v>
       </c>
       <c r="BM3" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN3" s="23" t="s">
+        <v>118</v>
+      </c>
       <c r="BO3" s="23" t="s">
-        <v>70</v>
+        <v>118</v>
+      </c>
+      <c r="BP3" s="23" t="s">
+        <v>119</v>
       </c>
       <c r="BQ3" s="23" t="s">
-        <v>70</v>
+        <v>120</v>
+      </c>
+      <c r="BR3" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="4" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" s="13">
         <v>3</v>
       </c>
@@ -3063,59 +4345,64 @@
         <v>70</v>
       </c>
       <c r="C4" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="M4" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="N4" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="H4" s="14" t="s">
+      <c r="O4" s="15">
+        <v>60341</v>
+      </c>
+      <c r="P4" s="15">
+        <v>-34936</v>
+      </c>
+      <c r="Q4" s="16">
+        <v>-0.36</v>
+      </c>
+      <c r="R4" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="I4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="M4" s="1"/>
-      <c r="N4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q4" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="R4" s="17" t="s">
-        <v>70</v>
-      </c>
       <c r="S4" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U4" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V4" s="15" t="s">
-        <v>70</v>
+        <v>129</v>
+      </c>
+      <c r="T4" s="15">
+        <v>23</v>
+      </c>
+      <c r="U4" s="16">
+        <v>2.89</v>
+      </c>
+      <c r="V4" s="15">
+        <v>3542</v>
       </c>
       <c r="W4" s="15" t="s">
         <v>70</v>
@@ -3123,22 +4410,41 @@
       <c r="X4" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z4" s="4"/>
-      <c r="AD4" s="20">
-        <v>23</v>
+      <c r="Y4" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="20">
+        <v>153.98</v>
+      </c>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="19">
+        <v>261</v>
+      </c>
+      <c r="AE4" s="15">
+        <v>8</v>
       </c>
       <c r="AF4" s="21">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AG4" s="22">
-        <v>0</v>
+        <v>0.3478</v>
+      </c>
+      <c r="AH4" s="20">
+        <v>8.37</v>
       </c>
       <c r="AI4" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="1"/>
-      <c r="AL4" s="20" t="s">
-        <v>70</v>
+        <v>0.8</v>
+      </c>
+      <c r="AK4" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="AL4" s="19">
+        <v>1076</v>
+      </c>
+      <c r="AM4" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN4" s="13" t="s">
         <v>70</v>
@@ -3146,8 +4452,18 @@
       <c r="AO4" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ4" s="20" t="s">
-        <v>70</v>
+      <c r="AP4" s="4"/>
+      <c r="AQ4" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR4" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS4" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="AT4" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU4" s="13" t="s">
         <v>70</v>
@@ -3156,34 +4472,34 @@
         <v>70</v>
       </c>
       <c r="AW4" s="13" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="AX4" s="13" t="s">
         <v>70</v>
       </c>
       <c r="AY4" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="AZ4" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BA4" s="13" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="BB4" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BC4" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD4" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BE4" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF4" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BG4" s="13" t="s">
         <v>70</v>
@@ -3191,20 +4507,38 @@
       <c r="BH4" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BI4" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ4" s="23" t="s">
+        <v>134</v>
+      </c>
       <c r="BK4" s="23" t="s">
-        <v>70</v>
+        <v>135</v>
+      </c>
+      <c r="BL4" s="23" t="s">
+        <v>136</v>
       </c>
       <c r="BM4" s="23" t="s">
-        <v>70</v>
+        <v>137</v>
+      </c>
+      <c r="BN4" s="23" t="s">
+        <v>138</v>
       </c>
       <c r="BO4" s="23" t="s">
-        <v>70</v>
+        <v>138</v>
+      </c>
+      <c r="BP4" s="23" t="s">
+        <v>139</v>
       </c>
       <c r="BQ4" s="23" t="s">
-        <v>70</v>
+        <v>140</v>
+      </c>
+      <c r="BR4" s="13" t="s">
+        <v>141</v>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="5" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
         <v>4</v>
       </c>
@@ -3212,50 +4546,52 @@
         <v>70</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>70</v>
+        <v>143</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>144</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="M5" s="1"/>
+        <v>142</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N5" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O5" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P5" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q5" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O5" s="15">
+        <v>84052</v>
+      </c>
+      <c r="Q5" s="16">
+        <v>0</v>
       </c>
       <c r="R5" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S5" s="18" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="T5" s="15" t="s">
         <v>70</v>
@@ -3272,15 +4608,15 @@
       <c r="X5" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z5" s="19">
-        <v>66.11</v>
-      </c>
-      <c r="AD5" s="20">
-        <v>40</v>
-      </c>
-      <c r="AF5" s="21">
-        <v>4.7</v>
-      </c>
+      <c r="Y5" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="4"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="2"/>
+      <c r="AF5" s="5"/>
       <c r="AG5" s="22">
         <v>0</v>
       </c>
@@ -3288,8 +4624,11 @@
         <v>0</v>
       </c>
       <c r="AK5" s="1"/>
-      <c r="AL5" s="20" t="s">
-        <v>70</v>
+      <c r="AL5" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM5" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN5" s="13" t="s">
         <v>70</v>
@@ -3297,8 +4636,14 @@
       <c r="AO5" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ5" s="20" t="s">
-        <v>70</v>
+      <c r="AP5" s="4"/>
+      <c r="AQ5" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR5" s="2"/>
+      <c r="AS5" s="1"/>
+      <c r="AT5" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU5" s="13" t="s">
         <v>70</v>
@@ -3342,20 +4687,27 @@
       <c r="BH5" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ5" s="1"/>
       <c r="BK5" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BL5" s="23" t="s">
+        <v>151</v>
+      </c>
       <c r="BM5" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN5" s="1"/>
       <c r="BO5" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP5" s="1"/>
       <c r="BQ5" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR5" s="1"/>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="6" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
         <v>5</v>
       </c>
@@ -3363,59 +4715,64 @@
         <v>70</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>70</v>
+        <v>153</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>70</v>
+        <v>154</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>155</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>89</v>
+        <v>157</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>70</v>
+        <v>158</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>91</v>
+        <v>160</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="M6" s="1"/>
+        <v>161</v>
+      </c>
+      <c r="M6" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N6" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O6" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P6" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q6" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O6" s="15">
+        <v>100246</v>
+      </c>
+      <c r="P6" s="15">
+        <v>178</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>0</v>
       </c>
       <c r="R6" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S6" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T6" s="15" t="s">
-        <v>70</v>
+        <v>162</v>
+      </c>
+      <c r="T6" s="15">
+        <v>26</v>
       </c>
       <c r="U6" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="V6" s="15" t="s">
-        <v>70</v>
+      <c r="V6" s="15">
+        <v>2080</v>
       </c>
       <c r="W6" s="15" t="s">
         <v>70</v>
@@ -3423,31 +4780,60 @@
       <c r="X6" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z6" s="4"/>
-      <c r="AD6" s="20">
-        <v>405</v>
+      <c r="Y6" s="19">
+        <v>2</v>
+      </c>
+      <c r="Z6" s="20">
+        <v>66.11</v>
+      </c>
+      <c r="AA6" s="4"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="19">
+        <v>41</v>
+      </c>
+      <c r="AE6" s="15">
+        <v>1</v>
       </c>
       <c r="AF6" s="21">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AG6" s="22">
-        <v>0</v>
-      </c>
+        <v>0.0385</v>
+      </c>
+      <c r="AH6" s="4"/>
       <c r="AI6" s="16">
         <v>0</v>
       </c>
-      <c r="AK6" s="1"/>
-      <c r="AL6" s="20" t="s">
-        <v>70</v>
+      <c r="AK6" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="AL6" s="19">
+        <v>34</v>
+      </c>
+      <c r="AM6" s="13" t="s">
+        <v>85</v>
       </c>
       <c r="AN6" s="13" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="AO6" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ6" s="20" t="s">
-        <v>70</v>
+      <c r="AP6" s="20">
+        <v>30.57</v>
+      </c>
+      <c r="AQ6" s="19">
+        <v>8</v>
+      </c>
+      <c r="AR6" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS6" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT6" s="13" t="s">
+        <v>85</v>
       </c>
       <c r="AU6" s="13" t="s">
         <v>70</v>
@@ -3491,20 +4877,29 @@
       <c r="BH6" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ6" s="23" t="s">
+        <v>165</v>
+      </c>
       <c r="BK6" s="23" t="s">
-        <v>70</v>
+        <v>166</v>
+      </c>
+      <c r="BL6" s="23" t="s">
+        <v>167</v>
       </c>
       <c r="BM6" s="23" t="s">
-        <v>70</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="BN6" s="1"/>
       <c r="BO6" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP6" s="1"/>
       <c r="BQ6" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR6" s="1"/>
     </row>
-    <row r="7" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="7" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
         <v>6</v>
       </c>
@@ -3512,59 +4907,64 @@
         <v>70</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>92</v>
+        <v>169</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>70</v>
+        <v>171</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>172</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>93</v>
+        <v>174</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>70</v>
+        <v>175</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>94</v>
+        <v>176</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>95</v>
+        <v>177</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="M7" s="1"/>
+        <v>178</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N7" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O7" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P7" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q7" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O7" s="15">
+        <v>97955</v>
+      </c>
+      <c r="P7" s="15">
+        <v>-28001</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>-0.21</v>
       </c>
       <c r="R7" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S7" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T7" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U7" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V7" s="15" t="s">
-        <v>70</v>
+        <v>179</v>
+      </c>
+      <c r="T7" s="15">
+        <v>13</v>
+      </c>
+      <c r="U7" s="16">
+        <v>3.5</v>
+      </c>
+      <c r="V7" s="15">
+        <v>832</v>
       </c>
       <c r="W7" s="15" t="s">
         <v>70</v>
@@ -3572,22 +4972,37 @@
       <c r="X7" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z7" s="4"/>
-      <c r="AD7" s="20">
-        <v>261</v>
+      <c r="Y7" s="19">
+        <v>3</v>
+      </c>
+      <c r="Z7" s="20">
+        <v>63.99</v>
+      </c>
+      <c r="AA7" s="4"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="2"/>
+      <c r="AD7" s="19">
+        <v>23</v>
+      </c>
+      <c r="AE7" s="15">
+        <v>4</v>
       </c>
       <c r="AF7" s="21">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG7" s="22">
-        <v>0</v>
-      </c>
+        <v>0.3077</v>
+      </c>
+      <c r="AH7" s="4"/>
       <c r="AI7" s="16">
         <v>0</v>
       </c>
       <c r="AK7" s="1"/>
-      <c r="AL7" s="20" t="s">
-        <v>70</v>
+      <c r="AL7" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM7" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN7" s="13" t="s">
         <v>70</v>
@@ -3595,17 +5010,27 @@
       <c r="AO7" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ7" s="20" t="s">
-        <v>70</v>
+      <c r="AP7" s="4"/>
+      <c r="AQ7" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR7" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS7" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="AT7" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU7" s="13" t="s">
-        <v>70</v>
+        <v>181</v>
       </c>
       <c r="AV7" s="14" t="s">
-        <v>70</v>
+        <v>182</v>
       </c>
       <c r="AW7" s="13" t="s">
-        <v>70</v>
+        <v>183</v>
       </c>
       <c r="AX7" s="13" t="s">
         <v>70</v>
@@ -3623,7 +5048,7 @@
         <v>70</v>
       </c>
       <c r="BC7" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD7" s="13" t="s">
         <v>70</v>
@@ -3640,20 +5065,29 @@
       <c r="BH7" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ7" s="23" t="s">
+        <v>184</v>
+      </c>
       <c r="BK7" s="23" t="s">
-        <v>70</v>
+        <v>185</v>
+      </c>
+      <c r="BL7" s="23" t="s">
+        <v>186</v>
       </c>
       <c r="BM7" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN7" s="1"/>
       <c r="BO7" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP7" s="1"/>
       <c r="BQ7" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR7" s="1"/>
     </row>
-    <row r="8" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="8" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
         <v>7</v>
       </c>
@@ -3661,59 +5095,64 @@
         <v>70</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>96</v>
+        <v>187</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>70</v>
+        <v>188</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>97</v>
+        <v>190</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>70</v>
+        <v>191</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>99</v>
+        <v>193</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M8" s="1"/>
+        <v>187</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N8" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O8" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P8" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q8" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O8" s="15">
+        <v>146502</v>
+      </c>
+      <c r="P8" s="15">
+        <v>-118244</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>-3.49</v>
       </c>
       <c r="R8" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S8" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T8" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U8" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V8" s="15" t="s">
-        <v>70</v>
+        <v>194</v>
+      </c>
+      <c r="T8" s="15">
+        <v>39</v>
+      </c>
+      <c r="U8" s="16">
+        <v>25.5</v>
+      </c>
+      <c r="V8" s="15">
+        <v>2730</v>
       </c>
       <c r="W8" s="15" t="s">
         <v>70</v>
@@ -3721,22 +5160,41 @@
       <c r="X8" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z8" s="4"/>
-      <c r="AD8" s="20">
-        <v>789</v>
+      <c r="Y8" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="20">
+        <v>69.99</v>
+      </c>
+      <c r="AA8" s="4"/>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="2"/>
+      <c r="AD8" s="19">
+        <v>405</v>
+      </c>
+      <c r="AE8" s="15">
+        <v>6</v>
       </c>
       <c r="AF8" s="21">
         <v>4.6</v>
       </c>
       <c r="AG8" s="22">
-        <v>0</v>
+        <v>0.15380000000000002</v>
+      </c>
+      <c r="AH8" s="20">
+        <v>5.38</v>
       </c>
       <c r="AI8" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="1"/>
-      <c r="AL8" s="20" t="s">
-        <v>70</v>
+        <v>0.77</v>
+      </c>
+      <c r="AK8" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="AL8" s="19">
+        <v>866</v>
+      </c>
+      <c r="AM8" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN8" s="13" t="s">
         <v>70</v>
@@ -3744,44 +5202,54 @@
       <c r="AO8" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ8" s="20" t="s">
-        <v>70</v>
+      <c r="AP8" s="4"/>
+      <c r="AQ8" s="19">
+        <v>9</v>
+      </c>
+      <c r="AR8" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS8" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="AT8" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU8" s="13" t="s">
-        <v>70</v>
+        <v>197</v>
       </c>
       <c r="AV8" s="14" t="s">
-        <v>70</v>
+        <v>198</v>
       </c>
       <c r="AW8" s="13" t="s">
-        <v>70</v>
+        <v>199</v>
       </c>
       <c r="AX8" s="13" t="s">
         <v>70</v>
       </c>
       <c r="AY8" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="AZ8" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BA8" s="13" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="BB8" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BC8" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD8" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BE8" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF8" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BG8" s="13" t="s">
         <v>70</v>
@@ -3789,20 +5257,38 @@
       <c r="BH8" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BI8" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ8" s="23" t="s">
+        <v>200</v>
+      </c>
       <c r="BK8" s="23" t="s">
-        <v>70</v>
+        <v>201</v>
+      </c>
+      <c r="BL8" s="23" t="s">
+        <v>202</v>
       </c>
       <c r="BM8" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN8" s="23" t="s">
+        <v>201</v>
+      </c>
       <c r="BO8" s="23" t="s">
-        <v>70</v>
+        <v>201</v>
+      </c>
+      <c r="BP8" s="23" t="s">
+        <v>203</v>
       </c>
       <c r="BQ8" s="23" t="s">
-        <v>70</v>
+        <v>204</v>
+      </c>
+      <c r="BR8" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="9" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
         <v>8</v>
       </c>
@@ -3810,59 +5296,64 @@
         <v>70</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>100</v>
+        <v>205</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>70</v>
+        <v>206</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>207</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>72</v>
+        <v>208</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>102</v>
+        <v>211</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>103</v>
+        <v>212</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="M9" s="1"/>
+        <v>205</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N9" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O9" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P9" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q9" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O9" s="15">
+        <v>181647</v>
+      </c>
+      <c r="P9" s="15">
+        <v>12251</v>
+      </c>
+      <c r="Q9" s="16">
+        <v>0.36</v>
       </c>
       <c r="R9" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S9" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T9" s="15" t="s">
-        <v>70</v>
+        <v>213</v>
+      </c>
+      <c r="T9" s="15">
+        <v>55</v>
       </c>
       <c r="U9" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="V9" s="15" t="s">
-        <v>70</v>
+      <c r="V9" s="15">
+        <v>1759</v>
       </c>
       <c r="W9" s="15" t="s">
         <v>70</v>
@@ -3870,22 +5361,41 @@
       <c r="X9" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z9" s="4"/>
-      <c r="AD9" s="20">
-        <v>4</v>
+      <c r="Y9" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="20">
+        <v>31.99</v>
+      </c>
+      <c r="AA9" s="4"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="2"/>
+      <c r="AD9" s="19">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="15">
+        <v>2</v>
       </c>
       <c r="AF9" s="21">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AG9" s="22">
-        <v>0</v>
+        <v>0.0364</v>
+      </c>
+      <c r="AH9" s="20">
+        <v>3.75</v>
       </c>
       <c r="AI9" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="1"/>
-      <c r="AL9" s="20" t="s">
-        <v>70</v>
+        <v>0.73</v>
+      </c>
+      <c r="AK9" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="AL9" s="19">
+        <v>29</v>
+      </c>
+      <c r="AM9" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN9" s="13" t="s">
         <v>70</v>
@@ -3893,17 +5403,27 @@
       <c r="AO9" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ9" s="20" t="s">
-        <v>70</v>
+      <c r="AP9" s="4"/>
+      <c r="AQ9" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR9" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS9" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="AT9" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU9" s="13" t="s">
-        <v>70</v>
+        <v>181</v>
       </c>
       <c r="AV9" s="14" t="s">
-        <v>70</v>
+        <v>216</v>
       </c>
       <c r="AW9" s="13" t="s">
-        <v>70</v>
+        <v>217</v>
       </c>
       <c r="AX9" s="13" t="s">
         <v>70</v>
@@ -3921,10 +5441,10 @@
         <v>70</v>
       </c>
       <c r="BC9" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD9" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BE9" s="13" t="s">
         <v>70</v>
@@ -3938,20 +5458,35 @@
       <c r="BH9" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ9" s="23" t="s">
+        <v>218</v>
+      </c>
       <c r="BK9" s="23" t="s">
-        <v>70</v>
+        <v>219</v>
+      </c>
+      <c r="BL9" s="23" t="s">
+        <v>220</v>
       </c>
       <c r="BM9" s="23" t="s">
-        <v>70</v>
+        <v>221</v>
+      </c>
+      <c r="BN9" s="23" t="s">
+        <v>218</v>
       </c>
       <c r="BO9" s="23" t="s">
-        <v>70</v>
+        <v>219</v>
+      </c>
+      <c r="BP9" s="23" t="s">
+        <v>222</v>
       </c>
       <c r="BQ9" s="23" t="s">
-        <v>70</v>
+        <v>223</v>
+      </c>
+      <c r="BR9" s="13" t="s">
+        <v>224</v>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="10" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
         <v>9</v>
       </c>
@@ -3959,59 +5494,64 @@
         <v>70</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>104</v>
+        <v>225</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>70</v>
+        <v>226</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>227</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>72</v>
+        <v>228</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>70</v>
+        <v>230</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>106</v>
+        <v>231</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>107</v>
+        <v>232</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="M10" s="1"/>
+        <v>225</v>
+      </c>
+      <c r="M10" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N10" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O10" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P10" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q10" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O10" s="15">
+        <v>184565</v>
+      </c>
+      <c r="P10" s="15">
+        <v>-113443</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>-2.43</v>
       </c>
       <c r="R10" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S10" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T10" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U10" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V10" s="15" t="s">
-        <v>70</v>
+        <v>233</v>
+      </c>
+      <c r="T10" s="15">
+        <v>34</v>
+      </c>
+      <c r="U10" s="16">
+        <v>1.81</v>
+      </c>
+      <c r="V10" s="15">
+        <v>884</v>
       </c>
       <c r="W10" s="15" t="s">
         <v>70</v>
@@ -4019,22 +5559,41 @@
       <c r="X10" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z10" s="4"/>
-      <c r="AD10" s="20">
+      <c r="Y10" s="19">
         <v>1</v>
       </c>
+      <c r="Z10" s="20">
+        <v>25.99</v>
+      </c>
+      <c r="AA10" s="4"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="2"/>
+      <c r="AD10" s="19">
+        <v>24</v>
+      </c>
+      <c r="AE10" s="15">
+        <v>7</v>
+      </c>
       <c r="AF10" s="21">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="AG10" s="22">
-        <v>0</v>
+        <v>0.2059</v>
+      </c>
+      <c r="AH10" s="20">
+        <v>4.37</v>
       </c>
       <c r="AI10" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="1"/>
-      <c r="AL10" s="20" t="s">
-        <v>70</v>
+        <v>0.68</v>
+      </c>
+      <c r="AK10" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="AL10" s="19">
+        <v>183</v>
+      </c>
+      <c r="AM10" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN10" s="13" t="s">
         <v>70</v>
@@ -4042,17 +5601,27 @@
       <c r="AO10" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ10" s="20" t="s">
-        <v>70</v>
+      <c r="AP10" s="4"/>
+      <c r="AQ10" s="19">
+        <v>9</v>
+      </c>
+      <c r="AR10" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS10" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="AT10" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU10" s="13" t="s">
-        <v>70</v>
+        <v>181</v>
       </c>
       <c r="AV10" s="14" t="s">
-        <v>70</v>
+        <v>236</v>
       </c>
       <c r="AW10" s="13" t="s">
-        <v>70</v>
+        <v>237</v>
       </c>
       <c r="AX10" s="13" t="s">
         <v>70</v>
@@ -4070,7 +5639,7 @@
         <v>70</v>
       </c>
       <c r="BC10" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD10" s="13" t="s">
         <v>70</v>
@@ -4087,20 +5656,35 @@
       <c r="BH10" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ10" s="23" t="s">
+        <v>238</v>
+      </c>
       <c r="BK10" s="23" t="s">
-        <v>70</v>
+        <v>239</v>
+      </c>
+      <c r="BL10" s="23" t="s">
+        <v>240</v>
       </c>
       <c r="BM10" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN10" s="23" t="s">
+        <v>238</v>
+      </c>
       <c r="BO10" s="23" t="s">
-        <v>70</v>
+        <v>239</v>
+      </c>
+      <c r="BP10" s="23" t="s">
+        <v>241</v>
       </c>
       <c r="BQ10" s="23" t="s">
-        <v>70</v>
+        <v>242</v>
+      </c>
+      <c r="BR10" s="13" t="s">
+        <v>243</v>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="11" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
         <v>10</v>
       </c>
@@ -4108,106 +5692,140 @@
         <v>70</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>108</v>
+        <v>244</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>70</v>
+        <v>245</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>70</v>
+        <v>246</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>247</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>72</v>
+        <v>248</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>109</v>
+        <v>249</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="J11" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="O11" s="15">
+        <v>202742</v>
+      </c>
+      <c r="P11" s="15">
+        <v>67932</v>
+      </c>
+      <c r="Q11" s="16">
+        <v>0.48</v>
+      </c>
+      <c r="R11" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="S11" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="T11" s="15">
+        <v>25</v>
+      </c>
+      <c r="U11" s="16">
+        <v>1</v>
+      </c>
+      <c r="V11" s="15">
+        <v>2000</v>
+      </c>
+      <c r="W11" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="X11" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y11" s="19">
+        <v>3</v>
+      </c>
+      <c r="Z11" s="20">
+        <v>79.98</v>
+      </c>
+      <c r="AA11" s="4"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="2"/>
+      <c r="AD11" s="19">
+        <v>791</v>
+      </c>
+      <c r="AE11" s="15">
+        <v>87</v>
+      </c>
+      <c r="AF11" s="21">
+        <v>4.6</v>
+      </c>
+      <c r="AG11" s="22">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="20">
+        <v>5.8</v>
+      </c>
+      <c r="AI11" s="16">
+        <v>0.78</v>
+      </c>
+      <c r="AK11" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="AL11" s="19">
+        <v>213</v>
+      </c>
+      <c r="AM11" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="K11" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O11" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P11" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q11" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="R11" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="S11" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T11" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U11" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V11" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="W11" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="X11" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z11" s="4"/>
-      <c r="AD11" s="20">
-        <v>24</v>
-      </c>
-      <c r="AF11" s="21">
-        <v>2.7</v>
-      </c>
-      <c r="AG11" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="1"/>
-      <c r="AL11" s="20" t="s">
-        <v>70</v>
-      </c>
       <c r="AN11" s="13" t="s">
         <v>70</v>
       </c>
       <c r="AO11" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ11" s="20" t="s">
-        <v>70</v>
+      <c r="AP11" s="4"/>
+      <c r="AQ11" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR11" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS11" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="AT11" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU11" s="13" t="s">
-        <v>70</v>
+        <v>257</v>
       </c>
       <c r="AV11" s="14" t="s">
-        <v>70</v>
+        <v>258</v>
       </c>
       <c r="AW11" s="13" t="s">
-        <v>70</v>
+        <v>259</v>
       </c>
       <c r="AX11" s="13" t="s">
         <v>70</v>
       </c>
       <c r="AY11" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="AZ11" s="13" t="s">
         <v>70</v>
@@ -4219,16 +5837,16 @@
         <v>70</v>
       </c>
       <c r="BC11" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD11" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BE11" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF11" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BG11" s="13" t="s">
         <v>70</v>
@@ -4236,20 +5854,38 @@
       <c r="BH11" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BI11" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ11" s="23" t="s">
+        <v>260</v>
+      </c>
       <c r="BK11" s="23" t="s">
-        <v>70</v>
+        <v>261</v>
+      </c>
+      <c r="BL11" s="23" t="s">
+        <v>262</v>
       </c>
       <c r="BM11" s="23" t="s">
-        <v>70</v>
+        <v>263</v>
+      </c>
+      <c r="BN11" s="23" t="s">
+        <v>261</v>
       </c>
       <c r="BO11" s="23" t="s">
-        <v>70</v>
+        <v>261</v>
+      </c>
+      <c r="BP11" s="23" t="s">
+        <v>264</v>
       </c>
       <c r="BQ11" s="23" t="s">
-        <v>70</v>
+        <v>265</v>
+      </c>
+      <c r="BR11" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="12" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
         <v>11</v>
       </c>
@@ -4257,56 +5893,59 @@
         <v>70</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>112</v>
+        <v>266</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>70</v>
+        <v>267</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>72</v>
+        <v>268</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>113</v>
+        <v>269</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>70</v>
+        <v>270</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>114</v>
+        <v>271</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>115</v>
+        <v>272</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="M12" s="1"/>
+        <v>266</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N12" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O12" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P12" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q12" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O12" s="15">
+        <v>205140</v>
+      </c>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="16">
+        <v>0</v>
       </c>
       <c r="R12" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S12" s="18" t="s">
-        <v>70</v>
+        <v>273</v>
       </c>
       <c r="T12" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="U12" s="16" t="s">
-        <v>70</v>
+      <c r="U12" s="16">
+        <v>0</v>
       </c>
       <c r="V12" s="15" t="s">
         <v>70</v>
@@ -4317,9 +5956,20 @@
       <c r="X12" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z12" s="4"/>
-      <c r="AD12" s="20">
+      <c r="Y12" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="20">
+        <v>72.75</v>
+      </c>
+      <c r="AA12" s="4"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="2"/>
+      <c r="AD12" s="19">
         <v>687</v>
+      </c>
+      <c r="AE12" s="15">
+        <v>1</v>
       </c>
       <c r="AF12" s="21">
         <v>4.6</v>
@@ -4327,12 +5977,20 @@
       <c r="AG12" s="22">
         <v>0</v>
       </c>
+      <c r="AH12" s="20">
+        <v>5.8</v>
+      </c>
       <c r="AI12" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="1"/>
-      <c r="AL12" s="20" t="s">
-        <v>70</v>
+        <v>0.77</v>
+      </c>
+      <c r="AK12" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="AL12" s="19">
+        <v>1102</v>
+      </c>
+      <c r="AM12" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN12" s="13" t="s">
         <v>70</v>
@@ -4340,17 +5998,27 @@
       <c r="AO12" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ12" s="20" t="s">
-        <v>70</v>
+      <c r="AP12" s="4"/>
+      <c r="AQ12" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR12" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS12" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="AT12" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU12" s="13" t="s">
-        <v>70</v>
+        <v>276</v>
       </c>
       <c r="AV12" s="14" t="s">
-        <v>70</v>
+        <v>277</v>
       </c>
       <c r="AW12" s="13" t="s">
-        <v>70</v>
+        <v>278</v>
       </c>
       <c r="AX12" s="13" t="s">
         <v>70</v>
@@ -4368,16 +6036,16 @@
         <v>70</v>
       </c>
       <c r="BC12" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD12" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BE12" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF12" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BG12" s="13" t="s">
         <v>70</v>
@@ -4385,20 +6053,35 @@
       <c r="BH12" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ12" s="23" t="s">
+        <v>279</v>
+      </c>
       <c r="BK12" s="23" t="s">
-        <v>70</v>
+        <v>280</v>
+      </c>
+      <c r="BL12" s="23" t="s">
+        <v>281</v>
       </c>
       <c r="BM12" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN12" s="23" t="s">
+        <v>282</v>
+      </c>
       <c r="BO12" s="23" t="s">
-        <v>70</v>
+        <v>282</v>
+      </c>
+      <c r="BP12" s="23" t="s">
+        <v>283</v>
       </c>
       <c r="BQ12" s="23" t="s">
-        <v>70</v>
+        <v>284</v>
+      </c>
+      <c r="BR12" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="13" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
         <v>12</v>
       </c>
@@ -4406,59 +6089,62 @@
         <v>70</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>116</v>
+        <v>285</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>70</v>
+        <v>286</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>287</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>72</v>
+        <v>288</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>117</v>
+        <v>289</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>118</v>
+        <v>291</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>119</v>
+        <v>292</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="M13" s="1"/>
+        <v>285</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N13" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O13" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P13" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q13" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O13" s="15">
+        <v>207022</v>
+      </c>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="16">
+        <v>0</v>
       </c>
       <c r="R13" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S13" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T13" s="15" t="s">
-        <v>70</v>
+        <v>293</v>
+      </c>
+      <c r="T13" s="15">
+        <v>1</v>
       </c>
       <c r="U13" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="V13" s="15" t="s">
-        <v>70</v>
+      <c r="V13" s="15">
+        <v>25</v>
       </c>
       <c r="W13" s="15" t="s">
         <v>70</v>
@@ -4466,18 +6152,39 @@
       <c r="X13" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z13" s="4"/>
-      <c r="AD13" s="2"/>
-      <c r="AF13" s="5"/>
+      <c r="Y13" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="20">
+        <v>24.99</v>
+      </c>
+      <c r="AA13" s="4"/>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="2"/>
+      <c r="AD13" s="19">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="2"/>
+      <c r="AF13" s="21">
+        <v>4</v>
+      </c>
       <c r="AG13" s="22">
         <v>0</v>
       </c>
+      <c r="AH13" s="20">
+        <v>5.15</v>
+      </c>
       <c r="AI13" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="1"/>
-      <c r="AL13" s="20" t="s">
-        <v>70</v>
+        <v>0.65</v>
+      </c>
+      <c r="AK13" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="AL13" s="19">
+        <v>139</v>
+      </c>
+      <c r="AM13" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN13" s="13" t="s">
         <v>70</v>
@@ -4485,17 +6192,27 @@
       <c r="AO13" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ13" s="20" t="s">
-        <v>70</v>
+      <c r="AP13" s="4"/>
+      <c r="AQ13" s="19">
+        <v>7</v>
+      </c>
+      <c r="AR13" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS13" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="AT13" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU13" s="13" t="s">
-        <v>70</v>
+        <v>181</v>
       </c>
       <c r="AV13" s="14" t="s">
-        <v>70</v>
+        <v>296</v>
       </c>
       <c r="AW13" s="13" t="s">
-        <v>70</v>
+        <v>297</v>
       </c>
       <c r="AX13" s="13" t="s">
         <v>70</v>
@@ -4522,7 +6239,7 @@
         <v>70</v>
       </c>
       <c r="BF13" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BG13" s="13" t="s">
         <v>70</v>
@@ -4530,20 +6247,35 @@
       <c r="BH13" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ13" s="23" t="s">
+        <v>298</v>
+      </c>
       <c r="BK13" s="23" t="s">
-        <v>70</v>
+        <v>299</v>
+      </c>
+      <c r="BL13" s="23" t="s">
+        <v>300</v>
       </c>
       <c r="BM13" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN13" s="23" t="s">
+        <v>301</v>
+      </c>
       <c r="BO13" s="23" t="s">
-        <v>70</v>
+        <v>299</v>
+      </c>
+      <c r="BP13" s="23" t="s">
+        <v>302</v>
       </c>
       <c r="BQ13" s="23" t="s">
-        <v>70</v>
+        <v>303</v>
+      </c>
+      <c r="BR13" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="14" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
         <v>13</v>
       </c>
@@ -4551,50 +6283,52 @@
         <v>70</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>120</v>
+        <v>304</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>70</v>
+        <v>305</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>306</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>72</v>
+        <v>307</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>121</v>
+        <v>308</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>70</v>
+        <v>309</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>122</v>
+        <v>310</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>123</v>
+        <v>311</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="M14" s="1"/>
+        <v>304</v>
+      </c>
+      <c r="M14" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N14" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O14" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P14" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q14" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O14" s="15">
+        <v>216616</v>
+      </c>
+      <c r="Q14" s="16">
+        <v>0</v>
       </c>
       <c r="R14" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S14" s="18" t="s">
-        <v>70</v>
+        <v>312</v>
       </c>
       <c r="T14" s="15" t="s">
         <v>70</v>
@@ -4611,13 +6345,15 @@
       <c r="X14" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y14" s="19">
+        <v>1</v>
+      </c>
       <c r="Z14" s="4"/>
-      <c r="AD14" s="20">
-        <v>136</v>
-      </c>
-      <c r="AF14" s="21">
-        <v>4.4</v>
-      </c>
+      <c r="AA14" s="4"/>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="2"/>
+      <c r="AD14" s="2"/>
+      <c r="AF14" s="5"/>
       <c r="AG14" s="22">
         <v>0</v>
       </c>
@@ -4625,8 +6361,11 @@
         <v>0</v>
       </c>
       <c r="AK14" s="1"/>
-      <c r="AL14" s="20" t="s">
-        <v>70</v>
+      <c r="AL14" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM14" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN14" s="13" t="s">
         <v>70</v>
@@ -4634,8 +6373,14 @@
       <c r="AO14" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ14" s="20" t="s">
-        <v>70</v>
+      <c r="AP14" s="4"/>
+      <c r="AQ14" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR14" s="2"/>
+      <c r="AS14" s="1"/>
+      <c r="AT14" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU14" s="13" t="s">
         <v>70</v>
@@ -4662,7 +6407,7 @@
         <v>70</v>
       </c>
       <c r="BC14" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD14" s="13" t="s">
         <v>70</v>
@@ -4671,7 +6416,7 @@
         <v>70</v>
       </c>
       <c r="BF14" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BG14" s="13" t="s">
         <v>70</v>
@@ -4679,20 +6424,27 @@
       <c r="BH14" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ14" s="1"/>
       <c r="BK14" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BL14" s="23" t="s">
+        <v>313</v>
+      </c>
       <c r="BM14" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN14" s="1"/>
       <c r="BO14" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP14" s="1"/>
       <c r="BQ14" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR14" s="1"/>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="15" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <v>14</v>
       </c>
@@ -4700,50 +6452,55 @@
         <v>70</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>124</v>
+        <v>314</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>70</v>
+        <v>315</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>101</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>125</v>
+        <v>316</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>70</v>
+        <v>317</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>126</v>
+        <v>318</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>127</v>
+        <v>319</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="M15" s="1"/>
+        <v>314</v>
+      </c>
+      <c r="M15" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N15" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O15" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P15" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q15" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O15" s="15">
+        <v>251194</v>
+      </c>
+      <c r="P15" s="15">
+        <v>12285</v>
+      </c>
+      <c r="Q15" s="16">
+        <v>0.05</v>
       </c>
       <c r="R15" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S15" s="18" t="s">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="T15" s="15" t="s">
         <v>70</v>
@@ -4760,40 +6517,69 @@
       <c r="X15" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z15" s="4"/>
-      <c r="AD15" s="20">
+      <c r="Y15" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="20">
+        <v>119.99</v>
+      </c>
+      <c r="AA15" s="4"/>
+      <c r="AB15" s="1"/>
+      <c r="AC15" s="2"/>
+      <c r="AD15" s="19">
+        <v>136</v>
+      </c>
+      <c r="AE15" s="15">
+        <v>2</v>
+      </c>
+      <c r="AF15" s="21">
+        <v>4.4</v>
+      </c>
+      <c r="AG15" s="22">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="20">
+        <v>6.05</v>
+      </c>
+      <c r="AI15" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="AK15" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="AL15" s="19">
+        <v>718</v>
+      </c>
+      <c r="AM15" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN15" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO15" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP15" s="4"/>
+      <c r="AQ15" s="19">
         <v>10</v>
       </c>
-      <c r="AF15" s="21">
-        <v>3.8</v>
-      </c>
-      <c r="AG15" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="1"/>
-      <c r="AL15" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="AN15" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO15" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AQ15" s="20" t="s">
-        <v>70</v>
+      <c r="AR15" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS15" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="AT15" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU15" s="13" t="s">
-        <v>70</v>
+        <v>197</v>
       </c>
       <c r="AV15" s="14" t="s">
-        <v>70</v>
+        <v>323</v>
       </c>
       <c r="AW15" s="13" t="s">
-        <v>70</v>
+        <v>324</v>
       </c>
       <c r="AX15" s="13" t="s">
         <v>70</v>
@@ -4811,16 +6597,16 @@
         <v>70</v>
       </c>
       <c r="BC15" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD15" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BE15" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF15" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BG15" s="13" t="s">
         <v>70</v>
@@ -4828,20 +6614,35 @@
       <c r="BH15" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ15" s="23" t="s">
+        <v>325</v>
+      </c>
       <c r="BK15" s="23" t="s">
-        <v>70</v>
+        <v>326</v>
+      </c>
+      <c r="BL15" s="23" t="s">
+        <v>327</v>
       </c>
       <c r="BM15" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN15" s="23" t="s">
+        <v>328</v>
+      </c>
       <c r="BO15" s="23" t="s">
-        <v>70</v>
+        <v>328</v>
+      </c>
+      <c r="BP15" s="23" t="s">
+        <v>329</v>
       </c>
       <c r="BQ15" s="23" t="s">
-        <v>70</v>
+        <v>330</v>
+      </c>
+      <c r="BR15" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="16" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
         <v>15</v>
       </c>
@@ -4849,50 +6650,52 @@
         <v>70</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>128</v>
+        <v>331</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>70</v>
+        <v>332</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>333</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>72</v>
+        <v>334</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>129</v>
+        <v>335</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>70</v>
+        <v>336</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>130</v>
+        <v>337</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>131</v>
+        <v>338</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="M16" s="1"/>
+        <v>331</v>
+      </c>
+      <c r="M16" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N16" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O16" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P16" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q16" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O16" s="15">
+        <v>326846</v>
+      </c>
+      <c r="Q16" s="16">
+        <v>0</v>
       </c>
       <c r="R16" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S16" s="18" t="s">
-        <v>70</v>
+        <v>339</v>
       </c>
       <c r="T16" s="15" t="s">
         <v>70</v>
@@ -4909,12 +6712,18 @@
       <c r="X16" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y16" s="19">
+        <v>1</v>
+      </c>
       <c r="Z16" s="4"/>
-      <c r="AD16" s="20">
-        <v>28</v>
+      <c r="AA16" s="4"/>
+      <c r="AB16" s="1"/>
+      <c r="AC16" s="2"/>
+      <c r="AD16" s="19">
+        <v>10</v>
       </c>
       <c r="AF16" s="21">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AG16" s="22">
         <v>0</v>
@@ -4923,8 +6732,11 @@
         <v>0</v>
       </c>
       <c r="AK16" s="1"/>
-      <c r="AL16" s="20" t="s">
-        <v>70</v>
+      <c r="AL16" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM16" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN16" s="13" t="s">
         <v>70</v>
@@ -4932,8 +6744,14 @@
       <c r="AO16" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ16" s="20" t="s">
-        <v>70</v>
+      <c r="AP16" s="4"/>
+      <c r="AQ16" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR16" s="2"/>
+      <c r="AS16" s="1"/>
+      <c r="AT16" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU16" s="13" t="s">
         <v>70</v>
@@ -4960,7 +6778,7 @@
         <v>70</v>
       </c>
       <c r="BC16" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD16" s="13" t="s">
         <v>70</v>
@@ -4977,20 +6795,27 @@
       <c r="BH16" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ16" s="1"/>
       <c r="BK16" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BL16" s="23" t="s">
+        <v>340</v>
+      </c>
       <c r="BM16" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN16" s="1"/>
       <c r="BO16" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP16" s="1"/>
       <c r="BQ16" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR16" s="1"/>
     </row>
-    <row r="17" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="17" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A17" s="13">
         <v>16</v>
       </c>
@@ -4998,50 +6823,52 @@
         <v>70</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>132</v>
+        <v>341</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>70</v>
+        <v>342</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>343</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>72</v>
+        <v>344</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>133</v>
+        <v>345</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>70</v>
+        <v>346</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>134</v>
+        <v>347</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>135</v>
+        <v>348</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="M17" s="1"/>
+        <v>349</v>
+      </c>
+      <c r="M17" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N17" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O17" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P17" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q17" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O17" s="15">
+        <v>340911</v>
+      </c>
+      <c r="Q17" s="16">
+        <v>0</v>
       </c>
       <c r="R17" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S17" s="18" t="s">
-        <v>70</v>
+        <v>350</v>
       </c>
       <c r="T17" s="15" t="s">
         <v>70</v>
@@ -5058,12 +6885,18 @@
       <c r="X17" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y17" s="19">
+        <v>1</v>
+      </c>
       <c r="Z17" s="4"/>
-      <c r="AD17" s="20">
-        <v>32</v>
+      <c r="AA17" s="4"/>
+      <c r="AB17" s="1"/>
+      <c r="AC17" s="2"/>
+      <c r="AD17" s="19">
+        <v>28</v>
       </c>
       <c r="AF17" s="21">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AG17" s="22">
         <v>0</v>
@@ -5072,8 +6905,11 @@
         <v>0</v>
       </c>
       <c r="AK17" s="1"/>
-      <c r="AL17" s="20" t="s">
-        <v>70</v>
+      <c r="AL17" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM17" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN17" s="13" t="s">
         <v>70</v>
@@ -5081,8 +6917,14 @@
       <c r="AO17" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ17" s="20" t="s">
-        <v>70</v>
+      <c r="AP17" s="4"/>
+      <c r="AQ17" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR17" s="2"/>
+      <c r="AS17" s="1"/>
+      <c r="AT17" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU17" s="13" t="s">
         <v>70</v>
@@ -5109,10 +6951,10 @@
         <v>70</v>
       </c>
       <c r="BC17" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD17" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BE17" s="13" t="s">
         <v>70</v>
@@ -5126,20 +6968,29 @@
       <c r="BH17" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ17" s="23" t="s">
+        <v>351</v>
+      </c>
       <c r="BK17" s="23" t="s">
-        <v>70</v>
+        <v>352</v>
+      </c>
+      <c r="BL17" s="23" t="s">
+        <v>353</v>
       </c>
       <c r="BM17" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN17" s="1"/>
       <c r="BO17" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP17" s="1"/>
       <c r="BQ17" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR17" s="1"/>
     </row>
-    <row r="18" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="18" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A18" s="13">
         <v>17</v>
       </c>
@@ -5147,50 +6998,52 @@
         <v>70</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>136</v>
+        <v>354</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>70</v>
+        <v>355</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>356</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>72</v>
+        <v>357</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>137</v>
+        <v>358</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>70</v>
+        <v>359</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>138</v>
+        <v>360</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>139</v>
+        <v>361</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="M18" s="1"/>
+        <v>354</v>
+      </c>
+      <c r="M18" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N18" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O18" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P18" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q18" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O18" s="15">
+        <v>464918</v>
+      </c>
+      <c r="Q18" s="16">
+        <v>0</v>
       </c>
       <c r="R18" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S18" s="18" t="s">
-        <v>70</v>
+        <v>362</v>
       </c>
       <c r="T18" s="15" t="s">
         <v>70</v>
@@ -5207,12 +7060,18 @@
       <c r="X18" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y18" s="19">
+        <v>1</v>
+      </c>
       <c r="Z18" s="4"/>
-      <c r="AD18" s="20">
-        <v>15</v>
+      <c r="AA18" s="4"/>
+      <c r="AB18" s="1"/>
+      <c r="AC18" s="2"/>
+      <c r="AD18" s="19">
+        <v>32</v>
       </c>
       <c r="AF18" s="21">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AG18" s="22">
         <v>0</v>
@@ -5221,8 +7080,11 @@
         <v>0</v>
       </c>
       <c r="AK18" s="1"/>
-      <c r="AL18" s="20" t="s">
-        <v>70</v>
+      <c r="AL18" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM18" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN18" s="13" t="s">
         <v>70</v>
@@ -5230,8 +7092,14 @@
       <c r="AO18" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ18" s="20" t="s">
-        <v>70</v>
+      <c r="AP18" s="4"/>
+      <c r="AQ18" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR18" s="2"/>
+      <c r="AS18" s="1"/>
+      <c r="AT18" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU18" s="13" t="s">
         <v>70</v>
@@ -5258,7 +7126,7 @@
         <v>70</v>
       </c>
       <c r="BC18" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD18" s="13" t="s">
         <v>70</v>
@@ -5275,20 +7143,29 @@
       <c r="BH18" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ18" s="23" t="s">
+        <v>115</v>
+      </c>
       <c r="BK18" s="23" t="s">
-        <v>70</v>
+        <v>116</v>
+      </c>
+      <c r="BL18" s="23" t="s">
+        <v>363</v>
       </c>
       <c r="BM18" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN18" s="1"/>
       <c r="BO18" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP18" s="1"/>
       <c r="BQ18" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR18" s="1"/>
     </row>
-    <row r="19" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="19" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A19" s="13">
         <v>18</v>
       </c>
@@ -5296,50 +7173,52 @@
         <v>70</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>140</v>
+        <v>364</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>70</v>
+        <v>365</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>343</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>72</v>
+        <v>344</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>141</v>
+        <v>366</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>70</v>
+        <v>367</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>142</v>
+        <v>368</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>143</v>
+        <v>369</v>
       </c>
       <c r="L19" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="M19" s="1"/>
+        <v>364</v>
+      </c>
+      <c r="M19" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N19" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O19" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P19" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q19" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O19" s="15">
+        <v>517067</v>
+      </c>
+      <c r="Q19" s="16">
+        <v>0</v>
       </c>
       <c r="R19" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S19" s="18" t="s">
-        <v>70</v>
+        <v>370</v>
       </c>
       <c r="T19" s="15" t="s">
         <v>70</v>
@@ -5356,12 +7235,18 @@
       <c r="X19" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y19" s="19">
+        <v>1</v>
+      </c>
       <c r="Z19" s="4"/>
-      <c r="AD19" s="20">
-        <v>11</v>
+      <c r="AA19" s="4"/>
+      <c r="AB19" s="1"/>
+      <c r="AC19" s="2"/>
+      <c r="AD19" s="19">
+        <v>15</v>
       </c>
       <c r="AF19" s="21">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AG19" s="22">
         <v>0</v>
@@ -5370,8 +7255,11 @@
         <v>0</v>
       </c>
       <c r="AK19" s="1"/>
-      <c r="AL19" s="20" t="s">
-        <v>70</v>
+      <c r="AL19" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM19" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN19" s="13" t="s">
         <v>70</v>
@@ -5379,8 +7267,14 @@
       <c r="AO19" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ19" s="20" t="s">
-        <v>70</v>
+      <c r="AP19" s="4"/>
+      <c r="AQ19" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR19" s="2"/>
+      <c r="AS19" s="1"/>
+      <c r="AT19" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU19" s="13" t="s">
         <v>70</v>
@@ -5407,7 +7301,7 @@
         <v>70</v>
       </c>
       <c r="BC19" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD19" s="13" t="s">
         <v>70</v>
@@ -5424,20 +7318,27 @@
       <c r="BH19" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ19" s="1"/>
       <c r="BK19" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BL19" s="23" t="s">
+        <v>371</v>
+      </c>
       <c r="BM19" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN19" s="1"/>
       <c r="BO19" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP19" s="1"/>
       <c r="BQ19" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR19" s="1"/>
     </row>
-    <row r="20" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="20" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A20" s="13">
         <v>19</v>
       </c>
@@ -5445,50 +7346,52 @@
         <v>70</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>144</v>
+        <v>372</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>70</v>
+        <v>373</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>72</v>
+        <v>374</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>145</v>
+        <v>375</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>70</v>
+        <v>376</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>146</v>
+        <v>377</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>147</v>
+        <v>378</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="M20" s="1"/>
+        <v>372</v>
+      </c>
+      <c r="M20" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N20" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O20" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P20" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q20" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O20" s="15">
+        <v>544989</v>
+      </c>
+      <c r="Q20" s="16">
+        <v>0</v>
       </c>
       <c r="R20" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S20" s="18" t="s">
-        <v>70</v>
+        <v>379</v>
       </c>
       <c r="T20" s="15" t="s">
         <v>70</v>
@@ -5505,12 +7408,18 @@
       <c r="X20" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y20" s="19">
+        <v>1</v>
+      </c>
       <c r="Z20" s="4"/>
-      <c r="AD20" s="20">
-        <v>2</v>
+      <c r="AA20" s="4"/>
+      <c r="AB20" s="1"/>
+      <c r="AC20" s="2"/>
+      <c r="AD20" s="19">
+        <v>11</v>
       </c>
       <c r="AF20" s="21">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="AG20" s="22">
         <v>0</v>
@@ -5519,8 +7428,11 @@
         <v>0</v>
       </c>
       <c r="AK20" s="1"/>
-      <c r="AL20" s="20" t="s">
-        <v>70</v>
+      <c r="AL20" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM20" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN20" s="13" t="s">
         <v>70</v>
@@ -5528,8 +7440,14 @@
       <c r="AO20" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ20" s="20" t="s">
-        <v>70</v>
+      <c r="AP20" s="4"/>
+      <c r="AQ20" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR20" s="2"/>
+      <c r="AS20" s="1"/>
+      <c r="AT20" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU20" s="13" t="s">
         <v>70</v>
@@ -5565,7 +7483,7 @@
         <v>70</v>
       </c>
       <c r="BF20" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BG20" s="13" t="s">
         <v>70</v>
@@ -5573,20 +7491,27 @@
       <c r="BH20" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ20" s="1"/>
       <c r="BK20" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BL20" s="23" t="s">
+        <v>380</v>
+      </c>
       <c r="BM20" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN20" s="1"/>
       <c r="BO20" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP20" s="1"/>
       <c r="BQ20" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR20" s="1"/>
     </row>
-    <row r="21" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="21" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A21" s="13">
         <v>20</v>
       </c>
@@ -5594,50 +7519,52 @@
         <v>70</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>148</v>
+        <v>381</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>70</v>
+        <v>382</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>227</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>72</v>
+        <v>383</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>149</v>
+        <v>384</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>150</v>
+        <v>385</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>151</v>
+        <v>386</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="M21" s="1"/>
+        <v>381</v>
+      </c>
+      <c r="M21" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N21" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O21" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P21" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q21" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O21" s="15">
+        <v>647557</v>
+      </c>
+      <c r="Q21" s="16">
+        <v>0</v>
       </c>
       <c r="R21" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S21" s="18" t="s">
-        <v>70</v>
+        <v>387</v>
       </c>
       <c r="T21" s="15" t="s">
         <v>70</v>
@@ -5654,12 +7581,18 @@
       <c r="X21" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y21" s="19">
+        <v>1</v>
+      </c>
       <c r="Z21" s="4"/>
-      <c r="AD21" s="20">
-        <v>27</v>
+      <c r="AA21" s="4"/>
+      <c r="AB21" s="1"/>
+      <c r="AC21" s="2"/>
+      <c r="AD21" s="19">
+        <v>2</v>
       </c>
       <c r="AF21" s="21">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="AG21" s="22">
         <v>0</v>
@@ -5668,8 +7601,11 @@
         <v>0</v>
       </c>
       <c r="AK21" s="1"/>
-      <c r="AL21" s="20" t="s">
-        <v>70</v>
+      <c r="AL21" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM21" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN21" s="13" t="s">
         <v>70</v>
@@ -5677,8 +7613,14 @@
       <c r="AO21" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ21" s="20" t="s">
-        <v>70</v>
+      <c r="AP21" s="4"/>
+      <c r="AQ21" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR21" s="2"/>
+      <c r="AS21" s="1"/>
+      <c r="AT21" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU21" s="13" t="s">
         <v>70</v>
@@ -5722,20 +7664,27 @@
       <c r="BH21" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ21" s="1"/>
       <c r="BK21" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BL21" s="23" t="s">
+        <v>240</v>
+      </c>
       <c r="BM21" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN21" s="1"/>
       <c r="BO21" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP21" s="1"/>
       <c r="BQ21" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR21" s="1"/>
     </row>
-    <row r="22" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="22" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A22" s="13">
         <v>21</v>
       </c>
@@ -5743,50 +7692,52 @@
         <v>70</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>152</v>
+        <v>388</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>70</v>
+        <v>389</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>390</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>72</v>
+        <v>391</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>153</v>
+        <v>392</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>70</v>
+        <v>393</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>154</v>
+        <v>394</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>155</v>
+        <v>395</v>
       </c>
       <c r="L22" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="M22" s="1"/>
+        <v>388</v>
+      </c>
+      <c r="M22" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N22" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O22" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P22" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q22" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O22" s="15">
+        <v>695481</v>
+      </c>
+      <c r="Q22" s="16">
+        <v>0</v>
       </c>
       <c r="R22" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S22" s="18" t="s">
-        <v>70</v>
+        <v>396</v>
       </c>
       <c r="T22" s="15" t="s">
         <v>70</v>
@@ -5803,12 +7754,18 @@
       <c r="X22" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y22" s="19">
+        <v>1</v>
+      </c>
       <c r="Z22" s="4"/>
-      <c r="AD22" s="20">
-        <v>40</v>
+      <c r="AA22" s="4"/>
+      <c r="AB22" s="1"/>
+      <c r="AC22" s="2"/>
+      <c r="AD22" s="19">
+        <v>27</v>
       </c>
       <c r="AF22" s="21">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AG22" s="22">
         <v>0</v>
@@ -5817,8 +7774,11 @@
         <v>0</v>
       </c>
       <c r="AK22" s="1"/>
-      <c r="AL22" s="20" t="s">
-        <v>70</v>
+      <c r="AL22" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM22" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN22" s="13" t="s">
         <v>70</v>
@@ -5826,8 +7786,14 @@
       <c r="AO22" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ22" s="20" t="s">
-        <v>70</v>
+      <c r="AP22" s="4"/>
+      <c r="AQ22" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR22" s="2"/>
+      <c r="AS22" s="1"/>
+      <c r="AT22" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU22" s="13" t="s">
         <v>70</v>
@@ -5854,7 +7820,7 @@
         <v>70</v>
       </c>
       <c r="BC22" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD22" s="13" t="s">
         <v>70</v>
@@ -5871,20 +7837,27 @@
       <c r="BH22" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ22" s="1"/>
       <c r="BK22" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BL22" s="23" t="s">
+        <v>397</v>
+      </c>
       <c r="BM22" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN22" s="1"/>
       <c r="BO22" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP22" s="1"/>
       <c r="BQ22" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR22" s="1"/>
     </row>
-    <row r="23" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="23" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
         <v>22</v>
       </c>
@@ -5892,50 +7865,52 @@
         <v>70</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>156</v>
+        <v>398</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>70</v>
+        <v>399</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>400</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>72</v>
+        <v>401</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>157</v>
+        <v>402</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>70</v>
+        <v>403</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>158</v>
+        <v>404</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>159</v>
+        <v>405</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="M23" s="1"/>
+        <v>398</v>
+      </c>
+      <c r="M23" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N23" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O23" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P23" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q23" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O23" s="15">
+        <v>788744</v>
+      </c>
+      <c r="Q23" s="16">
+        <v>0</v>
       </c>
       <c r="R23" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S23" s="18" t="s">
-        <v>70</v>
+        <v>406</v>
       </c>
       <c r="T23" s="15" t="s">
         <v>70</v>
@@ -5952,12 +7927,18 @@
       <c r="X23" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y23" s="19">
+        <v>1</v>
+      </c>
       <c r="Z23" s="4"/>
-      <c r="AD23" s="20">
-        <v>94</v>
+      <c r="AA23" s="4"/>
+      <c r="AB23" s="1"/>
+      <c r="AC23" s="2"/>
+      <c r="AD23" s="19">
+        <v>40</v>
       </c>
       <c r="AF23" s="21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AG23" s="22">
         <v>0</v>
@@ -5966,8 +7947,11 @@
         <v>0</v>
       </c>
       <c r="AK23" s="1"/>
-      <c r="AL23" s="20" t="s">
-        <v>70</v>
+      <c r="AL23" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM23" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN23" s="13" t="s">
         <v>70</v>
@@ -5975,8 +7959,14 @@
       <c r="AO23" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ23" s="20" t="s">
-        <v>70</v>
+      <c r="AP23" s="4"/>
+      <c r="AQ23" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR23" s="2"/>
+      <c r="AS23" s="1"/>
+      <c r="AT23" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU23" s="13" t="s">
         <v>70</v>
@@ -6003,7 +7993,7 @@
         <v>70</v>
       </c>
       <c r="BC23" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD23" s="13" t="s">
         <v>70</v>
@@ -6012,7 +8002,7 @@
         <v>70</v>
       </c>
       <c r="BF23" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BG23" s="13" t="s">
         <v>70</v>
@@ -6020,20 +8010,27 @@
       <c r="BH23" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ23" s="23" t="s">
+        <v>325</v>
+      </c>
       <c r="BK23" s="23" t="s">
-        <v>70</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="BL23" s="1"/>
       <c r="BM23" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN23" s="1"/>
       <c r="BO23" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP23" s="1"/>
       <c r="BQ23" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR23" s="1"/>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="24" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A24" s="13">
         <v>23</v>
       </c>
@@ -6041,50 +8038,52 @@
         <v>70</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>160</v>
+        <v>407</v>
       </c>
       <c r="D24" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>70</v>
+        <v>408</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>409</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>72</v>
+        <v>410</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>161</v>
+        <v>411</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>70</v>
+        <v>412</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>162</v>
+        <v>413</v>
       </c>
       <c r="K24" s="14" t="s">
-        <v>163</v>
+        <v>414</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="M24" s="1"/>
+        <v>407</v>
+      </c>
+      <c r="M24" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N24" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O24" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P24" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q24" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O24" s="15">
+        <v>796401</v>
+      </c>
+      <c r="Q24" s="16">
+        <v>0</v>
       </c>
       <c r="R24" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S24" s="18" t="s">
-        <v>70</v>
+        <v>415</v>
       </c>
       <c r="T24" s="15" t="s">
         <v>70</v>
@@ -6101,12 +8100,18 @@
       <c r="X24" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y24" s="19">
+        <v>1</v>
+      </c>
       <c r="Z24" s="4"/>
-      <c r="AD24" s="20">
-        <v>7</v>
+      <c r="AA24" s="4"/>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="2"/>
+      <c r="AD24" s="19">
+        <v>94</v>
       </c>
       <c r="AF24" s="21">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="AG24" s="22">
         <v>0</v>
@@ -6115,8 +8120,11 @@
         <v>0</v>
       </c>
       <c r="AK24" s="1"/>
-      <c r="AL24" s="20" t="s">
-        <v>70</v>
+      <c r="AL24" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM24" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN24" s="13" t="s">
         <v>70</v>
@@ -6124,8 +8132,14 @@
       <c r="AO24" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ24" s="20" t="s">
-        <v>70</v>
+      <c r="AP24" s="4"/>
+      <c r="AQ24" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR24" s="2"/>
+      <c r="AS24" s="1"/>
+      <c r="AT24" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU24" s="13" t="s">
         <v>70</v>
@@ -6152,7 +8166,7 @@
         <v>70</v>
       </c>
       <c r="BC24" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD24" s="13" t="s">
         <v>70</v>
@@ -6161,7 +8175,7 @@
         <v>70</v>
       </c>
       <c r="BF24" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BG24" s="13" t="s">
         <v>70</v>
@@ -6169,20 +8183,29 @@
       <c r="BH24" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ24" s="23" t="s">
+        <v>325</v>
+      </c>
       <c r="BK24" s="23" t="s">
-        <v>70</v>
+        <v>326</v>
+      </c>
+      <c r="BL24" s="23" t="s">
+        <v>416</v>
       </c>
       <c r="BM24" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN24" s="1"/>
       <c r="BO24" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP24" s="1"/>
       <c r="BQ24" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR24" s="1"/>
     </row>
-    <row r="25" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="25" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A25" s="13">
         <v>24</v>
       </c>
@@ -6190,50 +8213,52 @@
         <v>70</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>164</v>
+        <v>417</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>70</v>
+        <v>418</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>287</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>72</v>
+        <v>288</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>165</v>
+        <v>419</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>70</v>
+        <v>420</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>166</v>
+        <v>421</v>
       </c>
       <c r="K25" s="14" t="s">
-        <v>167</v>
+        <v>422</v>
       </c>
       <c r="L25" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="M25" s="1"/>
+        <v>417</v>
+      </c>
+      <c r="M25" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N25" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O25" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P25" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q25" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O25" s="15">
+        <v>890649</v>
+      </c>
+      <c r="Q25" s="16">
+        <v>0</v>
       </c>
       <c r="R25" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S25" s="18" t="s">
-        <v>70</v>
+        <v>423</v>
       </c>
       <c r="T25" s="15" t="s">
         <v>70</v>
@@ -6250,12 +8275,18 @@
       <c r="X25" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y25" s="19">
+        <v>1</v>
+      </c>
       <c r="Z25" s="4"/>
-      <c r="AD25" s="20">
-        <v>1</v>
+      <c r="AA25" s="4"/>
+      <c r="AB25" s="1"/>
+      <c r="AC25" s="2"/>
+      <c r="AD25" s="19">
+        <v>7</v>
       </c>
       <c r="AF25" s="21">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AG25" s="22">
         <v>0</v>
@@ -6264,8 +8295,11 @@
         <v>0</v>
       </c>
       <c r="AK25" s="1"/>
-      <c r="AL25" s="20" t="s">
-        <v>70</v>
+      <c r="AL25" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM25" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN25" s="13" t="s">
         <v>70</v>
@@ -6273,8 +8307,14 @@
       <c r="AO25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ25" s="20" t="s">
-        <v>70</v>
+      <c r="AP25" s="4"/>
+      <c r="AQ25" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR25" s="2"/>
+      <c r="AS25" s="1"/>
+      <c r="AT25" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU25" s="13" t="s">
         <v>70</v>
@@ -6301,10 +8341,10 @@
         <v>70</v>
       </c>
       <c r="BC25" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD25" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BE25" s="13" t="s">
         <v>70</v>
@@ -6318,20 +8358,29 @@
       <c r="BH25" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ25" s="23" t="s">
+        <v>424</v>
+      </c>
       <c r="BK25" s="23" t="s">
-        <v>70</v>
+        <v>425</v>
+      </c>
+      <c r="BL25" s="23" t="s">
+        <v>426</v>
       </c>
       <c r="BM25" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN25" s="1"/>
       <c r="BO25" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP25" s="1"/>
       <c r="BQ25" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR25" s="1"/>
     </row>
-    <row r="26" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="26" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
         <v>25</v>
       </c>
@@ -6339,50 +8388,53 @@
         <v>70</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>168</v>
+        <v>427</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>70</v>
+        <v>428</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>429</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>72</v>
+        <v>430</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>169</v>
+        <v>431</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>70</v>
+        <v>432</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>170</v>
+        <v>433</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>171</v>
+        <v>434</v>
       </c>
       <c r="L26" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="M26" s="1"/>
+        <v>435</v>
+      </c>
+      <c r="M26" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N26" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O26" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P26" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q26" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O26" s="15">
+        <v>932661</v>
+      </c>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="16">
+        <v>0</v>
       </c>
       <c r="R26" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S26" s="18" t="s">
-        <v>70</v>
+        <v>436</v>
       </c>
       <c r="T26" s="15" t="s">
         <v>70</v>
@@ -6399,22 +8451,37 @@
       <c r="X26" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z26" s="4"/>
-      <c r="AD26" s="20">
-        <v>26</v>
-      </c>
+      <c r="Y26" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="20">
+        <v>59.99</v>
+      </c>
+      <c r="AA26" s="4"/>
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="2"/>
+      <c r="AD26" s="19">
+        <v>1</v>
+      </c>
+      <c r="AE26" s="2"/>
       <c r="AF26" s="21">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AG26" s="22">
         <v>0</v>
       </c>
+      <c r="AH26" s="4"/>
       <c r="AI26" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="1"/>
-      <c r="AL26" s="20" t="s">
-        <v>70</v>
+        <v>0.85</v>
+      </c>
+      <c r="AK26" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="AL26" s="19">
+        <v>227</v>
+      </c>
+      <c r="AM26" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN26" s="13" t="s">
         <v>70</v>
@@ -6422,17 +8489,27 @@
       <c r="AO26" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ26" s="20" t="s">
-        <v>70</v>
+      <c r="AP26" s="4"/>
+      <c r="AQ26" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR26" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS26" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="AT26" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU26" s="13" t="s">
-        <v>70</v>
+        <v>181</v>
       </c>
       <c r="AV26" s="14" t="s">
-        <v>70</v>
+        <v>439</v>
       </c>
       <c r="AW26" s="13" t="s">
-        <v>70</v>
+        <v>440</v>
       </c>
       <c r="AX26" s="13" t="s">
         <v>70</v>
@@ -6467,20 +8544,27 @@
       <c r="BH26" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ26" s="1"/>
       <c r="BK26" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BL26" s="23" t="s">
+        <v>441</v>
+      </c>
       <c r="BM26" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN26" s="1"/>
       <c r="BO26" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP26" s="1"/>
       <c r="BQ26" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR26" s="1"/>
     </row>
-    <row r="27" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="27" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A27" s="13">
         <v>26</v>
       </c>
@@ -6488,50 +8572,52 @@
         <v>70</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>172</v>
+        <v>442</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>70</v>
+        <v>443</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>70</v>
+        <v>444</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>155</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>72</v>
+        <v>445</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>173</v>
+        <v>446</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>70</v>
+        <v>447</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>174</v>
+        <v>448</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>175</v>
+        <v>449</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="M27" s="1"/>
+        <v>450</v>
+      </c>
+      <c r="M27" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N27" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O27" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P27" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q27" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O27" s="15">
+        <v>1050716</v>
+      </c>
+      <c r="Q27" s="16">
+        <v>0</v>
       </c>
       <c r="R27" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S27" s="18" t="s">
-        <v>70</v>
+        <v>451</v>
       </c>
       <c r="T27" s="15" t="s">
         <v>70</v>
@@ -6548,12 +8634,18 @@
       <c r="X27" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y27" s="19">
+        <v>1</v>
+      </c>
       <c r="Z27" s="4"/>
-      <c r="AD27" s="20">
-        <v>2</v>
+      <c r="AA27" s="4"/>
+      <c r="AB27" s="1"/>
+      <c r="AC27" s="2"/>
+      <c r="AD27" s="19">
+        <v>26</v>
       </c>
       <c r="AF27" s="21">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="AG27" s="22">
         <v>0</v>
@@ -6562,8 +8654,11 @@
         <v>0</v>
       </c>
       <c r="AK27" s="1"/>
-      <c r="AL27" s="20" t="s">
-        <v>70</v>
+      <c r="AL27" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM27" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN27" s="13" t="s">
         <v>70</v>
@@ -6571,8 +8666,14 @@
       <c r="AO27" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ27" s="20" t="s">
-        <v>70</v>
+      <c r="AP27" s="4"/>
+      <c r="AQ27" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR27" s="2"/>
+      <c r="AS27" s="1"/>
+      <c r="AT27" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU27" s="13" t="s">
         <v>70</v>
@@ -6616,20 +8717,27 @@
       <c r="BH27" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ27" s="1"/>
       <c r="BK27" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BL27" s="23" t="s">
+        <v>452</v>
+      </c>
       <c r="BM27" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN27" s="1"/>
       <c r="BO27" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP27" s="1"/>
       <c r="BQ27" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR27" s="1"/>
     </row>
-    <row r="28" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="28" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A28" s="13">
         <v>27</v>
       </c>
@@ -6637,50 +8745,52 @@
         <v>70</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>176</v>
+        <v>453</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>70</v>
+        <v>454</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>287</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>72</v>
+        <v>288</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>177</v>
+        <v>455</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>70</v>
+        <v>456</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>178</v>
+        <v>457</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>131</v>
+        <v>458</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="M28" s="1"/>
+        <v>453</v>
+      </c>
+      <c r="M28" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N28" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O28" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P28" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q28" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O28" s="15">
+        <v>1057452</v>
+      </c>
+      <c r="Q28" s="16">
+        <v>0</v>
       </c>
       <c r="R28" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S28" s="18" t="s">
-        <v>70</v>
+        <v>459</v>
       </c>
       <c r="T28" s="15" t="s">
         <v>70</v>
@@ -6697,12 +8807,18 @@
       <c r="X28" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y28" s="19">
+        <v>1</v>
+      </c>
       <c r="Z28" s="4"/>
-      <c r="AD28" s="20">
-        <v>4</v>
+      <c r="AA28" s="4"/>
+      <c r="AB28" s="1"/>
+      <c r="AC28" s="2"/>
+      <c r="AD28" s="19">
+        <v>2</v>
       </c>
       <c r="AF28" s="21">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AG28" s="22">
         <v>0</v>
@@ -6711,8 +8827,11 @@
         <v>0</v>
       </c>
       <c r="AK28" s="1"/>
-      <c r="AL28" s="20" t="s">
-        <v>70</v>
+      <c r="AL28" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM28" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN28" s="13" t="s">
         <v>70</v>
@@ -6720,8 +8839,14 @@
       <c r="AO28" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ28" s="20" t="s">
-        <v>70</v>
+      <c r="AP28" s="4"/>
+      <c r="AQ28" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR28" s="2"/>
+      <c r="AS28" s="1"/>
+      <c r="AT28" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU28" s="13" t="s">
         <v>70</v>
@@ -6748,10 +8873,10 @@
         <v>70</v>
       </c>
       <c r="BC28" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD28" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BE28" s="13" t="s">
         <v>70</v>
@@ -6765,20 +8890,29 @@
       <c r="BH28" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ28" s="23" t="s">
+        <v>460</v>
+      </c>
       <c r="BK28" s="23" t="s">
-        <v>70</v>
+        <v>461</v>
+      </c>
+      <c r="BL28" s="23" t="s">
+        <v>462</v>
       </c>
       <c r="BM28" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN28" s="1"/>
       <c r="BO28" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP28" s="1"/>
       <c r="BQ28" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR28" s="1"/>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A29" s="13">
         <v>28</v>
       </c>
@@ -6786,50 +8920,52 @@
         <v>70</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>179</v>
+        <v>463</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>70</v>
+        <v>464</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>343</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>72</v>
+        <v>344</v>
       </c>
       <c r="H29" s="14" t="s">
-        <v>180</v>
+        <v>465</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>70</v>
+        <v>466</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>181</v>
+        <v>467</v>
       </c>
       <c r="K29" s="14" t="s">
-        <v>182</v>
+        <v>348</v>
       </c>
       <c r="L29" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="M29" s="1"/>
+        <v>463</v>
+      </c>
+      <c r="M29" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N29" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O29" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P29" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q29" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O29" s="15">
+        <v>1158454</v>
+      </c>
+      <c r="Q29" s="16">
+        <v>0</v>
       </c>
       <c r="R29" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S29" s="18" t="s">
-        <v>70</v>
+        <v>468</v>
       </c>
       <c r="T29" s="15" t="s">
         <v>70</v>
@@ -6846,12 +8982,18 @@
       <c r="X29" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y29" s="19">
+        <v>1</v>
+      </c>
       <c r="Z29" s="4"/>
-      <c r="AD29" s="20">
+      <c r="AA29" s="4"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="2"/>
+      <c r="AD29" s="19">
         <v>4</v>
       </c>
       <c r="AF29" s="21">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="AG29" s="22">
         <v>0</v>
@@ -6860,8 +9002,11 @@
         <v>0</v>
       </c>
       <c r="AK29" s="1"/>
-      <c r="AL29" s="20" t="s">
-        <v>70</v>
+      <c r="AL29" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM29" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN29" s="13" t="s">
         <v>70</v>
@@ -6869,8 +9014,14 @@
       <c r="AO29" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ29" s="20" t="s">
-        <v>70</v>
+      <c r="AP29" s="4"/>
+      <c r="AQ29" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR29" s="2"/>
+      <c r="AS29" s="1"/>
+      <c r="AT29" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU29" s="13" t="s">
         <v>70</v>
@@ -6897,7 +9048,7 @@
         <v>70</v>
       </c>
       <c r="BC29" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD29" s="13" t="s">
         <v>70</v>
@@ -6914,20 +9065,27 @@
       <c r="BH29" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ29" s="1"/>
       <c r="BK29" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BL29" s="23" t="s">
+        <v>353</v>
+      </c>
       <c r="BM29" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN29" s="1"/>
       <c r="BO29" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP29" s="1"/>
       <c r="BQ29" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR29" s="1"/>
     </row>
-    <row r="30" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="30" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A30" s="13">
         <v>29</v>
       </c>
@@ -6935,50 +9093,52 @@
         <v>70</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>183</v>
+        <v>469</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>70</v>
+        <v>470</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>471</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>72</v>
+        <v>472</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>184</v>
+        <v>473</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>70</v>
+        <v>474</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>185</v>
+        <v>475</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>186</v>
+        <v>476</v>
       </c>
       <c r="L30" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="M30" s="1"/>
+        <v>469</v>
+      </c>
+      <c r="M30" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N30" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O30" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P30" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q30" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O30" s="15">
+        <v>1217733</v>
+      </c>
+      <c r="Q30" s="16">
+        <v>0</v>
       </c>
       <c r="R30" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S30" s="18" t="s">
-        <v>70</v>
+        <v>477</v>
       </c>
       <c r="T30" s="15" t="s">
         <v>70</v>
@@ -6995,12 +9155,18 @@
       <c r="X30" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y30" s="19">
+        <v>1</v>
+      </c>
       <c r="Z30" s="4"/>
-      <c r="AD30" s="20">
-        <v>62</v>
+      <c r="AA30" s="4"/>
+      <c r="AB30" s="1"/>
+      <c r="AC30" s="2"/>
+      <c r="AD30" s="19">
+        <v>4</v>
       </c>
       <c r="AF30" s="21">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AG30" s="22">
         <v>0</v>
@@ -7009,8 +9175,11 @@
         <v>0</v>
       </c>
       <c r="AK30" s="1"/>
-      <c r="AL30" s="20" t="s">
-        <v>70</v>
+      <c r="AL30" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM30" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN30" s="13" t="s">
         <v>70</v>
@@ -7018,8 +9187,14 @@
       <c r="AO30" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ30" s="20" t="s">
-        <v>70</v>
+      <c r="AP30" s="4"/>
+      <c r="AQ30" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR30" s="2"/>
+      <c r="AS30" s="1"/>
+      <c r="AT30" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU30" s="13" t="s">
         <v>70</v>
@@ -7046,7 +9221,7 @@
         <v>70</v>
       </c>
       <c r="BC30" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BD30" s="13" t="s">
         <v>70</v>
@@ -7055,7 +9230,7 @@
         <v>70</v>
       </c>
       <c r="BF30" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BG30" s="13" t="s">
         <v>70</v>
@@ -7063,20 +9238,27 @@
       <c r="BH30" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ30" s="1"/>
       <c r="BK30" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BL30" s="23" t="s">
+        <v>478</v>
+      </c>
       <c r="BM30" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN30" s="1"/>
       <c r="BO30" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP30" s="1"/>
       <c r="BQ30" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR30" s="1"/>
     </row>
-    <row r="31" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="31" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A31" s="13">
         <v>30</v>
       </c>
@@ -7084,50 +9266,52 @@
         <v>70</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>187</v>
+        <v>479</v>
       </c>
       <c r="D31" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>70</v>
+        <v>480</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>481</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>72</v>
+        <v>482</v>
       </c>
       <c r="H31" s="14" t="s">
-        <v>188</v>
+        <v>483</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>70</v>
+        <v>484</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>189</v>
+        <v>485</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>190</v>
+        <v>486</v>
       </c>
       <c r="L31" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="M31" s="1"/>
+        <v>487</v>
+      </c>
+      <c r="M31" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N31" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O31" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P31" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q31" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O31" s="15">
+        <v>1411305</v>
+      </c>
+      <c r="Q31" s="16">
+        <v>0</v>
       </c>
       <c r="R31" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S31" s="18" t="s">
-        <v>70</v>
+        <v>488</v>
       </c>
       <c r="T31" s="15" t="s">
         <v>70</v>
@@ -7144,9 +9328,19 @@
       <c r="X31" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y31" s="19">
+        <v>1</v>
+      </c>
       <c r="Z31" s="4"/>
-      <c r="AD31" s="2"/>
-      <c r="AF31" s="5"/>
+      <c r="AA31" s="4"/>
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="2"/>
+      <c r="AD31" s="19">
+        <v>62</v>
+      </c>
+      <c r="AF31" s="21">
+        <v>4.6</v>
+      </c>
       <c r="AG31" s="22">
         <v>0</v>
       </c>
@@ -7154,8 +9348,11 @@
         <v>0</v>
       </c>
       <c r="AK31" s="1"/>
-      <c r="AL31" s="20" t="s">
-        <v>70</v>
+      <c r="AL31" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM31" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AN31" s="13" t="s">
         <v>70</v>
@@ -7163,8 +9360,14 @@
       <c r="AO31" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ31" s="20" t="s">
-        <v>70</v>
+      <c r="AP31" s="4"/>
+      <c r="AQ31" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR31" s="2"/>
+      <c r="AS31" s="1"/>
+      <c r="AT31" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AU31" s="13" t="s">
         <v>70</v>
@@ -7182,10 +9385,10 @@
         <v>70</v>
       </c>
       <c r="AZ31" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="BA31" s="13" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="BB31" s="13" t="s">
         <v>70</v>
@@ -7208,255 +9411,533 @@
       <c r="BH31" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ31" s="23" t="s">
+        <v>489</v>
+      </c>
       <c r="BK31" s="23" t="s">
-        <v>70</v>
+        <v>490</v>
+      </c>
+      <c r="BL31" s="23" t="s">
+        <v>491</v>
       </c>
       <c r="BM31" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN31" s="1"/>
       <c r="BO31" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP31" s="1"/>
       <c r="BQ31" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR31" s="1"/>
     </row>
-    <row r="32" ht="28" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A32" s="24"/>
-      <c r="B32" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="24"/>
-      <c r="N32" s="24"/>
-      <c r="O32" s="25"/>
-      <c r="P32" s="25"/>
-      <c r="Q32" s="26"/>
-      <c r="R32" s="24"/>
-      <c r="S32" s="25"/>
-      <c r="T32" s="25"/>
-      <c r="U32" s="26"/>
-      <c r="V32" s="25"/>
-      <c r="W32" s="25"/>
-      <c r="X32" s="25"/>
-      <c r="Y32" s="25"/>
-      <c r="Z32" s="27"/>
-      <c r="AA32" s="27"/>
-      <c r="AB32" s="24"/>
-      <c r="AC32" s="25"/>
-      <c r="AD32" s="25"/>
-      <c r="AE32" s="25"/>
-      <c r="AF32" s="28"/>
-      <c r="AG32" s="29"/>
-      <c r="AH32" s="27"/>
-      <c r="AI32" s="26"/>
-      <c r="AJ32" s="24"/>
-      <c r="AK32" s="24"/>
-      <c r="AL32" s="25"/>
-      <c r="AM32" s="24"/>
-      <c r="AN32" s="24"/>
-      <c r="AO32" s="24"/>
-      <c r="AP32" s="27"/>
-      <c r="AQ32" s="25"/>
-      <c r="AR32" s="25"/>
-      <c r="AS32" s="24"/>
-      <c r="AT32" s="24"/>
-      <c r="AU32" s="24"/>
-      <c r="AV32" s="24"/>
-      <c r="AW32" s="24"/>
-      <c r="AX32" s="24"/>
-      <c r="AY32" s="24"/>
-      <c r="AZ32" s="24"/>
-      <c r="BA32" s="24"/>
-      <c r="BB32" s="24"/>
-      <c r="BC32" s="24"/>
-      <c r="BD32" s="24"/>
-      <c r="BE32" s="24"/>
-      <c r="BF32" s="24"/>
-      <c r="BG32" s="24"/>
-      <c r="BH32" s="24"/>
-      <c r="BI32" s="24"/>
-      <c r="BJ32" s="24"/>
-      <c r="BK32" s="24"/>
-      <c r="BL32" s="24"/>
-      <c r="BM32" s="24"/>
-      <c r="BN32" s="24"/>
-      <c r="BO32" s="24"/>
-      <c r="BP32" s="24"/>
-      <c r="BQ32" s="24"/>
-      <c r="BR32" s="24"/>
+    <row r="32" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="A32" s="13">
+        <v>31</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>493</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>494</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>495</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>496</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>497</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>498</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>499</v>
+      </c>
+      <c r="L32" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="M32" s="14" t="s">
+        <v>501</v>
+      </c>
+      <c r="N32" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="O32" s="15">
+        <v>1559184</v>
+      </c>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="16">
+        <v>0</v>
+      </c>
+      <c r="R32" s="17" t="s">
+        <v>502</v>
+      </c>
+      <c r="S32" s="18" t="s">
+        <v>503</v>
+      </c>
+      <c r="T32" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="U32" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="V32" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="W32" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="X32" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y32" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="20">
+        <v>38.11</v>
+      </c>
+      <c r="AA32" s="4"/>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="2"/>
+      <c r="AD32" s="2"/>
+      <c r="AE32" s="2"/>
+      <c r="AF32" s="5"/>
+      <c r="AG32" s="22">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="20">
+        <v>5.05</v>
+      </c>
+      <c r="AI32" s="16">
+        <v>0.71</v>
+      </c>
+      <c r="AK32" s="13" t="s">
+        <v>504</v>
+      </c>
+      <c r="AL32" s="19">
+        <v>299</v>
+      </c>
+      <c r="AM32" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN32" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO32" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP32" s="4"/>
+      <c r="AQ32" s="19">
+        <v>8</v>
+      </c>
+      <c r="AR32" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS32" s="14" t="s">
+        <v>505</v>
+      </c>
+      <c r="AT32" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="AU32" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="AV32" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="AW32" s="13" t="s">
+        <v>507</v>
+      </c>
+      <c r="AX32" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AY32" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AZ32" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BA32" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BB32" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BC32" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="BD32" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BE32" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BF32" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BG32" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BH32" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="BJ32" s="23" t="s">
+        <v>508</v>
+      </c>
+      <c r="BK32" s="23" t="s">
+        <v>509</v>
+      </c>
+      <c r="BL32" s="23" t="s">
+        <v>510</v>
+      </c>
+      <c r="BM32" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="BN32" s="23" t="s">
+        <v>509</v>
+      </c>
+      <c r="BO32" s="23" t="s">
+        <v>509</v>
+      </c>
+      <c r="BP32" s="23" t="s">
+        <v>511</v>
+      </c>
+      <c r="BQ32" s="23" t="s">
+        <v>512</v>
+      </c>
+      <c r="BR32" s="13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="A33" s="24"/>
+      <c r="B33" s="24" t="s">
+        <v>513</v>
+      </c>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="24"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="24"/>
+      <c r="N33" s="24"/>
+      <c r="O33" s="25"/>
+      <c r="P33" s="25"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="24"/>
+      <c r="S33" s="25"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="26"/>
+      <c r="V33" s="25"/>
+      <c r="W33" s="25"/>
+      <c r="X33" s="25"/>
+      <c r="Y33" s="25"/>
+      <c r="Z33" s="27"/>
+      <c r="AA33" s="27"/>
+      <c r="AB33" s="24"/>
+      <c r="AC33" s="25"/>
+      <c r="AD33" s="25"/>
+      <c r="AE33" s="25"/>
+      <c r="AF33" s="28"/>
+      <c r="AG33" s="29"/>
+      <c r="AH33" s="27"/>
+      <c r="AI33" s="26"/>
+      <c r="AJ33" s="24"/>
+      <c r="AK33" s="24"/>
+      <c r="AL33" s="25"/>
+      <c r="AM33" s="24"/>
+      <c r="AN33" s="24"/>
+      <c r="AO33" s="24"/>
+      <c r="AP33" s="27"/>
+      <c r="AQ33" s="25"/>
+      <c r="AR33" s="25"/>
+      <c r="AS33" s="24"/>
+      <c r="AT33" s="24"/>
+      <c r="AU33" s="24"/>
+      <c r="AV33" s="24"/>
+      <c r="AW33" s="24"/>
+      <c r="AX33" s="24"/>
+      <c r="AY33" s="24"/>
+      <c r="AZ33" s="24"/>
+      <c r="BA33" s="24"/>
+      <c r="BB33" s="24"/>
+      <c r="BC33" s="24"/>
+      <c r="BD33" s="24"/>
+      <c r="BE33" s="24"/>
+      <c r="BF33" s="24"/>
+      <c r="BG33" s="24"/>
+      <c r="BH33" s="24"/>
+      <c r="BI33" s="24"/>
+      <c r="BJ33" s="24"/>
+      <c r="BK33" s="24"/>
+      <c r="BL33" s="24"/>
+      <c r="BM33" s="24"/>
+      <c r="BN33" s="24"/>
+      <c r="BO33" s="24"/>
+      <c r="BP33" s="24"/>
+      <c r="BQ33" s="24"/>
+      <c r="BR33" s="24"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" tooltip="https://www.amazon.es/dp/B0FPQMRBYZ"/>
-    <hyperlink ref="G2" r:id="rId2" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="G2" r:id="rId2" tooltip="https://www.amazon.es/stores/K%C3%A4rcherEspa%C3%B1a/page/B353BDC4-AECC-4400-8FE8-010A626D7853?lp_asin=B0FPQMRBYZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
     <hyperlink ref="J2" r:id="rId3" tooltip="https://www.amazon.es/dp/B0FPQMRBYZ?psc=1"/>
-    <hyperlink ref="K2" r:id="rId4" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81RtcozDdwL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="K2" r:id="rId4" tooltip="https://images-na.ssl-images-amazon.com/images/I/81RtcozDdwL._AC_US600_.jpg"/>
     <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.es/dp/B0FPQMRBYZ"/>
-    <hyperlink ref="C3" r:id="rId6" tooltip="https://www.amazon.es/dp/B0GXVR9CY9"/>
-    <hyperlink ref="G3" r:id="rId7" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J3" r:id="rId8" tooltip="https://www.amazon.es/dp/B0GXVR9CY9?psc=1"/>
-    <hyperlink ref="K3" r:id="rId9" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71um1FaVwRL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L3" r:id="rId10" tooltip="https://www.amazon.es/dp/B0GXVR9CY9"/>
-    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.es/dp/B0GMPVWCZM"/>
-    <hyperlink ref="G4" r:id="rId12" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.es/dp/B0GMPVWCZM?psc=1"/>
-    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81J2yw2XZnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.es/dp/B0GMPVWCZM"/>
-    <hyperlink ref="C5" r:id="rId16" tooltip="https://www.amazon.es/dp/B0HFRH1NNC"/>
-    <hyperlink ref="G5" r:id="rId17" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J5" r:id="rId18" tooltip="https://www.amazon.es/dp/B0HFRH1NNC?psc=1"/>
-    <hyperlink ref="K5" r:id="rId19" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L5" r:id="rId20" tooltip="https://www.amazon.es/dp/B0HFRH1NNC"/>
-    <hyperlink ref="C6" r:id="rId21" tooltip="https://www.amazon.es/dp/B0D3QGFGR8"/>
-    <hyperlink ref="G6" r:id="rId22" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J6" r:id="rId23" tooltip="https://www.amazon.es/dp/B0D3QGFGR8?psc=1"/>
-    <hyperlink ref="K6" r:id="rId24" tooltip="https://images-eu.ssl-images-amazon.com/images/I/716CxESQq9L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L6" r:id="rId25" tooltip="https://www.amazon.es/dp/B0D3QGFGR8"/>
-    <hyperlink ref="C7" r:id="rId26" tooltip="https://www.amazon.es/dp/B0CHMPZVZT"/>
-    <hyperlink ref="G7" r:id="rId27" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.es/dp/B0CHMPZVZT?psc=1"/>
-    <hyperlink ref="K7" r:id="rId29" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71FO+Ga+gLL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.es/dp/B0CHMPZVZT"/>
-    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.es/dp/B0GFCJ4JWY"/>
-    <hyperlink ref="G8" r:id="rId32" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.es/dp/B0GFCJ4JWY?psc=1"/>
-    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71AmFHqQF6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.es/dp/B0GFCJ4JWY"/>
-    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.es/dp/B0HG11J16S"/>
-    <hyperlink ref="G9" r:id="rId37" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.es/dp/B0HG11J16S?psc=1"/>
-    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.es/dp/B0HG11J16S"/>
-    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.es/dp/B0GF7CNTYL"/>
-    <hyperlink ref="G10" r:id="rId42" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.es/dp/B0GF7CNTYL?psc=1"/>
-    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.es/dp/B0GF7CNTYL"/>
-    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.es/dp/B0GHQLQBYD"/>
-    <hyperlink ref="G11" r:id="rId47" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.es/dp/B0GHQLQBYD?psc=1"/>
-    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-eu.ssl-images-amazon.com/images/I/610gU-iwIJL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.es/dp/B0GHQLQBYD"/>
-    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.es/dp/B0CJFR8YZ1"/>
-    <hyperlink ref="G12" r:id="rId52" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.es/dp/B0CJFR8YZ1?psc=1"/>
-    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71wwrAJ4EpL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.es/dp/B0CJFR8YZ1"/>
-    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK"/>
-    <hyperlink ref="G13" r:id="rId57" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK?psc=1"/>
-    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61HKr6BnAHL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK"/>
-    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.es/dp/B0D9BQHSWQ"/>
-    <hyperlink ref="G14" r:id="rId62" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.es/dp/B0D9BQHSWQ?psc=1"/>
-    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/619CHOWba4L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.es/dp/B0D9BQHSWQ"/>
-    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.es/dp/B0F6XNKG8M"/>
-    <hyperlink ref="G15" r:id="rId67" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.es/dp/B0F6XNKG8M?psc=1"/>
-    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.es/dp/B0F6XNKG8M"/>
-    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.es/dp/B0FVS559GZ"/>
-    <hyperlink ref="G16" r:id="rId72" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.es/dp/B0FVS559GZ?psc=1"/>
-    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.es/dp/B0FVS559GZ"/>
-    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.es/dp/B0DT1D15C6"/>
-    <hyperlink ref="G17" r:id="rId77" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.es/dp/B0DT1D15C6?psc=1"/>
-    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81vdWh-NSLL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.es/dp/B0DT1D15C6"/>
-    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.es/dp/B0FKRC3KQY"/>
-    <hyperlink ref="G18" r:id="rId82" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.es/dp/B0FKRC3KQY?psc=1"/>
-    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.es/dp/B0FKRC3KQY"/>
-    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.es/dp/B0FDWVV95V"/>
-    <hyperlink ref="G19" r:id="rId87" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.es/dp/B0FDWVV95V?psc=1"/>
-    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.es/dp/B0FDWVV95V"/>
-    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.es/dp/B0GYS43G8G"/>
-    <hyperlink ref="G20" r:id="rId92" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.es/dp/B0GYS43G8G?psc=1"/>
-    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.es/dp/B0GYS43G8G"/>
-    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.es/dp/B0D83SRY9V"/>
-    <hyperlink ref="G21" r:id="rId97" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.es/dp/B0D83SRY9V?psc=1"/>
-    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51LjSaAmb9L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.es/dp/B0D83SRY9V"/>
-    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.es/dp/B0FN3GPQZM"/>
-    <hyperlink ref="G22" r:id="rId102" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.es/dp/B0FN3GPQZM?psc=1"/>
-    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.es/dp/B0FN3GPQZM"/>
-    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.es/dp/B0F8HD3649"/>
-    <hyperlink ref="G23" r:id="rId107" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.es/dp/B0F8HD3649?psc=1"/>
-    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71CtAiuTm1L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.es/dp/B0F8HD3649"/>
-    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.es/dp/B0DNZ5LDQX"/>
-    <hyperlink ref="G24" r:id="rId112" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.es/dp/B0DNZ5LDQX?psc=1"/>
-    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61YjHSHoT6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.es/dp/B0DNZ5LDQX"/>
-    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.es/dp/B0FBGQY9YP"/>
-    <hyperlink ref="G25" r:id="rId117" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.es/dp/B0FBGQY9YP?psc=1"/>
-    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71OWNtREIXL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.es/dp/B0FBGQY9YP"/>
-    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.es/dp/B0G4RSJQVT"/>
-    <hyperlink ref="G26" r:id="rId122" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.es/dp/B0G4RSJQVT?psc=1"/>
-    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.es/dp/B0G4RSJQVT"/>
-    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.es/dp/B0F9NJM4V9"/>
-    <hyperlink ref="G27" r:id="rId127" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.es/dp/B0F9NJM4V9?psc=1"/>
-    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.es/dp/B0F9NJM4V9"/>
-    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.es/dp/B0FYM1D13D"/>
-    <hyperlink ref="G28" r:id="rId132" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.es/dp/B0FYM1D13D?psc=1"/>
-    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.es/dp/B0FYM1D13D"/>
-    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.es/dp/B0DWK8LJF9"/>
-    <hyperlink ref="G29" r:id="rId137" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.es/dp/B0DWK8LJF9?psc=1"/>
-    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61TZ0rMGBrL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.es/dp/B0DWK8LJF9"/>
-    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.es/dp/B0DNYVJ4PL"/>
-    <hyperlink ref="G30" r:id="rId142" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.es/dp/B0DNYVJ4PL?psc=1"/>
-    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71X5KPbPpoL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.es/dp/B0DNYVJ4PL"/>
-    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.es/dp/B0FBX24WH6"/>
-    <hyperlink ref="G31" r:id="rId147" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.es/dp/B0FBX24WH6?psc=1"/>
-    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61LvanTuKlL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.es/dp/B0FBX24WH6"/>
+    <hyperlink ref="M2" r:id="rId6" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N2" r:id="rId7"/>
+    <hyperlink ref="C3" r:id="rId8" tooltip="https://www.amazon.es/dp/B0GXVR9CY9"/>
+    <hyperlink ref="G3" r:id="rId9" tooltip="https://www.amazon.es/Jimmy/b/ref=bl_dp_s_web_17484947031?ie=UTF8&amp;node=17484947031&amp;field-lbr_brands_browse-bin=Jimmy"/>
+    <hyperlink ref="J3" r:id="rId10" tooltip="https://www.amazon.es/dp/B0GXVR9CY9?psc=1"/>
+    <hyperlink ref="K3" r:id="rId11" tooltip="https://m.media-amazon.com/images/I/41bn7Lrs3VL._AC_US600_.jpg"/>
+    <hyperlink ref="L3" r:id="rId12" tooltip="https://www.amazon.es/dp/B0GY2TN25G"/>
+    <hyperlink ref="M3" r:id="rId13" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N3" r:id="rId14"/>
+    <hyperlink ref="AW3" r:id="rId15" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AUUOYWQE00J1M"/>
+    <hyperlink ref="C4" r:id="rId16" tooltip="https://www.amazon.es/dp/B0CHMPZVZT"/>
+    <hyperlink ref="G4" r:id="rId17" tooltip="https://www.amazon.es/stores/JIGOO-ES/page/23E9C8F3-B11D-41BE-B25B-391D7999E178?lp_asin=B0CHMPZVZT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J4" r:id="rId18" tooltip="https://www.amazon.es/dp/B0CHMPZVZT?psc=1"/>
+    <hyperlink ref="K4" r:id="rId19" tooltip="https://images-na.ssl-images-amazon.com/images/I/71FO+Ga+gLL._AC_US600_.jpg"/>
+    <hyperlink ref="L4" r:id="rId20" tooltip="https://www.amazon.es/dp/B0CHMPZVZT"/>
+    <hyperlink ref="M4" r:id="rId21" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N4" r:id="rId22"/>
+    <hyperlink ref="AW4" r:id="rId23" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3HDNBYVK69SMO"/>
+    <hyperlink ref="C5" r:id="rId24" tooltip="https://www.amazon.es/dp/B0HBMBNXJ1"/>
+    <hyperlink ref="G5" r:id="rId25" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=RANJIMA"/>
+    <hyperlink ref="J5" r:id="rId26" tooltip="https://www.amazon.es/dp/B0HBMBNXJ1?psc=1"/>
+    <hyperlink ref="K5" r:id="rId27" tooltip="https://m.media-amazon.com/images/I/31DuAHlA2DL._AC_US200_.jpg"/>
+    <hyperlink ref="L5" r:id="rId28" tooltip="https://www.amazon.es/dp/B0HBMBNXJ1"/>
+    <hyperlink ref="M5" r:id="rId29" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N5" r:id="rId30"/>
+    <hyperlink ref="C6" r:id="rId31" tooltip="https://www.amazon.es/dp/B0HFRH1NNC"/>
+    <hyperlink ref="G6" r:id="rId32" tooltip="https://www.amazon.es/stores/Lubluelu/page/6949B717-1950-436B-B468-8BFB57AEF209?lp_asin=B0HFRH1NNC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J6" r:id="rId33" tooltip="https://www.amazon.es/dp/B0HFRH1NNC?psc=1"/>
+    <hyperlink ref="K6" r:id="rId34" tooltip="https://m.media-amazon.com/images/I/41WpJwb0PhL._AC_US600_.jpg"/>
+    <hyperlink ref="L6" r:id="rId35" tooltip="https://www.amazon.es/dp/B0G654P9MD"/>
+    <hyperlink ref="M6" r:id="rId36" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N6" r:id="rId37"/>
+    <hyperlink ref="C7" r:id="rId38" tooltip="https://www.amazon.es/dp/B0GMPVWCZM"/>
+    <hyperlink ref="G7" r:id="rId39" tooltip="https://www.amazon.es/Elecbee/b/ref=bl_dp_s_web_51202246031?ie=UTF8&amp;node=51202246031&amp;field-lbr_brands_browse-bin=Elecbee"/>
+    <hyperlink ref="J7" r:id="rId40" tooltip="https://www.amazon.es/dp/B0GMPVWCZM?psc=1"/>
+    <hyperlink ref="K7" r:id="rId41" tooltip="https://m.media-amazon.com/images/I/41tqM0+3BpL._AC_US600_.jpg"/>
+    <hyperlink ref="L7" r:id="rId42" tooltip="https://www.amazon.es/dp/B0H45T73K1"/>
+    <hyperlink ref="M7" r:id="rId43" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N7" r:id="rId44"/>
+    <hyperlink ref="AW7" r:id="rId45" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WTTH4P2M430O"/>
+    <hyperlink ref="C8" r:id="rId46" tooltip="https://www.amazon.es/dp/B0D3QGFGR8"/>
+    <hyperlink ref="G8" r:id="rId47" tooltip="https://www.amazon.es/stores/JIGOO-ES/page/23E9C8F3-B11D-41BE-B25B-391D7999E178?lp_asin=B0D3QGFGR8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J8" r:id="rId48" tooltip="https://www.amazon.es/dp/B0D3QGFGR8?psc=1"/>
+    <hyperlink ref="K8" r:id="rId49" tooltip="https://images-na.ssl-images-amazon.com/images/I/716CxESQq9L._AC_US600_.jpg"/>
+    <hyperlink ref="L8" r:id="rId50" tooltip="https://www.amazon.es/dp/B0D3QGFGR8"/>
+    <hyperlink ref="M8" r:id="rId51" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N8" r:id="rId52"/>
+    <hyperlink ref="AW8" r:id="rId53" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3DJH46Q40BXN4"/>
+    <hyperlink ref="C9" r:id="rId54" tooltip="https://www.amazon.es/dp/B0HG11J16S"/>
+    <hyperlink ref="G9" r:id="rId55" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Beghdhu"/>
+    <hyperlink ref="J9" r:id="rId56" tooltip="https://www.amazon.es/dp/B0HG11J16S?psc=1"/>
+    <hyperlink ref="K9" r:id="rId57" tooltip="https://images-na.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_US600_.jpg"/>
+    <hyperlink ref="L9" r:id="rId58" tooltip="https://www.amazon.es/dp/B0HG11J16S"/>
+    <hyperlink ref="M9" r:id="rId59" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N9" r:id="rId60"/>
+    <hyperlink ref="AW9" r:id="rId61" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2DJZ6ZEQ14JUA"/>
+    <hyperlink ref="C10" r:id="rId62" tooltip="https://www.amazon.es/dp/B0GHQLQBYD"/>
+    <hyperlink ref="G10" r:id="rId63" tooltip="https://www.amazon.es/stores/ALILILUYAA/page/6F2D9C3F-3247-41D0-93BE-BD3270082609?lp_asin=B0GHQLQBYD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J10" r:id="rId64" tooltip="https://www.amazon.es/dp/B0GHQLQBYD?psc=1"/>
+    <hyperlink ref="K10" r:id="rId65" tooltip="https://images-na.ssl-images-amazon.com/images/I/610gU-iwIJL._AC_US600_.jpg"/>
+    <hyperlink ref="L10" r:id="rId66" tooltip="https://www.amazon.es/dp/B0GHQLQBYD"/>
+    <hyperlink ref="M10" r:id="rId67" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N10" r:id="rId68"/>
+    <hyperlink ref="AW10" r:id="rId69" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ASTEKNQOF9QUQ"/>
+    <hyperlink ref="C11" r:id="rId70" tooltip="https://www.amazon.es/dp/B0GFCJ4JWY"/>
+    <hyperlink ref="G11" r:id="rId71" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=PEXCHO"/>
+    <hyperlink ref="J11" r:id="rId72" tooltip="https://www.amazon.es/dp/B0GFCJ4JWY?psc=1"/>
+    <hyperlink ref="K11" r:id="rId73" tooltip="https://m.media-amazon.com/images/I/51KOcYPAxDL._AC_US600_.jpg"/>
+    <hyperlink ref="L11" r:id="rId74" tooltip="https://www.amazon.es/dp/B0FHF6RYSW"/>
+    <hyperlink ref="M11" r:id="rId75" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N11" r:id="rId76"/>
+    <hyperlink ref="AW11" r:id="rId77" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1FS4IJJC47VBD"/>
+    <hyperlink ref="C12" r:id="rId78" tooltip="https://www.amazon.es/dp/B0CJFR8YZ1"/>
+    <hyperlink ref="G12" r:id="rId79" tooltip="https://www.amazon.es/stores/JIGOO-ES/page/23E9C8F3-B11D-41BE-B25B-391D7999E178?lp_asin=B0CJFR8YZ1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J12" r:id="rId80" tooltip="https://www.amazon.es/dp/B0CJFR8YZ1?psc=1"/>
+    <hyperlink ref="K12" r:id="rId81" tooltip="https://images-na.ssl-images-amazon.com/images/I/71wwrAJ4EpL._AC_US600_.jpg"/>
+    <hyperlink ref="L12" r:id="rId82" tooltip="https://www.amazon.es/dp/B0CJFR8YZ1"/>
+    <hyperlink ref="M12" r:id="rId83" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N12" r:id="rId84"/>
+    <hyperlink ref="AW12" r:id="rId85" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SBFZKR4LHBTM"/>
+    <hyperlink ref="C13" r:id="rId86" tooltip="https://www.amazon.es/dp/B0GF7CNTYL"/>
+    <hyperlink ref="G13" r:id="rId87" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
+    <hyperlink ref="J13" r:id="rId88" tooltip="https://www.amazon.es/dp/B0GF7CNTYL?psc=1"/>
+    <hyperlink ref="K13" r:id="rId89" tooltip="https://m.media-amazon.com/images/I/41CQc-U9WtL._AC_US600_.jpg"/>
+    <hyperlink ref="L13" r:id="rId90" tooltip="https://www.amazon.es/dp/B0GF7CNTYL"/>
+    <hyperlink ref="M13" r:id="rId91" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N13" r:id="rId92"/>
+    <hyperlink ref="AW13" r:id="rId93" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y"/>
+    <hyperlink ref="C14" r:id="rId94" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK"/>
+    <hyperlink ref="G14" r:id="rId95" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Bcuuozeeing"/>
+    <hyperlink ref="J14" r:id="rId96" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK?psc=1"/>
+    <hyperlink ref="K14" r:id="rId97" tooltip="https://m.media-amazon.com/images/I/41ei98pWxqL._AC_US200_.jpg"/>
+    <hyperlink ref="L14" r:id="rId98" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK"/>
+    <hyperlink ref="M14" r:id="rId99" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N14" r:id="rId100"/>
+    <hyperlink ref="C15" r:id="rId101" tooltip="https://www.amazon.es/dp/B0D9BQHSWQ"/>
+    <hyperlink ref="G15" r:id="rId102" tooltip="https://www.amazon.es/Jimmy/b/ref=bl_dp_s_web_17484947031?ie=UTF8&amp;node=17484947031&amp;field-lbr_brands_browse-bin=Jimmy"/>
+    <hyperlink ref="J15" r:id="rId103" tooltip="https://www.amazon.es/dp/B0D9BQHSWQ?psc=1"/>
+    <hyperlink ref="K15" r:id="rId104" tooltip="https://images-na.ssl-images-amazon.com/images/I/619CHOWba4L._AC_US600_.jpg"/>
+    <hyperlink ref="L15" r:id="rId105" tooltip="https://www.amazon.es/dp/B0D9BQHSWQ"/>
+    <hyperlink ref="M15" r:id="rId106" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N15" r:id="rId107"/>
+    <hyperlink ref="AW15" r:id="rId108" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UUYGTGLOQBB0"/>
+    <hyperlink ref="C16" r:id="rId109" tooltip="https://www.amazon.es/dp/B0F6XNKG8M"/>
+    <hyperlink ref="G16" r:id="rId110" tooltip="https://www.amazon.es/stores/Tiazhan/page/B4946EA8-16BD-438A-89E6-C36320E22788?lp_asin=B0F6XNKG8M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J16" r:id="rId111" tooltip="https://www.amazon.es/dp/B0F6XNKG8M?psc=1"/>
+    <hyperlink ref="K16" r:id="rId112" tooltip="https://m.media-amazon.com/images/I/41BYSfgxHfL._AC_US200_.jpg"/>
+    <hyperlink ref="L16" r:id="rId113" tooltip="https://www.amazon.es/dp/B0F6XNKG8M"/>
+    <hyperlink ref="M16" r:id="rId114" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N16" r:id="rId115"/>
+    <hyperlink ref="C17" r:id="rId116" tooltip="https://www.amazon.es/dp/B0FVS559GZ"/>
+    <hyperlink ref="G17" r:id="rId117" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J17" r:id="rId118" tooltip="https://www.amazon.es/dp/B0FVS559GZ?psc=1"/>
+    <hyperlink ref="K17" r:id="rId119" tooltip="https://m.media-amazon.com/images/I/31eLjeocEiL._AC_US200_.jpg"/>
+    <hyperlink ref="L17" r:id="rId120" tooltip="https://www.amazon.es/dp/B0GHDFVK7R"/>
+    <hyperlink ref="M17" r:id="rId121" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N17" r:id="rId122"/>
+    <hyperlink ref="C18" r:id="rId123" tooltip="https://www.amazon.es/dp/B0DT1D15C6"/>
+    <hyperlink ref="G18" r:id="rId124" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=CREATULIZE"/>
+    <hyperlink ref="J18" r:id="rId125" tooltip="https://www.amazon.es/dp/B0DT1D15C6?psc=1"/>
+    <hyperlink ref="K18" r:id="rId126" tooltip="https://m.media-amazon.com/images/I/51ZP52evVDL._AC_US200_.jpg"/>
+    <hyperlink ref="L18" r:id="rId127" tooltip="https://www.amazon.es/dp/B0DT1D15C6"/>
+    <hyperlink ref="M18" r:id="rId128" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N18" r:id="rId129"/>
+    <hyperlink ref="C19" r:id="rId130" tooltip="https://www.amazon.es/dp/B0FKRC3KQY"/>
+    <hyperlink ref="G19" r:id="rId131" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J19" r:id="rId132" tooltip="https://www.amazon.es/dp/B0FKRC3KQY?psc=1"/>
+    <hyperlink ref="K19" r:id="rId133" tooltip="https://m.media-amazon.com/images/I/31SPlR-BXSL._AC_US200_.jpg"/>
+    <hyperlink ref="L19" r:id="rId134" tooltip="https://www.amazon.es/dp/B0FKRC3KQY"/>
+    <hyperlink ref="M19" r:id="rId135" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N19" r:id="rId136"/>
+    <hyperlink ref="C20" r:id="rId137" tooltip="https://www.amazon.es/dp/B0FDWVV95V"/>
+    <hyperlink ref="G20" r:id="rId138" tooltip="https://www.amazon.es/stores/JIGOO-ES/page/23E9C8F3-B11D-41BE-B25B-391D7999E178?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J20" r:id="rId139" tooltip="https://www.amazon.es/dp/B0FDWVV95V?psc=1"/>
+    <hyperlink ref="K20" r:id="rId140" tooltip="https://m.media-amazon.com/images/I/31va0mFb48L._AC_US200_.jpg"/>
+    <hyperlink ref="L20" r:id="rId141" tooltip="https://www.amazon.es/dp/B0FDWVV95V"/>
+    <hyperlink ref="M20" r:id="rId142" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N20" r:id="rId143"/>
+    <hyperlink ref="C21" r:id="rId144" tooltip="https://www.amazon.es/dp/B0GYS43G8G"/>
+    <hyperlink ref="G21" r:id="rId145" tooltip="https://www.amazon.es/stores/ALILILUYAA/page/6F2D9C3F-3247-41D0-93BE-BD3270082609?lp_asin=B0GYS43G8G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J21" r:id="rId146" tooltip="https://www.amazon.es/dp/B0GYS43G8G?psc=1"/>
+    <hyperlink ref="K21" r:id="rId147" tooltip="https://m.media-amazon.com/images/I/31Nn49TeoxL._AC_US200_.jpg"/>
+    <hyperlink ref="L21" r:id="rId148" tooltip="https://www.amazon.es/dp/B0GYS43G8G"/>
+    <hyperlink ref="M21" r:id="rId149" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N21" r:id="rId150"/>
+    <hyperlink ref="C22" r:id="rId151" tooltip="https://www.amazon.es/dp/B0D83SRY9V"/>
+    <hyperlink ref="G22" r:id="rId152" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Redcoutt"/>
+    <hyperlink ref="J22" r:id="rId153" tooltip="https://www.amazon.es/dp/B0D83SRY9V?psc=1"/>
+    <hyperlink ref="K22" r:id="rId154" tooltip="https://m.media-amazon.com/images/I/51LjSaAmb9L._AC_US200_.jpg"/>
+    <hyperlink ref="L22" r:id="rId155" tooltip="https://www.amazon.es/dp/B0D83SRY9V"/>
+    <hyperlink ref="M22" r:id="rId156" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N22" r:id="rId157"/>
+    <hyperlink ref="C23" r:id="rId158" tooltip="https://www.amazon.es/dp/B0FN3GPQZM"/>
+    <hyperlink ref="G23" r:id="rId159" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Teant"/>
+    <hyperlink ref="J23" r:id="rId160" tooltip="https://www.amazon.es/dp/B0FN3GPQZM?psc=1"/>
+    <hyperlink ref="K23" r:id="rId161" tooltip="https://m.media-amazon.com/images/I/41B+I610d+L._AC_US200_.jpg"/>
+    <hyperlink ref="L23" r:id="rId162" tooltip="https://www.amazon.es/dp/B0FN3GPQZM"/>
+    <hyperlink ref="M23" r:id="rId163" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N23" r:id="rId164"/>
+    <hyperlink ref="C24" r:id="rId165" tooltip="https://www.amazon.es/dp/B0F8HD3649"/>
+    <hyperlink ref="G24" r:id="rId166" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Mayking"/>
+    <hyperlink ref="J24" r:id="rId167" tooltip="https://www.amazon.es/dp/B0F8HD3649?psc=1"/>
+    <hyperlink ref="K24" r:id="rId168" tooltip="https://m.media-amazon.com/images/I/41548PPAf0L._AC_US200_.jpg"/>
+    <hyperlink ref="L24" r:id="rId169" tooltip="https://www.amazon.es/dp/B0F8HD3649"/>
+    <hyperlink ref="M24" r:id="rId170" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N24" r:id="rId171"/>
+    <hyperlink ref="C25" r:id="rId172" tooltip="https://www.amazon.es/dp/B0DNZ5LDQX"/>
+    <hyperlink ref="G25" r:id="rId173" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
+    <hyperlink ref="J25" r:id="rId174" tooltip="https://www.amazon.es/dp/B0DNZ5LDQX?psc=1"/>
+    <hyperlink ref="K25" r:id="rId175" tooltip="https://m.media-amazon.com/images/I/41VwiuPGuQL._AC_US200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId176" tooltip="https://www.amazon.es/dp/B0DNZ5LDQX"/>
+    <hyperlink ref="M25" r:id="rId177" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N25" r:id="rId178"/>
+    <hyperlink ref="C26" r:id="rId179" tooltip="https://www.amazon.es/dp/B0FBGQY9YP"/>
+    <hyperlink ref="G26" r:id="rId180" tooltip="https://www.amazon.es/stores/Fey/page/43F7FFA5-3E54-4A0B-BF57-3795C4422856?lp_asin=B0FBGQY9YP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J26" r:id="rId181" tooltip="https://www.amazon.es/dp/B0FBGQY9YP?psc=1"/>
+    <hyperlink ref="K26" r:id="rId182" tooltip="https://images-na.ssl-images-amazon.com/images/I/71OWNtREIXL._AC_US600_.jpg"/>
+    <hyperlink ref="L26" r:id="rId183" tooltip="https://www.amazon.es/dp/B0FCCCLS1X"/>
+    <hyperlink ref="M26" r:id="rId184" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N26" r:id="rId185"/>
+    <hyperlink ref="AW26" r:id="rId186" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3MSJ66TMU8M67"/>
+    <hyperlink ref="C27" r:id="rId187" tooltip="https://www.amazon.es/dp/B0G4RSJQVT"/>
+    <hyperlink ref="G27" r:id="rId188" tooltip="https://www.amazon.es/stores/Lubluelu/page/6949B717-1950-436B-B468-8BFB57AEF209?lp_asin=B0G4RSJQVT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J27" r:id="rId189" tooltip="https://www.amazon.es/dp/B0G4RSJQVT?psc=1"/>
+    <hyperlink ref="K27" r:id="rId190" tooltip="https://m.media-amazon.com/images/I/41T59G+lWKL._AC_US200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId191" tooltip="https://www.amazon.es/dp/B0HJRMXSZC"/>
+    <hyperlink ref="M27" r:id="rId192" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N27" r:id="rId193"/>
+    <hyperlink ref="C28" r:id="rId194" tooltip="https://www.amazon.es/dp/B0F9NJM4V9"/>
+    <hyperlink ref="G28" r:id="rId195" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
+    <hyperlink ref="J28" r:id="rId196" tooltip="https://www.amazon.es/dp/B0F9NJM4V9?psc=1"/>
+    <hyperlink ref="K28" r:id="rId197" tooltip="https://m.media-amazon.com/images/I/41skTyVFYpL._AC_US200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId198" tooltip="https://www.amazon.es/dp/B0F9NJM4V9"/>
+    <hyperlink ref="M28" r:id="rId199" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N28" r:id="rId200"/>
+    <hyperlink ref="C29" r:id="rId201" tooltip="https://www.amazon.es/dp/B0FYM1D13D"/>
+    <hyperlink ref="G29" r:id="rId202" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J29" r:id="rId203" tooltip="https://www.amazon.es/dp/B0FYM1D13D?psc=1"/>
+    <hyperlink ref="K29" r:id="rId204" tooltip="https://m.media-amazon.com/images/I/31eLjeocEiL._AC_US200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId205" tooltip="https://www.amazon.es/dp/B0FYM1D13D"/>
+    <hyperlink ref="M29" r:id="rId206" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N29" r:id="rId207"/>
+    <hyperlink ref="C30" r:id="rId208" tooltip="https://www.amazon.es/dp/B0DWK8LJF9"/>
+    <hyperlink ref="G30" r:id="rId209" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=aichilra"/>
+    <hyperlink ref="J30" r:id="rId210" tooltip="https://www.amazon.es/dp/B0DWK8LJF9?psc=1"/>
+    <hyperlink ref="K30" r:id="rId211" tooltip="https://m.media-amazon.com/images/I/41ZFdwgCWGL._AC_US200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId212" tooltip="https://www.amazon.es/dp/B0DWK8LJF9"/>
+    <hyperlink ref="M30" r:id="rId213" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N30" r:id="rId214"/>
+    <hyperlink ref="C31" r:id="rId215" tooltip="https://www.amazon.es/dp/B0DNYVJ4PL"/>
+    <hyperlink ref="G31" r:id="rId216" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=FEPPO"/>
+    <hyperlink ref="J31" r:id="rId217" tooltip="https://www.amazon.es/dp/B0DNYVJ4PL?psc=1"/>
+    <hyperlink ref="K31" r:id="rId218" tooltip="https://m.media-amazon.com/images/I/41IqIqkjgVL._AC_US200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId219" tooltip="https://www.amazon.es/dp/B0DZTSQFKR"/>
+    <hyperlink ref="M31" r:id="rId220" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N31" r:id="rId221"/>
+    <hyperlink ref="C32" r:id="rId222" tooltip="https://www.amazon.es/dp/B0FBX24WH6"/>
+    <hyperlink ref="G32" r:id="rId223" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=syayw"/>
+    <hyperlink ref="J32" r:id="rId224" tooltip="https://www.amazon.es/dp/B0FBX24WH6?psc=1"/>
+    <hyperlink ref="K32" r:id="rId225" tooltip="https://images-na.ssl-images-amazon.com/images/I/61LvanTuKlL._AC_US600_.jpg"/>
+    <hyperlink ref="L32" r:id="rId226" tooltip="https://www.amazon.es/dp/B0FQ4FRYT7"/>
+    <hyperlink ref="M32" r:id="rId227" tooltip="https://www.amazon.es/b?node=2404713031"/>
+    <hyperlink ref="N32" r:id="rId228"/>
+    <hyperlink ref="AW32" r:id="rId229" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3T9BSXCSWI46M"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <drawing r:id="rId151"/>
+  <drawing r:id="rId230"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -7476,38 +9957,498 @@
         <v>21</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>192</v>
+        <v>514</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>193</v>
+        <v>515</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>194</v>
+        <v>516</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>195</v>
+        <v>517</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>196</v>
+        <v>73</v>
       </c>
       <c r="B2" s="15">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="C2" s="15">
-        <v>0</v>
+        <v>8991</v>
       </c>
       <c r="D2" s="15">
-        <v>0</v>
+        <v>386</v>
       </c>
       <c r="E2" s="15">
-        <v>0</v>
-      </c>
-      <c r="F2" s="19">
-        <v>5.06</v>
+        <v>33053</v>
+      </c>
+      <c r="F2" s="20">
+        <v>85.63</v>
       </c>
       <c r="G2" s="22">
+        <v>0.2901</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="15">
+        <v>62</v>
+      </c>
+      <c r="C3" s="15">
+        <v>4599</v>
+      </c>
+      <c r="D3" s="15">
+        <v>256</v>
+      </c>
+      <c r="E3" s="15">
+        <v>18990</v>
+      </c>
+      <c r="F3" s="20">
+        <v>74.18</v>
+      </c>
+      <c r="G3" s="22">
+        <v>0.17129999999999998</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="B4" s="15">
+        <v>55</v>
+      </c>
+      <c r="C4" s="15">
+        <v>1759</v>
+      </c>
+      <c r="D4" s="15">
+        <v>91</v>
+      </c>
+      <c r="E4" s="15">
+        <v>2911</v>
+      </c>
+      <c r="F4" s="20">
+        <v>31.99</v>
+      </c>
+      <c r="G4" s="22">
+        <v>0.1519</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="15">
+        <v>41</v>
+      </c>
+      <c r="C5" s="15">
+        <v>5945</v>
+      </c>
+      <c r="D5" s="15">
+        <v>319</v>
+      </c>
+      <c r="E5" s="15">
+        <v>46252</v>
+      </c>
+      <c r="F5" s="20">
+        <v>144.99</v>
+      </c>
+      <c r="G5" s="22">
+        <v>0.1133</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="B6" s="15">
+        <v>34</v>
+      </c>
+      <c r="C6" s="15">
+        <v>442</v>
+      </c>
+      <c r="D6" s="15">
+        <v>143</v>
+      </c>
+      <c r="E6" s="15">
+        <v>1858</v>
+      </c>
+      <c r="F6" s="20">
+        <v>13</v>
+      </c>
+      <c r="G6" s="22">
+        <v>0.09390000000000001</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" s="15">
+        <v>26</v>
+      </c>
+      <c r="C7" s="15">
+        <v>859</v>
+      </c>
+      <c r="D7" s="15">
+        <v>30</v>
+      </c>
+      <c r="E7" s="15">
+        <v>992</v>
+      </c>
+      <c r="F7" s="20">
+        <v>33.06</v>
+      </c>
+      <c r="G7" s="22">
+        <v>0.0718</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="B8" s="15">
+        <v>25</v>
+      </c>
+      <c r="C8" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D8" s="15">
+        <v>319</v>
+      </c>
+      <c r="E8" s="15">
+        <v>25514</v>
+      </c>
+      <c r="F8" s="20">
+        <v>79.98</v>
+      </c>
+      <c r="G8" s="22">
+        <v>0.0691</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" s="15">
+        <v>13</v>
+      </c>
+      <c r="C9" s="15">
+        <v>832</v>
+      </c>
+      <c r="D9" s="15">
+        <v>131</v>
+      </c>
+      <c r="E9" s="15">
+        <v>8383</v>
+      </c>
+      <c r="F9" s="20">
+        <v>63.99</v>
+      </c>
+      <c r="G9" s="22">
+        <v>0.0359</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="B10" s="15">
+        <v>1</v>
+      </c>
+      <c r="C10" s="15">
+        <v>8</v>
+      </c>
+      <c r="D10" s="15">
+        <v>30</v>
+      </c>
+      <c r="E10" s="15">
+        <v>250</v>
+      </c>
+      <c r="F10" s="20">
+        <v>8.33</v>
+      </c>
+      <c r="G10" s="22">
+        <v>0.0028000000000000004</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="B11" s="15">
+        <v>0</v>
+      </c>
+      <c r="C11" s="15">
+        <v>0</v>
+      </c>
+      <c r="D11" s="15">
+        <v>0</v>
+      </c>
+      <c r="E11" s="15">
+        <v>0</v>
+      </c>
+      <c r="F11" s="20">
+        <v>0</v>
+      </c>
+      <c r="G11" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="B12" s="15">
+        <v>0</v>
+      </c>
+      <c r="C12" s="15">
+        <v>0</v>
+      </c>
+      <c r="D12" s="15">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15">
+        <v>0</v>
+      </c>
+      <c r="F12" s="20">
+        <v>0</v>
+      </c>
+      <c r="G12" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="B13" s="15">
+        <v>0</v>
+      </c>
+      <c r="C13" s="15">
+        <v>0</v>
+      </c>
+      <c r="D13" s="15">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15">
+        <v>0</v>
+      </c>
+      <c r="F13" s="20">
+        <v>0</v>
+      </c>
+      <c r="G13" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="B14" s="15">
+        <v>0</v>
+      </c>
+      <c r="C14" s="15">
+        <v>0</v>
+      </c>
+      <c r="D14" s="15">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15">
+        <v>0</v>
+      </c>
+      <c r="F14" s="20">
+        <v>0</v>
+      </c>
+      <c r="G14" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="B15" s="15">
+        <v>0</v>
+      </c>
+      <c r="C15" s="15">
+        <v>0</v>
+      </c>
+      <c r="D15" s="15">
+        <v>0</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
+      </c>
+      <c r="F15" s="20">
+        <v>0</v>
+      </c>
+      <c r="G15" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="B16" s="15">
+        <v>0</v>
+      </c>
+      <c r="C16" s="15">
+        <v>0</v>
+      </c>
+      <c r="D16" s="15">
+        <v>0</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
+      </c>
+      <c r="F16" s="20">
+        <v>0</v>
+      </c>
+      <c r="G16" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="B17" s="15">
+        <v>0</v>
+      </c>
+      <c r="C17" s="15">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15">
+        <v>0</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0</v>
+      </c>
+      <c r="F17" s="20">
+        <v>0</v>
+      </c>
+      <c r="G17" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="B18" s="15">
+        <v>0</v>
+      </c>
+      <c r="C18" s="15">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15">
+        <v>0</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
+      </c>
+      <c r="F18" s="20">
+        <v>0</v>
+      </c>
+      <c r="G18" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="B19" s="15">
+        <v>0</v>
+      </c>
+      <c r="C19" s="15">
+        <v>0</v>
+      </c>
+      <c r="D19" s="15">
+        <v>0</v>
+      </c>
+      <c r="E19" s="15">
+        <v>0</v>
+      </c>
+      <c r="F19" s="20">
+        <v>59.99</v>
+      </c>
+      <c r="G19" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>471</v>
+      </c>
+      <c r="B20" s="15">
+        <v>0</v>
+      </c>
+      <c r="C20" s="15">
+        <v>0</v>
+      </c>
+      <c r="D20" s="15">
+        <v>0</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
+      </c>
+      <c r="F20" s="20">
+        <v>0</v>
+      </c>
+      <c r="G20" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>481</v>
+      </c>
+      <c r="B21" s="15">
+        <v>0</v>
+      </c>
+      <c r="C21" s="15">
+        <v>0</v>
+      </c>
+      <c r="D21" s="15">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15">
+        <v>0</v>
+      </c>
+      <c r="F21" s="20">
+        <v>0</v>
+      </c>
+      <c r="G21" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>494</v>
+      </c>
+      <c r="B22" s="15">
+        <v>0</v>
+      </c>
+      <c r="C22" s="15">
+        <v>0</v>
+      </c>
+      <c r="D22" s="15">
+        <v>0</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
+      </c>
+      <c r="F22" s="20">
+        <v>38.11</v>
+      </c>
+      <c r="G22" s="22">
         <v>0</v>
       </c>
     </row>
@@ -7519,7 +10460,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -7530,7 +10471,7 @@
   <sheetData>
     <row r="1" ht="27" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>197</v>
+        <v>518</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>19</v>
@@ -7539,38 +10480,337 @@
         <v>21</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>192</v>
+        <v>514</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>193</v>
+        <v>515</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>194</v>
+        <v>516</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>195</v>
+        <v>517</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>198</v>
+        <v>87</v>
       </c>
       <c r="B2" s="15">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="C2" s="15">
-        <v>0</v>
+        <v>9939</v>
       </c>
       <c r="D2" s="15">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="E2" s="15">
-        <v>0</v>
-      </c>
-      <c r="F2" s="19">
-        <v>5.06</v>
+        <v>31562</v>
+      </c>
+      <c r="F2" s="20">
+        <v>75.87</v>
       </c>
       <c r="G2" s="22">
+        <v>0.3619</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B3" s="15">
+        <v>55</v>
+      </c>
+      <c r="C3" s="15">
+        <v>1759</v>
+      </c>
+      <c r="D3" s="15">
+        <v>91</v>
+      </c>
+      <c r="E3" s="15">
+        <v>2911</v>
+      </c>
+      <c r="F3" s="20">
+        <v>31.99</v>
+      </c>
+      <c r="G3" s="22">
+        <v>0.1519</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="15">
+        <v>41</v>
+      </c>
+      <c r="C4" s="15">
+        <v>6970</v>
+      </c>
+      <c r="D4" s="15">
+        <v>155</v>
+      </c>
+      <c r="E4" s="15">
+        <v>26348</v>
+      </c>
+      <c r="F4" s="20">
+        <v>169.99</v>
+      </c>
+      <c r="G4" s="22">
+        <v>0.1133</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="15">
+        <v>39</v>
+      </c>
+      <c r="C5" s="15">
+        <v>2730</v>
+      </c>
+      <c r="D5" s="15">
+        <v>97</v>
+      </c>
+      <c r="E5" s="15">
+        <v>6789</v>
+      </c>
+      <c r="F5" s="20">
+        <v>69.99</v>
+      </c>
+      <c r="G5" s="22">
+        <v>0.10769999999999999</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B6" s="15">
+        <v>34</v>
+      </c>
+      <c r="C6" s="15">
+        <v>884</v>
+      </c>
+      <c r="D6" s="15">
+        <v>143</v>
+      </c>
+      <c r="E6" s="15">
+        <v>3717</v>
+      </c>
+      <c r="F6" s="20">
+        <v>25.99</v>
+      </c>
+      <c r="G6" s="22">
+        <v>0.09390000000000001</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="B7" s="15">
+        <v>25</v>
+      </c>
+      <c r="C7" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D7" s="15">
+        <v>319</v>
+      </c>
+      <c r="E7" s="15">
+        <v>25514</v>
+      </c>
+      <c r="F7" s="20">
+        <v>79.98</v>
+      </c>
+      <c r="G7" s="22">
+        <v>0.0691</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="15">
+        <v>23</v>
+      </c>
+      <c r="C8" s="15">
+        <v>3542</v>
+      </c>
+      <c r="D8" s="15">
+        <v>80</v>
+      </c>
+      <c r="E8" s="15">
+        <v>12318</v>
+      </c>
+      <c r="F8" s="20">
+        <v>153.98</v>
+      </c>
+      <c r="G8" s="22">
+        <v>0.0635</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" s="15">
+        <v>13</v>
+      </c>
+      <c r="C9" s="15">
+        <v>832</v>
+      </c>
+      <c r="D9" s="15">
+        <v>131</v>
+      </c>
+      <c r="E9" s="15">
+        <v>8383</v>
+      </c>
+      <c r="F9" s="20">
+        <v>63.99</v>
+      </c>
+      <c r="G9" s="22">
+        <v>0.0359</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="B10" s="15">
+        <v>1</v>
+      </c>
+      <c r="C10" s="15">
+        <v>25</v>
+      </c>
+      <c r="D10" s="15">
+        <v>30</v>
+      </c>
+      <c r="E10" s="15">
+        <v>750</v>
+      </c>
+      <c r="F10" s="20">
+        <v>24.99</v>
+      </c>
+      <c r="G10" s="22">
+        <v>0.0028000000000000004</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>519</v>
+      </c>
+      <c r="B11" s="15">
+        <v>0</v>
+      </c>
+      <c r="C11" s="15">
+        <v>0</v>
+      </c>
+      <c r="D11" s="15">
+        <v>0</v>
+      </c>
+      <c r="E11" s="15">
+        <v>0</v>
+      </c>
+      <c r="F11" s="20">
+        <v>0</v>
+      </c>
+      <c r="G11" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="B12" s="15">
+        <v>0</v>
+      </c>
+      <c r="C12" s="15">
+        <v>0</v>
+      </c>
+      <c r="D12" s="15">
+        <v>79</v>
+      </c>
+      <c r="E12" s="15">
+        <v>5747</v>
+      </c>
+      <c r="F12" s="20">
+        <v>72.75</v>
+      </c>
+      <c r="G12" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="B13" s="15">
+        <v>0</v>
+      </c>
+      <c r="C13" s="15">
+        <v>0</v>
+      </c>
+      <c r="D13" s="15">
+        <v>164</v>
+      </c>
+      <c r="E13" s="15">
+        <v>19678</v>
+      </c>
+      <c r="F13" s="20">
+        <v>119.99</v>
+      </c>
+      <c r="G13" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="B14" s="15">
+        <v>0</v>
+      </c>
+      <c r="C14" s="15">
+        <v>0</v>
+      </c>
+      <c r="D14" s="15">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15">
+        <v>0</v>
+      </c>
+      <c r="F14" s="20">
+        <v>59.99</v>
+      </c>
+      <c r="G14" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>505</v>
+      </c>
+      <c r="B15" s="15">
+        <v>0</v>
+      </c>
+      <c r="C15" s="15">
+        <v>0</v>
+      </c>
+      <c r="D15" s="15">
+        <v>0</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
+      </c>
+      <c r="F15" s="20">
+        <v>38.11</v>
+      </c>
+      <c r="G15" s="22">
         <v>0</v>
       </c>
     </row>
@@ -7590,37 +10830,37 @@
   <sheetData>
     <row r="1" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>199</v>
+        <v>520</v>
       </c>
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>200</v>
+        <v>521</v>
       </c>
     </row>
     <row r="3" ht="200" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="32" t="s">
-        <v>201</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
-        <v>202</v>
+        <v>523</v>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
-        <v>203</v>
+        <v>524</v>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:1" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
-        <v>204</v>
+        <v>525</v>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>205</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>
